--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -590,7 +590,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>100</v>
+        <v>74.86</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>100</v>
+        <v>73.8</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>100</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>100</v>
+        <v>73.17</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>100</v>
+        <v>72.22</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>100</v>
+        <v>72.22</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>100</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>100</v>
+        <v>70.87</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>100</v>
+        <v>68.92</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>100</v>
+        <v>68.88</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>100</v>
+        <v>68.73</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>100</v>
+        <v>68.72</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>100</v>
+        <v>67.62</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>100</v>
+        <v>67.37</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>100</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>100</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>100</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>100</v>
+        <v>65.83</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>100</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>100</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>100</v>
+        <v>65.02</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>100</v>
+        <v>64.72</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>100</v>
+        <v>64.63</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>100</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>100</v>
+        <v>63.57</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>100</v>
+        <v>63.31</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>100</v>
+        <v>62.67</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>100</v>
+        <v>60.67</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>100</v>
+        <v>59.67</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>100</v>
+        <v>59.13</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>100</v>
+        <v>59.13</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>100</v>
+        <v>55.31</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>100</v>
+        <v>55.31</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -425,96 +425,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R64"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kode KPPN</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kode BA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Kode Satker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Uraian Satker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Revisi DIPA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Deviasi Halaman III DIPA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kualitas Perencanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Penyerapan Anggaran</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Belanja Kontraktual</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Penyelesaian Tagihan</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Pengelolaan UP dan TUP</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Kualitas Pelaksanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Capaian Output</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Kualitas Hasil Pelaksanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Nilai Total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Konversi Bobot</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Dispensasi SPM (Pengurang)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Nilai Akhir (Nilai Total/Konversi Bobot)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Bulan</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Tahun</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Uraian Satker-RINGKAS</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Uraian Satker Final</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Satker</t>
         </is>
@@ -523,64 +553,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>690801</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" t="n">
         <v>94.89</v>
       </c>
-      <c r="F2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I2" t="n">
-        <v>100</v>
-      </c>
       <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" t="n">
+        <v>100</v>
+      </c>
+      <c r="P2" t="n">
         <v>88.98</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>90</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>98.86</v>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="U2" t="n">
         <v>2026</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>LOKA LABKESMAS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>LOKA LABKESMAS</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>LOKA LABKESMAS (690801)</t>
         </is>
@@ -589,23 +645,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>007130</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E3" t="n">
-        <v>100</v>
-      </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
@@ -616,37 +678,57 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" t="n">
+        <v>100</v>
+      </c>
+      <c r="M3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>75</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="U3" t="n">
         <v>2026</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>KEJARI  OKU</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>KEJARI  OKU</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>KEJARI  OKU (007130)</t>
         </is>
@@ -655,23 +737,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>692340</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" t="n">
-        <v>100</v>
-      </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
@@ -682,37 +770,57 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>75</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="U4" t="n">
         <v>2026</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>LAPAS MARTAPURA</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>LAPAS MARTAPURA</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>LAPAS MARTAPURA (692340)</t>
         </is>
@@ -721,23 +829,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>418458</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" t="n">
-        <v>100</v>
-      </c>
       <c r="F5" t="n">
         <v>100</v>
       </c>
@@ -748,37 +862,57 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>75</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="Q5" t="n">
+        <v>100</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75</v>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="U5" t="n">
         <v>2026</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>KEMENAG OKU (418458)</t>
         </is>
@@ -787,23 +921,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>641681</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>100</v>
-      </c>
-      <c r="D6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E6" t="n">
-        <v>100</v>
-      </c>
       <c r="F6" t="n">
         <v>100</v>
       </c>
@@ -814,37 +954,57 @@
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" t="n">
+        <v>100</v>
+      </c>
+      <c r="L6" t="n">
+        <v>100</v>
+      </c>
+      <c r="M6" t="n">
+        <v>100</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>75</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="n">
+        <v>100</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75</v>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="U6" t="n">
         <v>2026</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>POLRES OKU</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>POLRES OKU</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>POLRES OKU (641681)</t>
         </is>
@@ -853,23 +1013,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>098963</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" t="n">
-        <v>100</v>
-      </c>
       <c r="F7" t="n">
         <v>100</v>
       </c>
@@ -880,37 +1046,57 @@
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7" t="n">
+        <v>100</v>
+      </c>
+      <c r="K7" t="n">
+        <v>100</v>
+      </c>
+      <c r="L7" t="n">
+        <v>100</v>
+      </c>
+      <c r="M7" t="n">
+        <v>100</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>75</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="Q7" t="n">
+        <v>100</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="U7" t="n">
         <v>2026</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>PN BATURAJA</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>PN BATURAJA</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>PN BATURAJA (098963)</t>
         </is>
@@ -919,23 +1105,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>692339</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" t="n">
-        <v>100</v>
-      </c>
-      <c r="E8" t="n">
-        <v>100</v>
-      </c>
       <c r="F8" t="n">
         <v>100</v>
       </c>
@@ -946,37 +1138,57 @@
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" t="n">
+        <v>100</v>
+      </c>
+      <c r="K8" t="n">
+        <v>100</v>
+      </c>
+      <c r="L8" t="n">
+        <v>100</v>
+      </c>
+      <c r="M8" t="n">
+        <v>100</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>75</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="Q8" t="n">
+        <v>100</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="U8" t="n">
         <v>2026</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>RUTAN BATURAJA</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>RUTAN BATURAJA</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>RUTAN BATURAJA (692339)</t>
         </is>
@@ -985,23 +1197,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>692334</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>100</v>
-      </c>
-      <c r="D9" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" t="n">
-        <v>100</v>
-      </c>
       <c r="F9" t="n">
         <v>100</v>
       </c>
@@ -1012,37 +1230,57 @@
         <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
+        <v>100</v>
+      </c>
+      <c r="K9" t="n">
+        <v>100</v>
+      </c>
+      <c r="L9" t="n">
+        <v>100</v>
+      </c>
+      <c r="M9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>75</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>75</v>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="U9" t="n">
         <v>2026</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>LAPAS MUARA DUA</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>LAPAS MUARA DUA</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>LAPAS MUARA DUA (692334)</t>
         </is>
@@ -1051,23 +1289,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>685001</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D10" t="n">
-        <v>100</v>
-      </c>
-      <c r="E10" t="n">
-        <v>100</v>
-      </c>
       <c r="F10" t="n">
         <v>100</v>
       </c>
@@ -1078,37 +1322,57 @@
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
+        <v>100</v>
+      </c>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" t="n">
+        <v>100</v>
+      </c>
+      <c r="M10" t="n">
+        <v>100</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>75</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="Q10" t="n">
+        <v>100</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>75</v>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="U10" t="n">
         <v>2026</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>PUSLATPUR AD</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>PUSLATPUR AD</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>PUSLATPUR AD (685001)</t>
         </is>
@@ -1117,23 +1381,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>401944</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>100</v>
-      </c>
-      <c r="D11" t="n">
-        <v>100</v>
-      </c>
-      <c r="E11" t="n">
-        <v>100</v>
-      </c>
       <c r="F11" t="n">
         <v>100</v>
       </c>
@@ -1144,37 +1414,57 @@
         <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11" t="n">
+        <v>100</v>
+      </c>
+      <c r="K11" t="n">
+        <v>100</v>
+      </c>
+      <c r="L11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>75</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="Q11" t="n">
+        <v>100</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>75</v>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="U11" t="n">
         <v>2026</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>PA MARTAPURA</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>PA MARTAPURA</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>PA MARTAPURA (401944)</t>
         </is>
@@ -1183,23 +1473,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>402267</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>100</v>
-      </c>
-      <c r="D12" t="n">
-        <v>100</v>
-      </c>
-      <c r="E12" t="n">
-        <v>100</v>
-      </c>
       <c r="F12" t="n">
         <v>100</v>
       </c>
@@ -1210,37 +1506,57 @@
         <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
+      <c r="L12" t="n">
+        <v>100</v>
+      </c>
+      <c r="M12" t="n">
+        <v>100</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>75</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="Q12" t="n">
+        <v>100</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>75</v>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="U12" t="n">
         <v>2026</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>PA BATURAJA</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>PA BATURAJA</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>PA BATURAJA (402267)</t>
         </is>
@@ -1249,23 +1565,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>402268</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="n">
-        <v>100</v>
-      </c>
-      <c r="E13" t="n">
-        <v>100</v>
-      </c>
       <c r="F13" t="n">
         <v>100</v>
       </c>
@@ -1276,37 +1598,57 @@
         <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" t="n">
+        <v>100</v>
+      </c>
+      <c r="M13" t="n">
+        <v>100</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>75</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="Q13" t="n">
+        <v>100</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>75</v>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="U13" t="n">
         <v>2026</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>PA BATURAJA</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>PA BATURAJA</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>PA BATURAJA (402268)</t>
         </is>
@@ -1315,23 +1657,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>403409</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D14" t="n">
-        <v>100</v>
-      </c>
-      <c r="E14" t="n">
-        <v>100</v>
-      </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
@@ -1342,37 +1690,57 @@
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14" t="n">
+        <v>100</v>
+      </c>
+      <c r="K14" t="n">
+        <v>100</v>
+      </c>
+      <c r="L14" t="n">
+        <v>100</v>
+      </c>
+      <c r="M14" t="n">
+        <v>100</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>75</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="Q14" t="n">
+        <v>100</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>75</v>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="U14" t="n">
         <v>2026</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>PA MARTAPURA</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>PA MARTAPURA</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>PA MARTAPURA (403409)</t>
         </is>
@@ -1381,23 +1749,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>403410</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="n">
-        <v>100</v>
-      </c>
-      <c r="E15" t="n">
-        <v>100</v>
-      </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
@@ -1408,37 +1782,57 @@
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" t="n">
+        <v>100</v>
+      </c>
+      <c r="K15" t="n">
+        <v>100</v>
+      </c>
+      <c r="L15" t="n">
+        <v>100</v>
+      </c>
+      <c r="M15" t="n">
+        <v>100</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>75</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="Q15" t="n">
+        <v>100</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="U15" t="n">
         <v>2026</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>PA  MUARADUA</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>PA  MUARADUA</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>PA  MUARADUA (403410)</t>
         </is>
@@ -1447,23 +1841,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>665307</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="n">
-        <v>100</v>
-      </c>
-      <c r="E16" t="n">
-        <v>100</v>
-      </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
@@ -1474,37 +1874,57 @@
         <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16" t="n">
+        <v>100</v>
+      </c>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
+      <c r="L16" t="n">
+        <v>100</v>
+      </c>
+      <c r="M16" t="n">
+        <v>100</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>75</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="Q16" t="n">
+        <v>100</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>75</v>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="U16" t="n">
         <v>2026</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>POLRES OKUS</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>POLRES OKUS</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>POLRES OKUS (665307)</t>
         </is>
@@ -1513,23 +1933,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>665292</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>100</v>
-      </c>
-      <c r="D17" t="n">
-        <v>100</v>
-      </c>
-      <c r="E17" t="n">
-        <v>100</v>
-      </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
@@ -1540,37 +1966,57 @@
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17" t="n">
+        <v>100</v>
+      </c>
+      <c r="K17" t="n">
+        <v>100</v>
+      </c>
+      <c r="L17" t="n">
+        <v>100</v>
+      </c>
+      <c r="M17" t="n">
+        <v>100</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>75</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="Q17" t="n">
+        <v>100</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="U17" t="n">
         <v>2026</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>POLRES OKUT</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>POLRES OKUT</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>POLRES OKUT (665292)</t>
         </is>
@@ -1579,64 +2025,90 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>401945</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>100</v>
-      </c>
-      <c r="D18" t="n">
-        <v>100</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" t="n">
+        <v>100</v>
+      </c>
+      <c r="H18" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" t="n">
         <v>99.31999999999999</v>
       </c>
-      <c r="F18" t="n">
-        <v>100</v>
-      </c>
-      <c r="G18" t="n">
-        <v>100</v>
-      </c>
-      <c r="H18" t="n">
-        <v>100</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
       <c r="J18" t="n">
+        <v>100</v>
+      </c>
+      <c r="K18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L18" t="n">
+        <v>100</v>
+      </c>
+      <c r="M18" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>74.86</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
+      <c r="Q18" t="n">
+        <v>100</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="U18" t="n">
         <v>2026</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>PA MUARADUA</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>PA MUARADUA</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>PA MUARADUA (401945)</t>
         </is>
@@ -1645,64 +2117,90 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>424967</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>100</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
+        <v>100</v>
+      </c>
+      <c r="G19" t="n">
         <v>92.03</v>
       </c>
-      <c r="E19" t="n">
-        <v>100</v>
-      </c>
-      <c r="F19" t="n">
-        <v>100</v>
-      </c>
-      <c r="G19" t="n">
-        <v>100</v>
-      </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>96.02</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19" t="n">
+        <v>100</v>
+      </c>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
+      <c r="L19" t="n">
+        <v>100</v>
+      </c>
+      <c r="M19" t="n">
+        <v>100</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>73.8</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="Q19" t="n">
+        <v>100</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="U19" t="n">
         <v>2026</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>MTSN 1 OKUT</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>MTSN 1 OKUT</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>MTSN 1 OKUT (424967)</t>
         </is>
@@ -1711,64 +2209,90 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>007208</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>100</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
+        <v>100</v>
+      </c>
+      <c r="G20" t="n">
         <v>90.97</v>
       </c>
-      <c r="E20" t="n">
-        <v>100</v>
-      </c>
-      <c r="F20" t="n">
-        <v>100</v>
-      </c>
-      <c r="G20" t="n">
-        <v>100</v>
-      </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" t="n">
+        <v>100</v>
+      </c>
+      <c r="K20" t="n">
+        <v>100</v>
+      </c>
+      <c r="L20" t="n">
+        <v>100</v>
+      </c>
+      <c r="M20" t="n">
+        <v>100</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>73.65000000000001</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="Q20" t="n">
+        <v>100</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="T20" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="U20" t="n">
         <v>2026</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>KEJARI OKUS</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>KEJARI OKUS</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>KEJARI OKUS (007208)</t>
         </is>
@@ -1777,64 +2301,90 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>007190</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>100</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" t="n">
         <v>87.83</v>
       </c>
-      <c r="E21" t="n">
-        <v>100</v>
-      </c>
-      <c r="F21" t="n">
-        <v>100</v>
-      </c>
-      <c r="G21" t="n">
-        <v>100</v>
-      </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>93.92</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21" t="n">
+        <v>100</v>
+      </c>
+      <c r="K21" t="n">
+        <v>100</v>
+      </c>
+      <c r="L21" t="n">
+        <v>100</v>
+      </c>
+      <c r="M21" t="n">
+        <v>100</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>73.17</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="Q21" t="n">
+        <v>100</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>73.17</v>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="U21" t="n">
         <v>2026</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>KEJARI OKUT</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>KEJARI OKUT</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>KEJARI OKUT (007190)</t>
         </is>
@@ -1843,64 +2393,90 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>410574</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>100</v>
-      </c>
-      <c r="D22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" t="n">
-        <v>100</v>
-      </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" t="n">
+        <v>100</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>65</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="Q22" t="n">
+        <v>90</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O22" t="n">
+      <c r="U22" t="n">
         <v>2026</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>KPP BATURAJA</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>KPP BATURAJA</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>KPP BATURAJA (410574)</t>
         </is>
@@ -1909,64 +2485,90 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>666501</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>100</v>
-      </c>
-      <c r="D23" t="n">
-        <v>100</v>
-      </c>
-      <c r="E23" t="n">
-        <v>100</v>
-      </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23" t="n">
+        <v>100</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>100</v>
+      </c>
+      <c r="M23" t="n">
+        <v>100</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>65</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
+      <c r="Q23" t="n">
+        <v>90</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="U23" t="n">
         <v>2026</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (666501)</t>
         </is>
@@ -1975,64 +2577,90 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>686503</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>100</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
+        <v>100</v>
+      </c>
+      <c r="G24" t="n">
         <v>78.08</v>
       </c>
-      <c r="E24" t="n">
-        <v>100</v>
-      </c>
-      <c r="F24" t="n">
-        <v>100</v>
-      </c>
-      <c r="G24" t="n">
-        <v>100</v>
-      </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24" t="n">
+        <v>100</v>
+      </c>
+      <c r="K24" t="n">
+        <v>100</v>
+      </c>
+      <c r="L24" t="n">
+        <v>100</v>
+      </c>
+      <c r="M24" t="n">
+        <v>100</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>71.70999999999999</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="Q24" t="n">
+        <v>100</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>71.70999999999999</v>
+      </c>
+      <c r="T24" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="U24" t="n">
         <v>2026</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>BAWASLU OKUS</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>BAWASLU OKUS</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>BAWASLU OKUS (686503)</t>
         </is>
@@ -2041,64 +2669,90 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>426050</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>100</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
+        <v>100</v>
+      </c>
+      <c r="G25" t="n">
         <v>91.87</v>
       </c>
-      <c r="E25" t="n">
-        <v>100</v>
-      </c>
-      <c r="F25" t="n">
-        <v>100</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>95.94</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25" t="n">
+        <v>100</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>100</v>
+      </c>
+      <c r="M25" t="n">
+        <v>100</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>63.78</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="Q25" t="n">
+        <v>90</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="T25" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="U25" t="n">
         <v>2026</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>MTSN 1 OKU</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>MTSN 1 OKU</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>MTSN 1 OKU (426050)</t>
         </is>
@@ -2107,64 +2761,90 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>426066</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>100</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" t="n">
         <v>76.67</v>
       </c>
-      <c r="E26" t="n">
+      <c r="H26" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="I26" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="F26" t="n">
-        <v>100</v>
-      </c>
-      <c r="G26" t="n">
-        <v>100</v>
-      </c>
-      <c r="H26" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
       <c r="J26" t="n">
+        <v>100</v>
+      </c>
+      <c r="K26" t="n">
+        <v>100</v>
+      </c>
+      <c r="L26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M26" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>68.92</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="Q26" t="n">
+        <v>100</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>68.92</v>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="U26" t="n">
         <v>2026</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>MAN 1 OKUT</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>MAN 1 OKUT</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>MAN 1 OKUT (426066)</t>
         </is>
@@ -2173,64 +2853,90 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>668529</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>100</v>
-      </c>
-      <c r="D27" t="n">
-        <v>100</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
+        <v>100</v>
+      </c>
+      <c r="G27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H27" t="n">
+        <v>100</v>
+      </c>
+      <c r="I27" t="n">
         <v>84.94</v>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H27" t="n">
-        <v>100</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>100</v>
+      </c>
+      <c r="L27" t="n">
+        <v>100</v>
+      </c>
+      <c r="M27" t="n">
+        <v>94.98</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>61.99</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="Q27" t="n">
+        <v>90</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="T27" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="U27" t="n">
         <v>2026</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>BPS OKUT</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>BPS OKUT</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>BPS OKUT (668529)</t>
         </is>
@@ -2239,64 +2945,90 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>667215</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>100</v>
-      </c>
-      <c r="D28" t="n">
-        <v>100</v>
-      </c>
-      <c r="E28" t="n">
-        <v>100</v>
-      </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>100</v>
+      </c>
+      <c r="M28" t="n">
+        <v>100</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>55</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="Q28" t="n">
+        <v>80</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T28" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="U28" t="n">
         <v>2026</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>BPS OKUS</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>BPS OKUS</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>BPS OKUS (667215)</t>
         </is>
@@ -2305,64 +3037,90 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>440505</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>100</v>
-      </c>
-      <c r="D29" t="n">
-        <v>100</v>
-      </c>
-      <c r="E29" t="n">
-        <v>100</v>
-      </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>100</v>
+      </c>
+      <c r="M29" t="n">
+        <v>100</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
         <v>55</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="Q29" t="n">
+        <v>80</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T29" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="U29" t="n">
         <v>2026</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>KEMENAG OKUS (440505)</t>
         </is>
@@ -2371,64 +3129,90 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>440506</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>100</v>
-      </c>
-      <c r="D30" t="n">
-        <v>100</v>
-      </c>
-      <c r="E30" t="n">
-        <v>100</v>
-      </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>100</v>
+      </c>
+      <c r="M30" t="n">
+        <v>100</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>55</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="Q30" t="n">
+        <v>80</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O30" t="n">
+      <c r="U30" t="n">
         <v>2026</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>KEMENAG OKUS (440506)</t>
         </is>
@@ -2437,64 +3221,90 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>527975</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>100</v>
-      </c>
-      <c r="D31" t="n">
-        <v>100</v>
-      </c>
-      <c r="E31" t="n">
-        <v>100</v>
-      </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>100</v>
+      </c>
+      <c r="M31" t="n">
+        <v>100</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>55</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="Q31" t="n">
+        <v>80</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T31" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O31" t="n">
+      <c r="U31" t="n">
         <v>2026</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>KPPN BATURAJA</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>KPPN BATURAJA</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>KPPN BATURAJA (527975)</t>
         </is>
@@ -2503,64 +3313,90 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>666505</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>100</v>
-      </c>
-      <c r="D32" t="n">
-        <v>100</v>
-      </c>
-      <c r="E32" t="n">
-        <v>100</v>
-      </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>100</v>
+      </c>
+      <c r="M32" t="n">
+        <v>100</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>55</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="Q32" t="n">
+        <v>80</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T32" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O32" t="n">
+      <c r="U32" t="n">
         <v>2026</v>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (666505)</t>
         </is>
@@ -2569,64 +3405,90 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>666504</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>100</v>
-      </c>
-      <c r="D33" t="n">
-        <v>100</v>
-      </c>
-      <c r="E33" t="n">
-        <v>100</v>
-      </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>100</v>
+      </c>
+      <c r="M33" t="n">
+        <v>100</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>55</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
+      <c r="Q33" t="n">
+        <v>80</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T33" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="U33" t="n">
         <v>2026</v>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (666504)</t>
         </is>
@@ -2635,64 +3497,90 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>656574</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>100</v>
-      </c>
-      <c r="D34" t="n">
-        <v>100</v>
-      </c>
-      <c r="E34" t="n">
-        <v>100</v>
-      </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>100</v>
+      </c>
+      <c r="M34" t="n">
+        <v>100</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>55</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
+      <c r="Q34" t="n">
+        <v>80</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T34" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O34" t="n">
+      <c r="U34" t="n">
         <v>2026</v>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>KPU OKUS</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>KPU OKUS</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>KPU OKUS (656574)</t>
         </is>
@@ -2701,64 +3589,90 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>418462</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>100</v>
-      </c>
-      <c r="D35" t="n">
-        <v>100</v>
-      </c>
-      <c r="E35" t="n">
-        <v>100</v>
-      </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>100</v>
+      </c>
+      <c r="M35" t="n">
+        <v>100</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>55</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="Q35" t="n">
+        <v>80</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T35" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O35" t="n">
+      <c r="U35" t="n">
         <v>2026</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>MTSN 2 OKUS</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>MTSN 2 OKUS</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>MTSN 2 OKUS (418462)</t>
         </is>
@@ -2767,64 +3681,90 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>440503</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>100</v>
-      </c>
-      <c r="D36" t="n">
-        <v>100</v>
-      </c>
-      <c r="E36" t="n">
-        <v>100</v>
-      </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>100</v>
+      </c>
+      <c r="M36" t="n">
+        <v>100</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>55</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
+      <c r="Q36" t="n">
+        <v>80</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T36" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="U36" t="n">
         <v>2026</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>KEMENAG OKUS (440503)</t>
         </is>
@@ -2833,64 +3773,90 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>440502</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>100</v>
-      </c>
-      <c r="D37" t="n">
-        <v>100</v>
-      </c>
-      <c r="E37" t="n">
-        <v>100</v>
-      </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>100</v>
+      </c>
+      <c r="M37" t="n">
+        <v>100</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>55</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
+      <c r="Q37" t="n">
+        <v>80</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T37" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O37" t="n">
+      <c r="U37" t="n">
         <v>2026</v>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>KEMENAG OKUS (440502)</t>
         </is>
@@ -2899,64 +3865,90 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>111079</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>100</v>
-      </c>
-      <c r="D38" t="n">
-        <v>100</v>
-      </c>
-      <c r="E38" t="n">
-        <v>100</v>
-      </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>100</v>
+      </c>
+      <c r="M38" t="n">
+        <v>100</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
         <v>55</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="Q38" t="n">
+        <v>80</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T38" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O38" t="n">
+      <c r="U38" t="n">
         <v>2026</v>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>BNN OKUT</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>BNN OKUT</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>BNN OKUT (111079)</t>
         </is>
@@ -2965,64 +3957,90 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>111071</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>100</v>
-      </c>
-      <c r="D39" t="n">
-        <v>100</v>
-      </c>
-      <c r="E39" t="n">
-        <v>100</v>
-      </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>100</v>
+      </c>
+      <c r="M39" t="n">
+        <v>100</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>55</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
+      <c r="Q39" t="n">
+        <v>80</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T39" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O39" t="n">
+      <c r="U39" t="n">
         <v>2026</v>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (111071)</t>
         </is>
@@ -3031,64 +4049,90 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>656553</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>100</v>
-      </c>
-      <c r="D40" t="n">
-        <v>100</v>
-      </c>
-      <c r="E40" t="n">
-        <v>100</v>
-      </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>100</v>
+      </c>
+      <c r="M40" t="n">
+        <v>100</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
         <v>55</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="Q40" t="n">
+        <v>80</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T40" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O40" t="n">
+      <c r="U40" t="n">
         <v>2026</v>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>KPU OKU</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>KPU OKU</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>KPU OKU (656553)</t>
         </is>
@@ -3097,64 +4141,90 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>692625</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>100</v>
-      </c>
-      <c r="D41" t="n">
-        <v>100</v>
-      </c>
-      <c r="E41" t="n">
-        <v>100</v>
-      </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>100</v>
+      </c>
+      <c r="M41" t="n">
+        <v>100</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>55</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="Q41" t="n">
+        <v>80</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T41" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O41" t="n">
+      <c r="U41" t="n">
         <v>2026</v>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>BAPAS OKU INDUK</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>BAPAS OKU INDUK</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>BAPAS OKU INDUK (692625)</t>
         </is>
@@ -3163,64 +4233,90 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>099228</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>100</v>
-      </c>
-      <c r="D42" t="n">
-        <v>100</v>
-      </c>
-      <c r="E42" t="n">
-        <v>100</v>
-      </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>100</v>
+      </c>
+      <c r="M42" t="n">
+        <v>100</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>55</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="Q42" t="n">
+        <v>80</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T42" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O42" t="n">
+      <c r="U42" t="n">
         <v>2026</v>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>PN BATURAJA</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>PN BATURAJA</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>PN BATURAJA (099228)</t>
         </is>
@@ -3229,64 +4325,90 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>656560</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>100</v>
-      </c>
-      <c r="D43" t="n">
-        <v>100</v>
-      </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" t="n">
+        <v>100</v>
+      </c>
+      <c r="H43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>100</v>
+      </c>
+      <c r="M43" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
         <v>54.98</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
+      <c r="Q43" t="n">
+        <v>80</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="T43" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O43" t="n">
+      <c r="U43" t="n">
         <v>2026</v>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>KPU OKUT</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>KPU OKUT</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>KPU OKUT (656560)</t>
         </is>
@@ -3295,64 +4417,90 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>418456</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>100</v>
-      </c>
-      <c r="D44" t="n">
-        <v>100</v>
-      </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
+        <v>100</v>
+      </c>
+      <c r="G44" t="n">
+        <v>100</v>
+      </c>
+      <c r="H44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" t="n">
         <v>99.86</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>100</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>100</v>
+      </c>
+      <c r="M44" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
         <v>54.97</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="Q44" t="n">
+        <v>80</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>68.72</v>
+      </c>
+      <c r="T44" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O44" t="n">
+      <c r="U44" t="n">
         <v>2026</v>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>KEMENAG OKU (418456)</t>
         </is>
@@ -3361,64 +4509,90 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>428258</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>100</v>
-      </c>
-      <c r="D45" t="n">
+      <c r="F45" t="n">
+        <v>100</v>
+      </c>
+      <c r="G45" t="n">
         <v>93.98</v>
       </c>
-      <c r="E45" t="n">
-        <v>100</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>100</v>
+      </c>
+      <c r="M45" t="n">
+        <v>100</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
         <v>54.1</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
+      <c r="Q45" t="n">
+        <v>80</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>67.62</v>
+      </c>
+      <c r="T45" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O45" t="n">
+      <c r="U45" t="n">
         <v>2026</v>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>BPS OKU</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>BPS OKU</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>BPS OKU (428258)</t>
         </is>
@@ -3427,64 +4601,90 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>344894</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>100</v>
-      </c>
-      <c r="D46" t="n">
+      <c r="F46" t="n">
+        <v>100</v>
+      </c>
+      <c r="G46" t="n">
         <v>74.04000000000001</v>
       </c>
-      <c r="E46" t="n">
+      <c r="H46" t="n">
+        <v>87.02</v>
+      </c>
+      <c r="I46" t="n">
         <v>97.62</v>
       </c>
-      <c r="F46" t="n">
-        <v>100</v>
-      </c>
-      <c r="G46" t="n">
-        <v>100</v>
-      </c>
-      <c r="H46" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
       <c r="J46" t="n">
+        <v>100</v>
+      </c>
+      <c r="K46" t="n">
+        <v>100</v>
+      </c>
+      <c r="L46" t="n">
+        <v>100</v>
+      </c>
+      <c r="M46" t="n">
+        <v>100</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
         <v>60.63</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
+      <c r="Q46" t="n">
+        <v>90</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="T46" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O46" t="n">
+      <c r="U46" t="n">
         <v>2026</v>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>RUMKIT NOESMIR</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>RUMKIT NOESMIR</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>RUMKIT NOESMIR (344894)</t>
         </is>
@@ -3493,64 +4693,90 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>431142</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>100</v>
-      </c>
-      <c r="D47" t="n">
-        <v>100</v>
-      </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
+        <v>100</v>
+      </c>
+      <c r="G47" t="n">
+        <v>100</v>
+      </c>
+      <c r="H47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I47" t="n">
         <v>94.26000000000001</v>
       </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>100</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>100</v>
+      </c>
+      <c r="M47" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
         <v>53.85</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
+      <c r="Q47" t="n">
+        <v>80</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="T47" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O47" t="n">
+      <c r="U47" t="n">
         <v>2026</v>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>BPN OKU</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>BPN OKU</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>BPN OKU (431142)</t>
         </is>
@@ -3559,64 +4785,90 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>424245</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>100</v>
-      </c>
-      <c r="D48" t="n">
+      <c r="F48" t="n">
+        <v>100</v>
+      </c>
+      <c r="G48" t="n">
         <v>91.63</v>
       </c>
-      <c r="E48" t="n">
-        <v>100</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>100</v>
+      </c>
+      <c r="M48" t="n">
+        <v>100</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
         <v>53.74</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
+      <c r="Q48" t="n">
+        <v>80</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>67.18000000000001</v>
+      </c>
+      <c r="T48" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O48" t="n">
+      <c r="U48" t="n">
         <v>2026</v>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>MAN 1 OKU</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>MAN 1 OKU</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>MAN 1 OKU (424245)</t>
         </is>
@@ -3625,64 +4877,90 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>597558</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>100</v>
-      </c>
-      <c r="D49" t="n">
-        <v>100</v>
-      </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
+        <v>100</v>
+      </c>
+      <c r="G49" t="n">
+        <v>100</v>
+      </c>
+      <c r="H49" t="n">
+        <v>100</v>
+      </c>
+      <c r="I49" t="n">
         <v>93.59</v>
       </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>100</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>100</v>
+      </c>
+      <c r="M49" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
         <v>53.72</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
+      <c r="Q49" t="n">
+        <v>80</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="T49" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O49" t="n">
+      <c r="U49" t="n">
         <v>2026</v>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>MAN 2 OKUS</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>MAN 2 OKUS</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>MAN 2 OKUS (597558)</t>
         </is>
@@ -3691,64 +4969,90 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>666503</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>100</v>
-      </c>
-      <c r="D50" t="n">
+      <c r="F50" t="n">
+        <v>100</v>
+      </c>
+      <c r="G50" t="n">
         <v>71.22</v>
       </c>
-      <c r="E50" t="n">
+      <c r="H50" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="I50" t="n">
         <v>92.81999999999999</v>
       </c>
-      <c r="F50" t="n">
-        <v>100</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>100</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
       <c r="J50" t="n">
+        <v>100</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>100</v>
+      </c>
+      <c r="M50" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
         <v>59.25</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="Q50" t="n">
+        <v>90</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="T50" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O50" t="n">
+      <c r="U50" t="n">
         <v>2026</v>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (666503)</t>
         </is>
@@ -3757,64 +5061,90 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>418457</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>100</v>
-      </c>
-      <c r="D51" t="n">
-        <v>100</v>
-      </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
+        <v>100</v>
+      </c>
+      <c r="G51" t="n">
+        <v>100</v>
+      </c>
+      <c r="H51" t="n">
+        <v>100</v>
+      </c>
+      <c r="I51" t="n">
         <v>85.97</v>
       </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>100</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>100</v>
+      </c>
+      <c r="M51" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
         <v>52.19</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
+      <c r="Q51" t="n">
+        <v>80</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="T51" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O51" t="n">
+      <c r="U51" t="n">
         <v>2026</v>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>KEMENAG OKU (418457)</t>
         </is>
@@ -3823,64 +5153,90 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>418459</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>100</v>
-      </c>
-      <c r="D52" t="n">
-        <v>100</v>
-      </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
+        <v>100</v>
+      </c>
+      <c r="G52" t="n">
+        <v>100</v>
+      </c>
+      <c r="H52" t="n">
+        <v>100</v>
+      </c>
+      <c r="I52" t="n">
         <v>85.41</v>
       </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>100</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
       <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>100</v>
+      </c>
+      <c r="M52" t="n">
+        <v>92.70999999999999</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
         <v>52.08</v>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
+      <c r="Q52" t="n">
+        <v>80</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="T52" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O52" t="n">
+      <c r="U52" t="n">
         <v>2026</v>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>KEMENAG OKU (418459)</t>
         </is>
@@ -3889,64 +5245,90 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>553792</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>100</v>
-      </c>
-      <c r="D53" t="n">
+      <c r="F53" t="n">
+        <v>100</v>
+      </c>
+      <c r="G53" t="n">
         <v>80.12</v>
       </c>
-      <c r="E53" t="n">
-        <v>100</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>90.06</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>100</v>
+      </c>
+      <c r="M53" t="n">
+        <v>100</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
         <v>52.02</v>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
+      <c r="Q53" t="n">
+        <v>80</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>65.02</v>
+      </c>
+      <c r="T53" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O53" t="n">
+      <c r="U53" t="n">
         <v>2026</v>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>MTSN 1 OKUS</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>MTSN 1 OKUS</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>MTSN 1 OKUS (553792)</t>
         </is>
@@ -3955,64 +5337,90 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>418471</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>100</v>
-      </c>
-      <c r="D54" t="n">
+      <c r="F54" t="n">
+        <v>100</v>
+      </c>
+      <c r="G54" t="n">
         <v>61.58</v>
       </c>
-      <c r="E54" t="n">
+      <c r="H54" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="I54" t="n">
         <v>77.42</v>
       </c>
-      <c r="F54" t="n">
-        <v>100</v>
-      </c>
-      <c r="G54" t="n">
-        <v>100</v>
-      </c>
-      <c r="H54" t="n">
-        <v>100</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
       <c r="J54" t="n">
+        <v>100</v>
+      </c>
+      <c r="K54" t="n">
+        <v>100</v>
+      </c>
+      <c r="L54" t="n">
+        <v>100</v>
+      </c>
+      <c r="M54" t="n">
+        <v>94.36</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
         <v>64.72</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
+      <c r="Q54" t="n">
+        <v>100</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="T54" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O54" t="n">
+      <c r="U54" t="n">
         <v>2026</v>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>MTSN 2 OKUT</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>MTSN 2 OKUT</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>MTSN 2 OKUT (418471)</t>
         </is>
@@ -4021,64 +5429,90 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>553099</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>100</v>
-      </c>
-      <c r="D55" t="n">
+      <c r="F55" t="n">
+        <v>100</v>
+      </c>
+      <c r="G55" t="n">
         <v>78.01000000000001</v>
       </c>
-      <c r="E55" t="n">
-        <v>100</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>100</v>
+      </c>
+      <c r="M55" t="n">
+        <v>100</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
         <v>51.7</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
+      <c r="Q55" t="n">
+        <v>80</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>64.63</v>
+      </c>
+      <c r="T55" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O55" t="n">
+      <c r="U55" t="n">
         <v>2026</v>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>MTSN 3 OKUT</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>MTSN 3 OKUT</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>MTSN 3 OKUT (553099)</t>
         </is>
@@ -4087,64 +5521,90 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>440504</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>100</v>
-      </c>
-      <c r="D56" t="n">
+      <c r="F56" t="n">
+        <v>100</v>
+      </c>
+      <c r="G56" t="n">
         <v>94.52</v>
       </c>
-      <c r="E56" t="n">
+      <c r="H56" t="n">
+        <v>97.26000000000001</v>
+      </c>
+      <c r="I56" t="n">
         <v>85.13</v>
       </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>100</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
       <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>100</v>
+      </c>
+      <c r="M56" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
         <v>51.2</v>
       </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
+      <c r="Q56" t="n">
+        <v>80</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="T56" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O56" t="n">
+      <c r="U56" t="n">
         <v>2026</v>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>KEMENAG OKUS (440504)</t>
         </is>
@@ -4153,64 +5613,90 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>670561</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>100</v>
-      </c>
-      <c r="D57" t="n">
+      <c r="F57" t="n">
+        <v>100</v>
+      </c>
+      <c r="G57" t="n">
         <v>90.37</v>
       </c>
-      <c r="E57" t="n">
+      <c r="H57" t="n">
+        <v>95.19</v>
+      </c>
+      <c r="I57" t="n">
         <v>86.52</v>
       </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>100</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
       <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>100</v>
+      </c>
+      <c r="M57" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
         <v>50.86</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
+      <c r="Q57" t="n">
+        <v>80</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="T57" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O57" t="n">
+      <c r="U57" t="n">
         <v>2026</v>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>BPN OKUS</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>BPN OKUS</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>BPN OKUS (670561)</t>
         </is>
@@ -4219,64 +5705,90 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>419006</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>100</v>
-      </c>
-      <c r="D58" t="n">
+      <c r="F58" t="n">
+        <v>100</v>
+      </c>
+      <c r="G58" t="n">
         <v>79.26000000000001</v>
       </c>
-      <c r="E58" t="n">
+      <c r="H58" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I58" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>100</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
       <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>100</v>
+      </c>
+      <c r="M58" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
         <v>50.65</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
+      <c r="Q58" t="n">
+        <v>80</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="T58" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O58" t="n">
+      <c r="U58" t="n">
         <v>2026</v>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>BAWASLU OKU</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>BAWASLU OKU</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>BAWASLU OKU (419006)</t>
         </is>
@@ -4285,64 +5797,90 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>574370</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>100</v>
-      </c>
-      <c r="D59" t="n">
-        <v>100</v>
-      </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
+        <v>100</v>
+      </c>
+      <c r="G59" t="n">
+        <v>100</v>
+      </c>
+      <c r="H59" t="n">
+        <v>100</v>
+      </c>
+      <c r="I59" t="n">
         <v>75.66</v>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>100</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
       <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>100</v>
+      </c>
+      <c r="M59" t="n">
+        <v>87.83</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
         <v>50.13</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
+      <c r="Q59" t="n">
+        <v>80</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="T59" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O59" t="n">
+      <c r="U59" t="n">
         <v>2026</v>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>MTSN 3 OKUS</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>MTSN 3 OKUS</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>MTSN 3 OKUS (574370)</t>
         </is>
@@ -4351,64 +5889,90 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>666502</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>100</v>
-      </c>
-      <c r="D60" t="n">
-        <v>100</v>
-      </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
+        <v>100</v>
+      </c>
+      <c r="G60" t="n">
+        <v>100</v>
+      </c>
+      <c r="H60" t="n">
+        <v>100</v>
+      </c>
+      <c r="I60" t="n">
         <v>67.69</v>
       </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>100</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
       <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>100</v>
+      </c>
+      <c r="M60" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
         <v>48.54</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
+      <c r="Q60" t="n">
+        <v>80</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="T60" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O60" t="n">
+      <c r="U60" t="n">
         <v>2026</v>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (666502)</t>
         </is>
@@ -4417,64 +5981,90 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>661192</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>100</v>
-      </c>
-      <c r="D61" t="n">
+      <c r="F61" t="n">
+        <v>100</v>
+      </c>
+      <c r="G61" t="n">
         <v>61.72</v>
       </c>
-      <c r="E61" t="n">
+      <c r="H61" t="n">
+        <v>80.86</v>
+      </c>
+      <c r="I61" t="n">
         <v>92.39</v>
       </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>100</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
       <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>100</v>
+      </c>
+      <c r="M61" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
         <v>47.74</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
+      <c r="Q61" t="n">
+        <v>80</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>59.67</v>
+      </c>
+      <c r="T61" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O61" t="n">
+      <c r="U61" t="n">
         <v>2026</v>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>MTSN 4 OKUS</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>MTSN 4 OKUS</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>MTSN 4 OKUS (661192)</t>
         </is>
@@ -4483,64 +6073,90 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>597480</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>100</v>
-      </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
+        <v>100</v>
+      </c>
+      <c r="G62" t="n">
         <v>64.54000000000001</v>
       </c>
-      <c r="E62" t="n">
+      <c r="H62" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="I62" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>100</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
       <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>100</v>
+      </c>
+      <c r="M62" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
         <v>47.3</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
+      <c r="Q62" t="n">
+        <v>80</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>59.13</v>
+      </c>
+      <c r="T62" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O62" t="n">
+      <c r="U62" t="n">
         <v>2026</v>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>MTSN 4 OKUT</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>MTSN 4 OKUT</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>MTSN 4 OKUT (597480)</t>
         </is>
@@ -4549,64 +6165,90 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>662127</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>100</v>
-      </c>
-      <c r="D63" t="n">
+      <c r="F63" t="n">
+        <v>100</v>
+      </c>
+      <c r="G63" t="n">
         <v>51.48</v>
       </c>
-      <c r="E63" t="n">
+      <c r="H63" t="n">
+        <v>75.73999999999999</v>
+      </c>
+      <c r="I63" t="n">
         <v>97.89</v>
       </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>100</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
       <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>100</v>
+      </c>
+      <c r="M63" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
         <v>47.3</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
+      <c r="Q63" t="n">
+        <v>80</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>59.13</v>
+      </c>
+      <c r="T63" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O63" t="n">
+      <c r="U63" t="n">
         <v>2026</v>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>MAN 1 OKUS</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>MAN 1 OKUS</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>MAN 1 OKUS (662127)</t>
         </is>
@@ -4615,64 +6257,90 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>669055</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>100</v>
-      </c>
-      <c r="D64" t="n">
-        <v>100</v>
-      </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
+        <v>100</v>
+      </c>
+      <c r="G64" t="n">
+        <v>100</v>
+      </c>
+      <c r="H64" t="n">
+        <v>100</v>
+      </c>
+      <c r="I64" t="n">
         <v>46.25</v>
       </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>100</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
       <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>100</v>
+      </c>
+      <c r="M64" t="n">
+        <v>73.13</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
         <v>44.25</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
+      <c r="Q64" t="n">
+        <v>80</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="T64" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O64" t="n">
+      <c r="U64" t="n">
         <v>2026</v>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>BPN OKUT</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>BPN OKUT</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>BPN OKUT (669055)</t>
         </is>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,54 +456,54 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Kualitas Perencanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kualitas Pelaksanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kualitas Hasil Pelaksanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Revisi DIPA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Deviasi Halaman III DIPA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Kualitas Perencanaan Anggaran</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Penyerapan Anggaran</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Belanja Kontraktual</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Penyelesaian Tagihan</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Pengelolaan UP dan TUP</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Kualitas Pelaksanaan Anggaran</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Capaian Output</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Kualitas Hasil Pelaksanaan Anggaran</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Nilai Total</t>
@@ -536,25 +536,53 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Peringkat</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Uraian Satker-RINGKAS</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Period_Sort</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Total Pagu</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Jenis Satker</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Uraian Satker Final</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Satker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -580,25 +608,25 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
       </c>
       <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="n">
         <v>94.89</v>
       </c>
-      <c r="J2" t="n">
-        <v>100</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>98.3</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -626,27 +654,51 @@
       <c r="U2" t="n">
         <v>2026</v>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>LOKA LABKESMAS</t>
-        </is>
+      <c r="V2" t="n">
+        <v>1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>95645370000</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA (690801)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -675,7 +727,7 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -693,7 +745,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -718,27 +770,51 @@
       <c r="U3" t="n">
         <v>2026</v>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>KEJARI  OKU</t>
-        </is>
+      <c r="V3" t="n">
+        <v>2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>95984080000</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU (007130)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -767,7 +843,7 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>100</v>
@@ -785,7 +861,7 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -810,27 +886,51 @@
       <c r="U4" t="n">
         <v>2026</v>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>LAPAS MARTAPURA</t>
-        </is>
+      <c r="V4" t="n">
+        <v>2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>139571760000</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MARTAPURA</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MARTAPURA (692340)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -859,7 +959,7 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>100</v>
@@ -877,7 +977,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -902,27 +1002,51 @@
       <c r="U5" t="n">
         <v>2026</v>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU</t>
-        </is>
+      <c r="V5" t="n">
+        <v>2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>9346940000</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418458)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -951,7 +1075,7 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>100</v>
@@ -969,7 +1093,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -994,27 +1118,51 @@
       <c r="U6" t="n">
         <v>2026</v>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>POLRES OKU</t>
-        </is>
+      <c r="V6" t="n">
+        <v>2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>POLRES OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>727218440000</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU (641681)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1043,7 +1191,7 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>100</v>
@@ -1061,7 +1209,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1086,27 +1234,51 @@
       <c r="U7" t="n">
         <v>2026</v>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>PN BATURAJA</t>
-        </is>
+      <c r="V7" t="n">
+        <v>2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>128489370000</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA (098963)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1135,7 +1307,7 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>100</v>
@@ -1153,7 +1325,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1178,27 +1350,51 @@
       <c r="U8" t="n">
         <v>2026</v>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RUTAN BATURAJA</t>
-        </is>
+      <c r="V8" t="n">
+        <v>2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>106528210000</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA (692339)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1227,7 +1423,7 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
@@ -1245,7 +1441,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1270,27 +1466,51 @@
       <c r="U9" t="n">
         <v>2026</v>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>LAPAS MUARA DUA</t>
-        </is>
+      <c r="V9" t="n">
+        <v>2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>105914680000</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA (692334)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1319,7 +1539,7 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -1337,7 +1557,7 @@
         <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1362,27 +1582,51 @@
       <c r="U10" t="n">
         <v>2026</v>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>PUSLATPUR AD</t>
-        </is>
+      <c r="V10" t="n">
+        <v>2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>405581540000</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD (685001)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1411,7 +1655,7 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -1429,7 +1673,7 @@
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1454,27 +1698,51 @@
       <c r="U11" t="n">
         <v>2026</v>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>PA MARTAPURA</t>
-        </is>
+      <c r="V11" t="n">
+        <v>2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>64847500000</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA (401944)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1503,7 +1771,7 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
@@ -1521,7 +1789,7 @@
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1546,27 +1814,51 @@
       <c r="U12" t="n">
         <v>2026</v>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>PA BATURAJA</t>
-        </is>
+      <c r="V12" t="n">
+        <v>2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>42331120000</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA (402267)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1595,7 +1887,7 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>100</v>
@@ -1613,7 +1905,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1638,27 +1930,51 @@
       <c r="U13" t="n">
         <v>2026</v>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>PA BATURAJA</t>
-        </is>
+      <c r="V13" t="n">
+        <v>2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>1230000000</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA (402268)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1687,7 +2003,7 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>100</v>
@@ -1705,7 +2021,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1730,27 +2046,51 @@
       <c r="U14" t="n">
         <v>2026</v>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>PA MARTAPURA</t>
-        </is>
+      <c r="V14" t="n">
+        <v>2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>1376500000</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A15" t="n">
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1779,7 +2119,7 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>100</v>
@@ -1797,7 +2137,7 @@
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1822,27 +2162,51 @@
       <c r="U15" t="n">
         <v>2026</v>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>PA  MUARADUA</t>
-        </is>
+      <c r="V15" t="n">
+        <v>2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>729500000</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MUARADUA</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MUARADUA (403410)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A16" t="n">
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1871,7 +2235,7 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>100</v>
@@ -1889,7 +2253,7 @@
         <v>100</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1914,27 +2278,51 @@
       <c r="U16" t="n">
         <v>2026</v>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>POLRES OKUS</t>
-        </is>
+      <c r="V16" t="n">
+        <v>2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>POLRES OKUS (665307)</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>574646890000</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN (665307)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A17" t="n">
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1963,7 +2351,7 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>100</v>
@@ -1981,7 +2369,7 @@
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2006,27 +2394,51 @@
       <c r="U17" t="n">
         <v>2026</v>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>POLRES OKUT</t>
-        </is>
+      <c r="V17" t="n">
+        <v>2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>819256290000</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU TIMUR (665292)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A18" t="n">
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2052,28 +2464,28 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>99.83</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
+        <v>100</v>
+      </c>
+      <c r="J18" t="n">
+        <v>100</v>
+      </c>
+      <c r="K18" t="n">
         <v>99.31999999999999</v>
       </c>
-      <c r="J18" t="n">
-        <v>100</v>
-      </c>
-      <c r="K18" t="n">
-        <v>100</v>
-      </c>
       <c r="L18" t="n">
         <v>100</v>
       </c>
       <c r="M18" t="n">
-        <v>99.83</v>
+        <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2098,27 +2510,51 @@
       <c r="U18" t="n">
         <v>2026</v>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>PA MUARADUA</t>
-        </is>
+      <c r="V18" t="n">
+        <v>3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>40484710000</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MUARADUA</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MUARADUA (401945)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A19" t="n">
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2141,20 +2577,20 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>96.02</v>
       </c>
       <c r="G19" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
         <v>92.03</v>
       </c>
-      <c r="H19" t="n">
-        <v>96.02</v>
-      </c>
-      <c r="I19" t="n">
-        <v>100</v>
-      </c>
-      <c r="J19" t="n">
-        <v>100</v>
-      </c>
       <c r="K19" t="n">
         <v>100</v>
       </c>
@@ -2165,7 +2601,7 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2190,27 +2626,51 @@
       <c r="U19" t="n">
         <v>2026</v>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>MTSN 1 OKUT</t>
-        </is>
+      <c r="V19" t="n">
+        <v>4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>13427580000</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (424967)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A20" t="n">
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2233,20 +2693,20 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>100</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="G20" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" t="n">
         <v>90.97</v>
       </c>
-      <c r="H20" t="n">
-        <v>95.48999999999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>100</v>
-      </c>
-      <c r="J20" t="n">
-        <v>100</v>
-      </c>
       <c r="K20" t="n">
         <v>100</v>
       </c>
@@ -2257,7 +2717,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2282,27 +2742,51 @@
       <c r="U20" t="n">
         <v>2026</v>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>KEJARI OKUS</t>
-        </is>
+      <c r="V20" t="n">
+        <v>5</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>82576290000</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2325,20 +2809,20 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>93.92</v>
       </c>
       <c r="G21" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>100</v>
+      </c>
+      <c r="J21" t="n">
         <v>87.83</v>
       </c>
-      <c r="H21" t="n">
-        <v>93.92</v>
-      </c>
-      <c r="I21" t="n">
-        <v>100</v>
-      </c>
-      <c r="J21" t="n">
-        <v>100</v>
-      </c>
       <c r="K21" t="n">
         <v>100</v>
       </c>
@@ -2349,7 +2833,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2374,27 +2858,51 @@
       <c r="U21" t="n">
         <v>2026</v>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>KEJARI OKUT</t>
-        </is>
+      <c r="V21" t="n">
+        <v>6</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>81321040000</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR (007190)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A22" t="n">
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2423,7 +2931,7 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>100</v>
@@ -2432,16 +2940,16 @@
         <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" t="n">
         <v>100</v>
       </c>
       <c r="M22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2466,27 +2974,51 @@
       <c r="U22" t="n">
         <v>2026</v>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>KPP BATURAJA</t>
-        </is>
+      <c r="V22" t="n">
+        <v>7</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>53136840000</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A23" t="n">
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2515,7 +3047,7 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>100</v>
@@ -2524,16 +3056,16 @@
         <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23" t="n">
         <v>100</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2558,27 +3090,51 @@
       <c r="U23" t="n">
         <v>2026</v>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT</t>
-        </is>
+      <c r="V23" t="n">
+        <v>7</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>475588950000</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666501)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="A24" t="n">
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2601,20 +3157,20 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="G24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" t="n">
         <v>78.08</v>
       </c>
-      <c r="H24" t="n">
-        <v>89.04000000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>100</v>
-      </c>
-      <c r="J24" t="n">
-        <v>100</v>
-      </c>
       <c r="K24" t="n">
         <v>100</v>
       </c>
@@ -2625,7 +3181,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2650,27 +3206,51 @@
       <c r="U24" t="n">
         <v>2026</v>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>BAWASLU OKUS</t>
-        </is>
+      <c r="V24" t="n">
+        <v>8</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>31225620000</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN (686503)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A25" t="n">
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2693,31 +3273,31 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
+        <v>95.94</v>
       </c>
       <c r="G25" t="n">
+        <v>100</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>100</v>
+      </c>
+      <c r="J25" t="n">
         <v>91.87</v>
       </c>
-      <c r="H25" t="n">
-        <v>95.94</v>
-      </c>
-      <c r="I25" t="n">
-        <v>100</v>
-      </c>
-      <c r="J25" t="n">
-        <v>100</v>
-      </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25" t="n">
         <v>100</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2742,27 +3322,51 @@
       <c r="U25" t="n">
         <v>2026</v>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>MTSN 1 OKU</t>
-        </is>
+      <c r="V25" t="n">
+        <v>9</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>9098870000</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU (426050)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A26" t="n">
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2785,31 +3389,31 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>100</v>
+        <v>88.34</v>
       </c>
       <c r="G26" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" t="n">
         <v>76.67</v>
       </c>
-      <c r="H26" t="n">
-        <v>88.34</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="J26" t="n">
-        <v>100</v>
-      </c>
-      <c r="K26" t="n">
-        <v>100</v>
-      </c>
       <c r="L26" t="n">
         <v>100</v>
       </c>
       <c r="M26" t="n">
-        <v>96.78</v>
+        <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2834,27 +3438,51 @@
       <c r="U26" t="n">
         <v>2026</v>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>MAN 1 OKUT</t>
-        </is>
+      <c r="V26" t="n">
+        <v>10</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>20589110000</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (426066)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A27" t="n">
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2880,28 +3508,28 @@
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>94.98</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
+        <v>100</v>
+      </c>
+      <c r="J27" t="n">
+        <v>100</v>
+      </c>
+      <c r="K27" t="n">
         <v>84.94</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>100</v>
-      </c>
       <c r="L27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>94.98</v>
+        <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -2926,27 +3554,51 @@
       <c r="U27" t="n">
         <v>2026</v>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>BPS OKUT</t>
-        </is>
+      <c r="V27" t="n">
+        <v>11</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>65205040000</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR (668529)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="A28" t="n">
+        <v>41</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2955,17 +3607,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2975,25 +3627,25 @@
         <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3018,27 +3670,51 @@
       <c r="U28" t="n">
         <v>2026</v>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>BPS OKUS</t>
-        </is>
+      <c r="V28" t="n">
+        <v>12</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>5127100000</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA (099228)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A29" t="n">
+        <v>40</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3047,17 +3723,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3067,25 +3743,25 @@
         <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3110,27 +3786,51 @@
       <c r="U29" t="n">
         <v>2026</v>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS</t>
-        </is>
+      <c r="V29" t="n">
+        <v>12</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>31572500000</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>BAPAS KELAS II OKU INDUK</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>BAPAS KELAS II OKU INDUK (692625)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="A30" t="n">
+        <v>39</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3139,17 +3839,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3159,25 +3859,25 @@
         <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3202,27 +3902,51 @@
       <c r="U30" t="n">
         <v>2026</v>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS</t>
-        </is>
+      <c r="V30" t="n">
+        <v>12</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>38902730000</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU (656553)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A31" t="n">
+        <v>38</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3231,17 +3955,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3251,25 +3975,25 @@
         <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3294,27 +4018,51 @@
       <c r="U31" t="n">
         <v>2026</v>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA</t>
-        </is>
+      <c r="V31" t="n">
+        <v>12</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>1707230000</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (111071)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="A32" t="n">
+        <v>37</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3323,17 +4071,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -3343,25 +4091,25 @@
         <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3386,27 +4134,51 @@
       <c r="U32" t="n">
         <v>2026</v>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT</t>
-        </is>
+      <c r="V32" t="n">
+        <v>12</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>10675360000</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR (111079)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="A33" t="n">
+        <v>35</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3420,12 +4192,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -3435,25 +4207,25 @@
         <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3478,27 +4250,51 @@
       <c r="U33" t="n">
         <v>2026</v>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT</t>
-        </is>
+      <c r="V33" t="n">
+        <v>12</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>10710500000</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440503)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="A34" t="n">
+        <v>36</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3507,17 +4303,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -3527,25 +4323,25 @@
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3570,27 +4366,51 @@
       <c r="U34" t="n">
         <v>2026</v>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>KPU OKUS</t>
-        </is>
+      <c r="V34" t="n">
+        <v>12</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA34" t="n">
+        <v>317944150000</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440502)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="A35" t="n">
+        <v>32</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3604,12 +4424,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -3619,25 +4439,25 @@
         <v>100</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>100</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3662,27 +4482,51 @@
       <c r="U35" t="n">
         <v>2026</v>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>MTSN 2 OKUS</t>
-        </is>
+      <c r="V35" t="n">
+        <v>12</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>3127760000</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666504)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="A36" t="n">
+        <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3696,12 +4540,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -3711,25 +4555,25 @@
         <v>100</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -3754,27 +4598,51 @@
       <c r="U36" t="n">
         <v>2026</v>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS</t>
-        </is>
+      <c r="V36" t="n">
+        <v>12</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>5891850000</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (418462)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="A37" t="n">
+        <v>33</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3783,17 +4651,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -3803,25 +4671,25 @@
         <v>100</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -3846,27 +4714,51 @@
       <c r="U37" t="n">
         <v>2026</v>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS</t>
-        </is>
+      <c r="V37" t="n">
+        <v>12</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="n">
+        <v>43471570000</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN (656574)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A38" t="n">
+        <v>31</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3875,17 +4767,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -3895,25 +4787,25 @@
         <v>100</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3938,27 +4830,51 @@
       <c r="U38" t="n">
         <v>2026</v>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>BNN OKUT</t>
-        </is>
+      <c r="V38" t="n">
+        <v>12</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>3484030000</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666505)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="A39" t="n">
+        <v>30</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3967,17 +4883,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -3987,25 +4903,25 @@
         <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -4030,27 +4946,51 @@
       <c r="U39" t="n">
         <v>2026</v>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT</t>
-        </is>
+      <c r="V39" t="n">
+        <v>12</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA39" t="n">
+        <v>11480750000</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A40" t="n">
+        <v>29</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4059,17 +4999,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -4079,25 +5019,25 @@
         <v>100</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -4122,27 +5062,51 @@
       <c r="U40" t="n">
         <v>2026</v>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>KPU OKU</t>
-        </is>
+      <c r="V40" t="n">
+        <v>12</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>970430000</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440506)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="A41" t="n">
+        <v>28</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4151,17 +5115,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -4171,25 +5135,25 @@
         <v>100</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -4214,27 +5178,51 @@
       <c r="U41" t="n">
         <v>2026</v>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>BAPAS OKU INDUK</t>
-        </is>
+      <c r="V41" t="n">
+        <v>12</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>1001460000</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440505)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="A42" t="n">
+        <v>27</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4243,17 +5231,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -4263,25 +5251,25 @@
         <v>100</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -4306,27 +5294,51 @@
       <c r="U42" t="n">
         <v>2026</v>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>PN BATURAJA</t>
-        </is>
+      <c r="V42" t="n">
+        <v>12</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>40671640000</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN (667215)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="A43" t="n">
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4352,28 +5364,28 @@
         <v>100</v>
       </c>
       <c r="G43" t="n">
-        <v>100</v>
+        <v>99.95</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J43" t="n">
+        <v>100</v>
+      </c>
+      <c r="K43" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>99.95</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -4398,27 +5410,51 @@
       <c r="U43" t="n">
         <v>2026</v>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>KPU OKUT</t>
-        </is>
+      <c r="V43" t="n">
+        <v>13</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA43" t="n">
+        <v>39931940000</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR (656560)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="A44" t="n">
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4444,28 +5480,28 @@
         <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>100</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
+        <v>100</v>
+      </c>
+      <c r="J44" t="n">
+        <v>100</v>
+      </c>
+      <c r="K44" t="n">
         <v>99.86</v>
       </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>99.93000000000001</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -4490,27 +5526,51 @@
       <c r="U44" t="n">
         <v>2026</v>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU</t>
-        </is>
+      <c r="V44" t="n">
+        <v>14</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA44" t="n">
+        <v>345163450000</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418456)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="A45" t="n">
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -4533,31 +5593,31 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="G45" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>100</v>
+      </c>
+      <c r="J45" t="n">
         <v>93.98</v>
       </c>
-      <c r="H45" t="n">
-        <v>96.98999999999999</v>
-      </c>
-      <c r="I45" t="n">
-        <v>100</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4582,27 +5642,51 @@
       <c r="U45" t="n">
         <v>2026</v>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>BPS OKU</t>
-        </is>
+      <c r="V45" t="n">
+        <v>15</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>39404370000</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="A46" t="n">
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4625,23 +5709,23 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>100</v>
+        <v>87.02</v>
       </c>
       <c r="G46" t="n">
+        <v>100</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>100</v>
+      </c>
+      <c r="J46" t="n">
         <v>74.04000000000001</v>
       </c>
-      <c r="H46" t="n">
-        <v>87.02</v>
-      </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>97.62</v>
       </c>
-      <c r="J46" t="n">
-        <v>100</v>
-      </c>
-      <c r="K46" t="n">
-        <v>100</v>
-      </c>
       <c r="L46" t="n">
         <v>100</v>
       </c>
@@ -4649,7 +5733,7 @@
         <v>100</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -4674,27 +5758,51 @@
       <c r="U46" t="n">
         <v>2026</v>
       </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>RUMKIT NOESMIR</t>
-        </is>
+      <c r="V46" t="n">
+        <v>16</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA46" t="n">
+        <v>287629890000</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ (344894)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="A47" t="n">
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4720,28 +5828,28 @@
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>100</v>
+        <v>97.13</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
+        <v>100</v>
+      </c>
+      <c r="J47" t="n">
+        <v>100</v>
+      </c>
+      <c r="K47" t="n">
         <v>94.26000000000001</v>
       </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>97.13</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -4766,27 +5874,51 @@
       <c r="U47" t="n">
         <v>2026</v>
       </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>BPN OKU</t>
-        </is>
+      <c r="V47" t="n">
+        <v>17</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA47" t="n">
+        <v>74397990000</v>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU (431142)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="A48" t="n">
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4809,31 +5941,31 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="G48" t="n">
+        <v>100</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>100</v>
+      </c>
+      <c r="J48" t="n">
         <v>91.63</v>
       </c>
-      <c r="H48" t="n">
-        <v>95.81999999999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>100</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L48" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -4858,27 +5990,51 @@
       <c r="U48" t="n">
         <v>2026</v>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>MAN 1 OKU</t>
-        </is>
+      <c r="V48" t="n">
+        <v>18</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA48" t="n">
+        <v>15177700000</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU (424245)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="A49" t="n">
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -4904,28 +6060,28 @@
         <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
+        <v>100</v>
+      </c>
+      <c r="J49" t="n">
+        <v>100</v>
+      </c>
+      <c r="K49" t="n">
         <v>93.59</v>
       </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>96.8</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -4950,27 +6106,51 @@
       <c r="U49" t="n">
         <v>2026</v>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>MAN 2 OKUS</t>
-        </is>
+      <c r="V49" t="n">
+        <v>19</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA49" t="n">
+        <v>3898470000</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (597558)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="A50" t="n">
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4993,31 +6173,31 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>85.61</v>
       </c>
       <c r="G50" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J50" t="n">
         <v>71.22</v>
       </c>
-      <c r="H50" t="n">
-        <v>85.61</v>
-      </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>92.81999999999999</v>
       </c>
-      <c r="J50" t="n">
-        <v>100</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" t="n">
         <v>100</v>
       </c>
       <c r="M50" t="n">
-        <v>97.61</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -5042,27 +6222,51 @@
       <c r="U50" t="n">
         <v>2026</v>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT</t>
-        </is>
+      <c r="V50" t="n">
+        <v>20</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA50" t="n">
+        <v>16133240000</v>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="A51" t="n">
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -5088,28 +6292,28 @@
         <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>100</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
+        <v>100</v>
+      </c>
+      <c r="J51" t="n">
+        <v>100</v>
+      </c>
+      <c r="K51" t="n">
         <v>85.97</v>
       </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
       <c r="L51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>92.98999999999999</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -5134,27 +6338,51 @@
       <c r="U51" t="n">
         <v>2026</v>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU</t>
-        </is>
+      <c r="V51" t="n">
+        <v>21</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA51" t="n">
+        <v>7789580000</v>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418457)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="A52" t="n">
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5180,28 +6408,28 @@
         <v>100</v>
       </c>
       <c r="G52" t="n">
-        <v>100</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
+        <v>100</v>
+      </c>
+      <c r="J52" t="n">
+        <v>100</v>
+      </c>
+      <c r="K52" t="n">
         <v>85.41</v>
       </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
       <c r="L52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>92.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -5226,27 +6454,51 @@
       <c r="U52" t="n">
         <v>2026</v>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU</t>
-        </is>
+      <c r="V52" t="n">
+        <v>22</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA52" t="n">
+        <v>1731600000</v>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418459)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="A53" t="n">
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5269,31 +6521,31 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>90.06</v>
       </c>
       <c r="G53" t="n">
+        <v>100</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>100</v>
+      </c>
+      <c r="J53" t="n">
         <v>80.12</v>
       </c>
-      <c r="H53" t="n">
-        <v>90.06</v>
-      </c>
-      <c r="I53" t="n">
-        <v>100</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -5318,27 +6570,51 @@
       <c r="U53" t="n">
         <v>2026</v>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>MTSN 1 OKUS</t>
-        </is>
+      <c r="V53" t="n">
+        <v>23</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA53" t="n">
+        <v>9731020000</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (553792)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="A54" t="n">
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -5361,31 +6637,31 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="G54" t="n">
+        <v>94.36</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>100</v>
+      </c>
+      <c r="J54" t="n">
         <v>61.58</v>
       </c>
-      <c r="H54" t="n">
-        <v>80.79000000000001</v>
-      </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>77.42</v>
       </c>
-      <c r="J54" t="n">
-        <v>100</v>
-      </c>
-      <c r="K54" t="n">
-        <v>100</v>
-      </c>
       <c r="L54" t="n">
         <v>100</v>
       </c>
       <c r="M54" t="n">
-        <v>94.36</v>
+        <v>100</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -5410,27 +6686,51 @@
       <c r="U54" t="n">
         <v>2026</v>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>MTSN 2 OKUT</t>
-        </is>
+      <c r="V54" t="n">
+        <v>24</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA54" t="n">
+        <v>6368000000</v>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR (418471)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A55" t="n">
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5453,31 +6753,31 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="G55" t="n">
+        <v>100</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>100</v>
+      </c>
+      <c r="J55" t="n">
         <v>78.01000000000001</v>
       </c>
-      <c r="H55" t="n">
-        <v>89.01000000000001</v>
-      </c>
-      <c r="I55" t="n">
-        <v>100</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -5502,27 +6802,51 @@
       <c r="U55" t="n">
         <v>2026</v>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>MTSN 3 OKUT</t>
-        </is>
+      <c r="V55" t="n">
+        <v>25</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA55" t="n">
+        <v>5176090000</v>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR (553099)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="A56" t="n">
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -5545,31 +6869,31 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="G56" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>100</v>
+      </c>
+      <c r="J56" t="n">
         <v>94.52</v>
       </c>
-      <c r="H56" t="n">
-        <v>97.26000000000001</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="K56" t="n">
         <v>85.13</v>
       </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
       <c r="L56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>92.56999999999999</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -5594,27 +6918,51 @@
       <c r="U56" t="n">
         <v>2026</v>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS</t>
-        </is>
+      <c r="V56" t="n">
+        <v>26</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA56" t="n">
+        <v>10808640000</v>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440504)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="A57" t="n">
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -5637,31 +6985,31 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
+        <v>95.19</v>
       </c>
       <c r="G57" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>100</v>
+      </c>
+      <c r="J57" t="n">
         <v>90.37</v>
       </c>
-      <c r="H57" t="n">
-        <v>95.19</v>
-      </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>86.52</v>
       </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
       <c r="L57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>93.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -5686,27 +7034,51 @@
       <c r="U57" t="n">
         <v>2026</v>
       </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>BPN OKUS</t>
-        </is>
+      <c r="V57" t="n">
+        <v>27</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA57" t="n">
+        <v>50054370000</v>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN (670561)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A58" t="n">
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -5729,31 +7101,31 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>89.63</v>
       </c>
       <c r="G58" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>100</v>
+      </c>
+      <c r="J58" t="n">
         <v>79.26000000000001</v>
       </c>
-      <c r="H58" t="n">
-        <v>89.63</v>
-      </c>
-      <c r="I58" t="n">
+      <c r="K58" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>96.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -5778,27 +7150,51 @@
       <c r="U58" t="n">
         <v>2026</v>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>BAWASLU OKU</t>
-        </is>
+      <c r="V58" t="n">
+        <v>28</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA58" t="n">
+        <v>29335310000</v>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU (419006)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="A59" t="n">
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -5824,28 +7220,28 @@
         <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>87.83</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
+        <v>100</v>
+      </c>
+      <c r="J59" t="n">
+        <v>100</v>
+      </c>
+      <c r="K59" t="n">
         <v>75.66</v>
       </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>87.83</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -5870,27 +7266,51 @@
       <c r="U59" t="n">
         <v>2026</v>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>MTSN 3 OKUS</t>
-        </is>
+      <c r="V59" t="n">
+        <v>29</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA59" t="n">
+        <v>7585360000</v>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN (574370)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="A60" t="n">
+        <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -5916,28 +7336,28 @@
         <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
+        <v>100</v>
+      </c>
+      <c r="J60" t="n">
+        <v>100</v>
+      </c>
+      <c r="K60" t="n">
         <v>67.69</v>
       </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
       <c r="L60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>83.84999999999999</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -5962,27 +7382,51 @@
       <c r="U60" t="n">
         <v>2026</v>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT</t>
-        </is>
+      <c r="V60" t="n">
+        <v>30</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA60" t="n">
+        <v>15707450000</v>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666502)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="A61" t="n">
+        <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -6005,31 +7449,31 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>80.86</v>
       </c>
       <c r="G61" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>100</v>
+      </c>
+      <c r="J61" t="n">
         <v>61.72</v>
       </c>
-      <c r="H61" t="n">
-        <v>80.86</v>
-      </c>
-      <c r="I61" t="n">
+      <c r="K61" t="n">
         <v>92.39</v>
       </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
       <c r="L61" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>96.2</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -6054,27 +7498,51 @@
       <c r="U61" t="n">
         <v>2026</v>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>MTSN 4 OKUS</t>
-        </is>
+      <c r="V61" t="n">
+        <v>31</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA61" t="n">
+        <v>5671610000</v>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN (661192)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="A62" t="n">
+        <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -6097,31 +7565,31 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>82.27</v>
       </c>
       <c r="G62" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>100</v>
+      </c>
+      <c r="J62" t="n">
         <v>64.54000000000001</v>
       </c>
-      <c r="H62" t="n">
-        <v>82.27</v>
-      </c>
-      <c r="I62" t="n">
+      <c r="K62" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
       <c r="L62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>94.05</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -6146,27 +7614,51 @@
       <c r="U62" t="n">
         <v>2026</v>
       </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>MTSN 4 OKUT</t>
-        </is>
+      <c r="V62" t="n">
+        <v>32</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA62" t="n">
+        <v>4481070000</v>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR (597480)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="A63" t="n">
+        <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6189,31 +7681,31 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="G63" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>100</v>
+      </c>
+      <c r="J63" t="n">
         <v>51.48</v>
       </c>
-      <c r="H63" t="n">
-        <v>75.73999999999999</v>
-      </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>97.89</v>
       </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
       <c r="L63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>98.95</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -6238,27 +7730,51 @@
       <c r="U63" t="n">
         <v>2026</v>
       </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>MAN 1 OKUS</t>
-        </is>
+      <c r="V63" t="n">
+        <v>32</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA63" t="n">
+        <v>13489830000</v>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (662127)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="A64" t="n">
+        <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6284,28 +7800,28 @@
         <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>100</v>
+        <v>73.13</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
+        <v>100</v>
+      </c>
+      <c r="J64" t="n">
+        <v>100</v>
+      </c>
+      <c r="K64" t="n">
         <v>46.25</v>
       </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>73.13</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -6330,19 +7846,45 @@
       <c r="U64" t="n">
         <v>2026</v>
       </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>BPN OKUT</t>
-        </is>
+      <c r="V64" t="n">
+        <v>33</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AA64" t="n">
+        <v>114852670000</v>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN (669055)</t>
         </is>
       </c>
     </row>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -546,37 +546,37 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Period_Sort</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Total Pagu</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Jenis Satker</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>Uraian Satker-RINGKAS</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Period_Sort</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Total Pagu</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Jenis Satker</t>
-        </is>
-      </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>Satker</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>Uraian Satker Final</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Satker</t>
         </is>
       </c>
     </row>
@@ -664,35 +664,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA2" t="n">
+      <c r="Z2" t="n">
         <v>95645370000</v>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA (690801)</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
     </row>
@@ -780,35 +780,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA3" t="n">
+      <c r="Z3" t="n">
         <v>95984080000</v>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU (007130)</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
     </row>
@@ -896,35 +896,35 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA4" t="n">
+      <c r="Z4" t="n">
         <v>139571760000</v>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA (692340)</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
     </row>
@@ -1012,35 +1012,35 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA5" t="n">
+      <c r="Z5" t="n">
         <v>9346940000</v>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418458)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
     </row>
@@ -1128,35 +1128,35 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA6" t="n">
+      <c r="Z6" t="n">
         <v>727218440000</v>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU (641681)</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
     </row>
@@ -1244,35 +1244,35 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA7" t="n">
+      <c r="Z7" t="n">
         <v>128489370000</v>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA (098963)</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
     </row>
@@ -1360,35 +1360,35 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA8" t="n">
+      <c r="Z8" t="n">
         <v>106528210000</v>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA (692339)</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
     </row>
@@ -1476,35 +1476,35 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA9" t="n">
+      <c r="Z9" t="n">
         <v>105914680000</v>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA (692334)</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
     </row>
@@ -1592,35 +1592,35 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA10" t="n">
+      <c r="Z10" t="n">
         <v>405581540000</v>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD (685001)</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
     </row>
@@ -1708,35 +1708,35 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA11" t="n">
+      <c r="Z11" t="n">
         <v>64847500000</v>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA (401944)</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
     </row>
@@ -1824,35 +1824,35 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA12" t="n">
+      <c r="Z12" t="n">
         <v>42331120000</v>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402267)</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
     </row>
@@ -1940,35 +1940,35 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA13" t="n">
+      <c r="Z13" t="n">
         <v>1230000000</v>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402268)</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
     </row>
@@ -2056,35 +2056,35 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA14" t="n">
+      <c r="Z14" t="n">
         <v>1376500000</v>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
     </row>
@@ -2172,35 +2172,35 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA15" t="n">
+      <c r="Z15" t="n">
         <v>729500000</v>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA (403410)</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
     </row>
@@ -2288,35 +2288,35 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA16" t="n">
+      <c r="Z16" t="n">
         <v>574646890000</v>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN (665307)</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
     </row>
@@ -2404,35 +2404,35 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA17" t="n">
+      <c r="Z17" t="n">
         <v>819256290000</v>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR (665292)</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
     </row>
@@ -2520,35 +2520,35 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA18" t="n">
+      <c r="Z18" t="n">
         <v>40484710000</v>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA (401945)</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
     </row>
@@ -2636,35 +2636,35 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA19" t="n">
+      <c r="Z19" t="n">
         <v>13427580000</v>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (424967)</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
     </row>
@@ -2752,35 +2752,35 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA20" t="n">
+      <c r="Z20" t="n">
         <v>82576290000</v>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
     </row>
@@ -2868,35 +2868,35 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA21" t="n">
+      <c r="Z21" t="n">
         <v>81321040000</v>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR (007190)</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
     </row>
@@ -2984,35 +2984,35 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA22" t="n">
+      <c r="Z22" t="n">
         <v>53136840000</v>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
     </row>
@@ -3100,35 +3100,35 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA23" t="n">
+      <c r="Z23" t="n">
         <v>475588950000</v>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666501)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
@@ -3216,35 +3216,35 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA24" t="n">
+      <c r="Z24" t="n">
         <v>31225620000</v>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN (686503)</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
     </row>
@@ -3332,35 +3332,35 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA25" t="n">
+      <c r="Z25" t="n">
         <v>9098870000</v>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU (426050)</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
     </row>
@@ -3448,35 +3448,35 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA26" t="n">
+      <c r="Z26" t="n">
         <v>20589110000</v>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR (426066)</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
     </row>
@@ -3564,35 +3564,35 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA27" t="n">
+      <c r="Z27" t="n">
         <v>65205040000</v>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR (668529)</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
     </row>
@@ -3680,35 +3680,35 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA28" t="n">
+      <c r="Z28" t="n">
         <v>5127100000</v>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA (099228)</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
     </row>
@@ -3796,35 +3796,35 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA29" t="n">
+      <c r="Z29" t="n">
         <v>31572500000</v>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK (692625)</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
     </row>
@@ -3912,35 +3912,35 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA30" t="n">
+      <c r="Z30" t="n">
         <v>38902730000</v>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU (656553)</t>
+          <t>KPU OKU</t>
         </is>
       </c>
     </row>
@@ -4028,35 +4028,35 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA31" t="n">
+      <c r="Z31" t="n">
         <v>1707230000</v>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (111071)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
@@ -4144,35 +4144,35 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA32" t="n">
+      <c r="Z32" t="n">
         <v>10675360000</v>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR (111079)</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
     </row>
@@ -4260,35 +4260,35 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA33" t="n">
+      <c r="Z33" t="n">
         <v>10710500000</v>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440503)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
     </row>
@@ -4376,35 +4376,35 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA34" t="n">
+      <c r="Z34" t="n">
         <v>317944150000</v>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440502)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
     </row>
@@ -4492,35 +4492,35 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA35" t="n">
+      <c r="Z35" t="n">
         <v>3127760000</v>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666504)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
@@ -4608,35 +4608,35 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA36" t="n">
+      <c r="Z36" t="n">
         <v>5891850000</v>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (418462)</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
     </row>
@@ -4724,35 +4724,35 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA37" t="n">
+      <c r="Z37" t="n">
         <v>43471570000</v>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN (656574)</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
     </row>
@@ -4840,35 +4840,35 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA38" t="n">
+      <c r="Z38" t="n">
         <v>3484030000</v>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666505)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
@@ -4956,35 +4956,35 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA39" t="n">
+      <c r="Z39" t="n">
         <v>11480750000</v>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
     </row>
@@ -5072,35 +5072,35 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA40" t="n">
+      <c r="Z40" t="n">
         <v>970430000</v>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440506)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
     </row>
@@ -5188,35 +5188,35 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA41" t="n">
+      <c r="Z41" t="n">
         <v>1001460000</v>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440505)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
     </row>
@@ -5304,35 +5304,35 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA42" t="n">
+      <c r="Z42" t="n">
         <v>40671640000</v>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN (667215)</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
     </row>
@@ -5420,35 +5420,35 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA43" t="n">
+      <c r="Z43" t="n">
         <v>39931940000</v>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR (656560)</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
     </row>
@@ -5536,35 +5536,35 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA44" t="n">
+      <c r="Z44" t="n">
         <v>345163450000</v>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418456)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
     </row>
@@ -5652,35 +5652,35 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA45" t="n">
+      <c r="Z45" t="n">
         <v>39404370000</v>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
+          <t>BPS OKU</t>
         </is>
       </c>
     </row>
@@ -5768,35 +5768,35 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA46" t="n">
+      <c r="Z46" t="n">
         <v>287629890000</v>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ (344894)</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
     </row>
@@ -5884,35 +5884,35 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA47" t="n">
+      <c r="Z47" t="n">
         <v>74397990000</v>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU (431142)</t>
+          <t>BPN OKU</t>
         </is>
       </c>
     </row>
@@ -6000,35 +6000,35 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA48" t="n">
+      <c r="Z48" t="n">
         <v>15177700000</v>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU (424245)</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
     </row>
@@ -6116,35 +6116,35 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA49" t="n">
+      <c r="Z49" t="n">
         <v>3898470000</v>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN (597558)</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
     </row>
@@ -6232,35 +6232,35 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA50" t="n">
+      <c r="Z50" t="n">
         <v>16133240000</v>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
@@ -6348,35 +6348,35 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA51" t="n">
+      <c r="Z51" t="n">
         <v>7789580000</v>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418457)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
     </row>
@@ -6464,35 +6464,35 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA52" t="n">
+      <c r="Z52" t="n">
         <v>1731600000</v>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU (418459)</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
     </row>
@@ -6580,35 +6580,35 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA53" t="n">
+      <c r="Z53" t="n">
         <v>9731020000</v>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (553792)</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
     </row>
@@ -6696,35 +6696,35 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA54" t="n">
+      <c r="Z54" t="n">
         <v>6368000000</v>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR (418471)</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
     </row>
@@ -6812,35 +6812,35 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA55" t="n">
+      <c r="Z55" t="n">
         <v>5176090000</v>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR (553099)</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
     </row>
@@ -6928,35 +6928,35 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA56" t="n">
+      <c r="Z56" t="n">
         <v>10808640000</v>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440504)</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
     </row>
@@ -7044,35 +7044,35 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA57" t="n">
+      <c r="Z57" t="n">
         <v>50054370000</v>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN (670561)</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
     </row>
@@ -7160,35 +7160,35 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA58" t="n">
+      <c r="Z58" t="n">
         <v>29335310000</v>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU (419006)</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
     </row>
@@ -7276,35 +7276,35 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA59" t="n">
+      <c r="Z59" t="n">
         <v>7585360000</v>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN (574370)</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
     </row>
@@ -7392,35 +7392,35 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA60" t="n">
+      <c r="Z60" t="n">
         <v>15707450000</v>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666502)</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
@@ -7508,35 +7508,35 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA61" t="n">
+      <c r="Z61" t="n">
         <v>5671610000</v>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN (661192)</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
     </row>
@@ -7624,35 +7624,35 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA62" t="n">
+      <c r="Z62" t="n">
         <v>4481070000</v>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR (597480)</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
     </row>
@@ -7740,35 +7740,35 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA63" t="n">
+      <c r="Z63" t="n">
         <v>13489830000</v>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN (662127)</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
     </row>
@@ -7856,35 +7856,35 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AA64" t="n">
+      <c r="Z64" t="n">
         <v>114852670000</v>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN (669055)</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
     </row>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -425,4748 +425,7464 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Kode KPPN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Kode BA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Kode Satker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Uraian Satker</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Kualitas Perencanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kualitas Pelaksanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kualitas Hasil Pelaksanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Revisi DIPA</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Deviasi Halaman III DIPA</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Penyerapan Anggaran</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Belanja Kontraktual</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Penyelesaian Tagihan</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Pengelolaan UP dan TUP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Capaian Output</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Nilai Total</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Konversi Bobot</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Dispensasi SPM (Pengurang)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Nilai Akhir (Nilai Total/Konversi Bobot)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Bulan</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Tahun</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Peringkat</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Period_Sort</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Total Pagu</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Jenis Satker</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Uraian Satker-RINGKAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Satker</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Uraian Satker Final</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>024</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>690801</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>690801</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="n">
+        <v>94.89</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" t="n">
+        <v>100</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88.98</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>90</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>98.86</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="U2" t="n">
         <v>2026</v>
       </c>
-      <c r="H2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="Z2" t="n">
         <v>95645370000</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>LOKA LABKESMAS</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>LOKA LABKESMAS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>006</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>007130</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>007130</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" t="n">
+        <v>100</v>
+      </c>
+      <c r="M3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N3" t="n">
+        <v>100</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>75</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="U3" t="n">
         <v>2026</v>
       </c>
-      <c r="H3" t="n">
+      <c r="V3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="Z3" t="n">
         <v>95984080000</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>KEJARI  OKU</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>KEJARI  OKU</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>692340</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>692340</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>75</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="Q4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="U4" t="n">
         <v>2026</v>
       </c>
-      <c r="H4" t="n">
+      <c r="V4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="Z4" t="n">
         <v>139571760000</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>LAPAS MARTAPURA</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>LAPAS MARTAPURA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>418458</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>418458</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>75</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="Q5" t="n">
+        <v>100</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75</v>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="U5" t="n">
         <v>2026</v>
       </c>
-      <c r="H5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="Z5" t="n">
         <v>9346940000</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>060</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>641681</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>641681</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>100</v>
+      </c>
+      <c r="J6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" t="n">
+        <v>100</v>
+      </c>
+      <c r="L6" t="n">
+        <v>100</v>
+      </c>
+      <c r="M6" t="n">
+        <v>100</v>
+      </c>
+      <c r="N6" t="n">
+        <v>100</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>75</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="Q6" t="n">
+        <v>100</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75</v>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="U6" t="n">
         <v>2026</v>
       </c>
-      <c r="H6" t="n">
+      <c r="V6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="Z6" t="n">
         <v>727218440000</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>POLRES OKU</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>POLRES OKU (641681)</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>POLRES OKU</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>005</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>098963</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>098963</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="n">
+        <v>100</v>
+      </c>
+      <c r="K7" t="n">
+        <v>100</v>
+      </c>
+      <c r="L7" t="n">
+        <v>100</v>
+      </c>
+      <c r="M7" t="n">
+        <v>100</v>
+      </c>
+      <c r="N7" t="n">
+        <v>100</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>75</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="Q7" t="n">
+        <v>100</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="U7" t="n">
         <v>2026</v>
       </c>
-      <c r="H7" t="n">
+      <c r="V7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="Z7" t="n">
         <v>128489370000</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>PN BATURAJA</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>PN BATURAJA (098963)</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>PN BATURAJA</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>692339</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>692339</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" t="n">
+        <v>100</v>
+      </c>
+      <c r="K8" t="n">
+        <v>100</v>
+      </c>
+      <c r="L8" t="n">
+        <v>100</v>
+      </c>
+      <c r="M8" t="n">
+        <v>100</v>
+      </c>
+      <c r="N8" t="n">
+        <v>100</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>75</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="Q8" t="n">
+        <v>100</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="U8" t="n">
         <v>2026</v>
       </c>
-      <c r="H8" t="n">
+      <c r="V8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="Z8" t="n">
         <v>106528210000</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>RUTAN BATURAJA</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>RUTAN BATURAJA</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>692334</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>692334</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" t="n">
+        <v>100</v>
+      </c>
+      <c r="K9" t="n">
+        <v>100</v>
+      </c>
+      <c r="L9" t="n">
+        <v>100</v>
+      </c>
+      <c r="M9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N9" t="n">
+        <v>100</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>75</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>75</v>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="U9" t="n">
         <v>2026</v>
       </c>
-      <c r="H9" t="n">
+      <c r="V9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="Z9" t="n">
         <v>105914680000</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>LAPAS MUARA DUA</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>LAPAS MUARA DUA</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>012</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>685001</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>685001</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" t="n">
+        <v>100</v>
+      </c>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" t="n">
+        <v>100</v>
+      </c>
+      <c r="M10" t="n">
+        <v>100</v>
+      </c>
+      <c r="N10" t="n">
+        <v>100</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>75</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="Q10" t="n">
+        <v>100</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>75</v>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="U10" t="n">
         <v>2026</v>
       </c>
-      <c r="H10" t="n">
+      <c r="V10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="Z10" t="n">
         <v>405581540000</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>PUSLATPUR AD</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>PUSLATPUR AD</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>005</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>401944</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>401944</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" t="n">
+        <v>100</v>
+      </c>
+      <c r="K11" t="n">
+        <v>100</v>
+      </c>
+      <c r="L11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" t="n">
+        <v>100</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>75</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="Q11" t="n">
+        <v>100</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>75</v>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="U11" t="n">
         <v>2026</v>
       </c>
-      <c r="H11" t="n">
+      <c r="V11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="Z11" t="n">
         <v>64847500000</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>PA MARTAPURA</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>PA MARTAPURA</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>005</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>402267</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>402267</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
+      <c r="L12" t="n">
+        <v>100</v>
+      </c>
+      <c r="M12" t="n">
+        <v>100</v>
+      </c>
+      <c r="N12" t="n">
+        <v>100</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>75</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="Q12" t="n">
+        <v>100</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>75</v>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="U12" t="n">
         <v>2026</v>
       </c>
-      <c r="H12" t="n">
+      <c r="V12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="Z12" t="n">
         <v>42331120000</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>PA BATURAJA</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>PA BATURAJA (402267)</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>PA BATURAJA</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>005</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>402268</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>402268</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" t="n">
+        <v>100</v>
+      </c>
+      <c r="M13" t="n">
+        <v>100</v>
+      </c>
+      <c r="N13" t="n">
+        <v>100</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>75</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="Q13" t="n">
+        <v>100</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>75</v>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="U13" t="n">
         <v>2026</v>
       </c>
-      <c r="H13" t="n">
+      <c r="V13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="Z13" t="n">
         <v>1230000000</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>PA BATURAJA</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>PA BATURAJA (402268)</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>PA BATURAJA</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>005</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>403409</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>403409</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
+        <v>100</v>
+      </c>
+      <c r="K14" t="n">
+        <v>100</v>
+      </c>
+      <c r="L14" t="n">
+        <v>100</v>
+      </c>
+      <c r="M14" t="n">
+        <v>100</v>
+      </c>
+      <c r="N14" t="n">
+        <v>100</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>75</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="Q14" t="n">
+        <v>100</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>75</v>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="U14" t="n">
         <v>2026</v>
       </c>
-      <c r="H14" t="n">
+      <c r="V14" t="n">
         <v>2</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="Z14" t="n">
         <v>1376500000</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>PA MARTAPURA</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>PA MARTAPURA</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A15" t="n">
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>005</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>403410</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>403410</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MUARADUA</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" t="n">
+        <v>100</v>
+      </c>
+      <c r="K15" t="n">
+        <v>100</v>
+      </c>
+      <c r="L15" t="n">
+        <v>100</v>
+      </c>
+      <c r="M15" t="n">
+        <v>100</v>
+      </c>
+      <c r="N15" t="n">
+        <v>100</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>75</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="Q15" t="n">
+        <v>100</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="U15" t="n">
         <v>2026</v>
       </c>
-      <c r="H15" t="n">
+      <c r="V15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="Z15" t="n">
         <v>729500000</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>PA  MUARADUA</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>PA  MUARADUA</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A16" t="n">
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>060</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>665307</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>665307</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>100</v>
+      </c>
+      <c r="J16" t="n">
+        <v>100</v>
+      </c>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
+      <c r="L16" t="n">
+        <v>100</v>
+      </c>
+      <c r="M16" t="n">
+        <v>100</v>
+      </c>
+      <c r="N16" t="n">
+        <v>100</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>75</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="Q16" t="n">
+        <v>100</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>75</v>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="U16" t="n">
         <v>2026</v>
       </c>
-      <c r="H16" t="n">
+      <c r="V16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="Z16" t="n">
         <v>574646890000</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>POLRES OKUS</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>POLRES OKUS (665307)</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>POLRES OKUS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A17" t="n">
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>060</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>665292</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>665292</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" t="n">
+        <v>100</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="n">
+        <v>100</v>
+      </c>
+      <c r="K17" t="n">
+        <v>100</v>
+      </c>
+      <c r="L17" t="n">
+        <v>100</v>
+      </c>
+      <c r="M17" t="n">
+        <v>100</v>
+      </c>
+      <c r="N17" t="n">
+        <v>100</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>75</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="Q17" t="n">
+        <v>100</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="U17" t="n">
         <v>2026</v>
       </c>
-      <c r="H17" t="n">
+      <c r="V17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="Z17" t="n">
         <v>819256290000</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>POLRES OKUT</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>POLRES OKUT (665292)</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>POLRES OKUT</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A18" t="n">
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>005</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>401945</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>401945</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MUARADUA</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>100</v>
+      </c>
+      <c r="J18" t="n">
+        <v>100</v>
+      </c>
+      <c r="K18" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="L18" t="n">
+        <v>100</v>
+      </c>
+      <c r="M18" t="n">
+        <v>100</v>
+      </c>
+      <c r="N18" t="n">
+        <v>100</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>74.86</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="Q18" t="n">
+        <v>100</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="U18" t="n">
         <v>2026</v>
       </c>
-      <c r="H18" t="n">
+      <c r="V18" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="Z18" t="n">
         <v>40484710000</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>PA MUARADUA</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>PA MUARADUA (401945)</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>PA MUARADUA</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A19" t="n">
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>424967</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>424967</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>96.02</v>
+      </c>
+      <c r="G19" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
+        <v>92.03</v>
+      </c>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
+      <c r="L19" t="n">
+        <v>100</v>
+      </c>
+      <c r="M19" t="n">
+        <v>100</v>
+      </c>
+      <c r="N19" t="n">
+        <v>100</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>73.8</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="Q19" t="n">
+        <v>100</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="U19" t="n">
         <v>2026</v>
       </c>
-      <c r="H19" t="n">
+      <c r="V19" t="n">
         <v>4</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="Z19" t="n">
         <v>13427580000</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>MTSN 1 OKUT</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>MTSN 1 OKUT</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A20" t="n">
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>006</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>007208</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>007208</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>95.48999999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" t="n">
+        <v>90.97</v>
+      </c>
+      <c r="K20" t="n">
+        <v>100</v>
+      </c>
+      <c r="L20" t="n">
+        <v>100</v>
+      </c>
+      <c r="M20" t="n">
+        <v>100</v>
+      </c>
+      <c r="N20" t="n">
+        <v>100</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>73.65000000000001</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="Q20" t="n">
+        <v>100</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="T20" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="U20" t="n">
         <v>2026</v>
       </c>
-      <c r="H20" t="n">
+      <c r="V20" t="n">
         <v>5</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="Z20" t="n">
         <v>82576290000</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>KEJARI OKUS</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>KEJARI OKUS</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>006</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>007190</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>007190</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>93.92</v>
+      </c>
+      <c r="G21" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>100</v>
+      </c>
+      <c r="J21" t="n">
+        <v>87.83</v>
+      </c>
+      <c r="K21" t="n">
+        <v>100</v>
+      </c>
+      <c r="L21" t="n">
+        <v>100</v>
+      </c>
+      <c r="M21" t="n">
+        <v>100</v>
+      </c>
+      <c r="N21" t="n">
+        <v>100</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>73.17</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="Q21" t="n">
+        <v>100</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>73.17</v>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="U21" t="n">
         <v>2026</v>
       </c>
-      <c r="H21" t="n">
+      <c r="V21" t="n">
         <v>6</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="Z21" t="n">
         <v>81321040000</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>KEJARI OKUT</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>KEJARI OKUT</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A22" t="n">
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>015</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>410574</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>410574</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>100</v>
+      </c>
+      <c r="G22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" t="n">
+        <v>100</v>
+      </c>
+      <c r="L22" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>100</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>90</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>72.22</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="U22" t="n">
         <v>2026</v>
       </c>
-      <c r="H22" t="n">
+      <c r="V22" t="n">
         <v>7</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="Z22" t="n">
         <v>53136840000</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>KPP BATURAJA</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>KPP BATURAJA</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A23" t="n">
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>666501</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>666501</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" t="n">
+        <v>100</v>
+      </c>
+      <c r="K23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L23" t="n">
+        <v>100</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>100</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>90</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>72.22</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="U23" t="n">
         <v>2026</v>
       </c>
-      <c r="H23" t="n">
+      <c r="V23" t="n">
         <v>7</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="Z23" t="n">
         <v>475588950000</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A24" t="n">
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>686503</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>686503</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>89.04000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="K24" t="n">
+        <v>100</v>
+      </c>
+      <c r="L24" t="n">
+        <v>100</v>
+      </c>
+      <c r="M24" t="n">
+        <v>100</v>
+      </c>
+      <c r="N24" t="n">
+        <v>100</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>71.70999999999999</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="Q24" t="n">
+        <v>100</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>71.70999999999999</v>
+      </c>
+      <c r="T24" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="U24" t="n">
         <v>2026</v>
       </c>
-      <c r="H24" t="n">
+      <c r="V24" t="n">
         <v>8</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="Z24" t="n">
         <v>31225620000</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>BAWASLU OKUS</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>BAWASLU OKUS</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A25" t="n">
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>426050</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>426050</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>95.94</v>
+      </c>
+      <c r="G25" t="n">
+        <v>100</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>100</v>
+      </c>
+      <c r="J25" t="n">
+        <v>91.87</v>
+      </c>
+      <c r="K25" t="n">
+        <v>100</v>
+      </c>
+      <c r="L25" t="n">
+        <v>100</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>100</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>90</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>70.87</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="U25" t="n">
         <v>2026</v>
       </c>
-      <c r="H25" t="n">
+      <c r="V25" t="n">
         <v>9</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="Z25" t="n">
         <v>9098870000</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>MTSN 1 OKU</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>MTSN 1 OKU</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A26" t="n">
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>426066</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>426066</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="G26" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="K26" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="L26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M26" t="n">
+        <v>100</v>
+      </c>
+      <c r="N26" t="n">
+        <v>100</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>68.92</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="Q26" t="n">
+        <v>100</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>68.92</v>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="U26" t="n">
         <v>2026</v>
       </c>
-      <c r="H26" t="n">
+      <c r="V26" t="n">
         <v>10</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="Z26" t="n">
         <v>20589110000</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>MAN 1 OKUT</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>MAN 1 OKUT</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A27" t="n">
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>054</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>668529</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>668529</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>100</v>
+      </c>
+      <c r="G27" t="n">
+        <v>94.98</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>100</v>
+      </c>
+      <c r="J27" t="n">
+        <v>100</v>
+      </c>
+      <c r="K27" t="n">
+        <v>84.94</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>100</v>
+      </c>
+      <c r="N27" t="n">
+        <v>100</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>90</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>68.88</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="U27" t="n">
         <v>2026</v>
       </c>
-      <c r="H27" t="n">
+      <c r="V27" t="n">
         <v>11</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="Z27" t="n">
         <v>65205040000</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>BPS OKUT</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>BPS OKUT (668529)</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>BPS OKUT</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A28" t="n">
+        <v>41</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>005</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>099228</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>099228</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>100</v>
+      </c>
+      <c r="J28" t="n">
+        <v>100</v>
+      </c>
+      <c r="K28" t="n">
+        <v>100</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>100</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>80</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>68.75</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="U28" t="n">
         <v>2026</v>
       </c>
-      <c r="H28" t="n">
+      <c r="V28" t="n">
         <v>12</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="Z28" t="n">
         <v>5127100000</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>PN BATURAJA</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>PN BATURAJA (099228)</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>PN BATURAJA</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A29" t="n">
+        <v>40</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>692625</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>692625</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BAPAS KELAS II OKU INDUK</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>100</v>
+      </c>
+      <c r="G29" t="n">
+        <v>100</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" t="n">
+        <v>100</v>
+      </c>
+      <c r="K29" t="n">
+        <v>100</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>100</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>80</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>68.75</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="U29" t="n">
         <v>2026</v>
       </c>
-      <c r="H29" t="n">
+      <c r="V29" t="n">
         <v>12</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="Z29" t="n">
         <v>31572500000</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>BAPAS OKU INDUK</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>BAPAS OKU INDUK</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A30" t="n">
+        <v>39</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>076</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>656553</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>656553</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" t="n">
+        <v>100</v>
+      </c>
+      <c r="K30" t="n">
+        <v>100</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>100</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>80</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>68.75</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="U30" t="n">
         <v>2026</v>
       </c>
-      <c r="H30" t="n">
+      <c r="V30" t="n">
         <v>12</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="Z30" t="n">
         <v>38902730000</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>KPU OKU</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>KPU OKU (656553)</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>KPU OKU</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A31" t="n">
+        <v>38</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>111071</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>111071</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>100</v>
+      </c>
+      <c r="G31" t="n">
+        <v>100</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>100</v>
+      </c>
+      <c r="J31" t="n">
+        <v>100</v>
+      </c>
+      <c r="K31" t="n">
+        <v>100</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>100</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>80</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>68.75</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="U31" t="n">
         <v>2026</v>
       </c>
-      <c r="H31" t="n">
+      <c r="V31" t="n">
         <v>12</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="Z31" t="n">
         <v>1707230000</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A32" t="n">
+        <v>37</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>066</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>111079</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>111079</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>100</v>
+      </c>
+      <c r="G32" t="n">
+        <v>100</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>100</v>
+      </c>
+      <c r="J32" t="n">
+        <v>100</v>
+      </c>
+      <c r="K32" t="n">
+        <v>100</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>100</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>80</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>68.75</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="U32" t="n">
         <v>2026</v>
       </c>
-      <c r="H32" t="n">
+      <c r="V32" t="n">
         <v>12</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="Z32" t="n">
         <v>10675360000</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>BNN OKUT</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>BNN OKUT (111079)</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>BNN OKUT</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A33" t="n">
+        <v>35</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>440503</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>440503</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>100</v>
+      </c>
+      <c r="G33" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>100</v>
+      </c>
+      <c r="J33" t="n">
+        <v>100</v>
+      </c>
+      <c r="K33" t="n">
+        <v>100</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>100</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>80</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>68.75</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="U33" t="n">
         <v>2026</v>
       </c>
-      <c r="H33" t="n">
+      <c r="V33" t="n">
         <v>12</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="Z33" t="n">
         <v>10710500000</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A34" t="n">
+        <v>36</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>440502</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>440502</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>100</v>
+      </c>
+      <c r="G34" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>100</v>
+      </c>
+      <c r="J34" t="n">
+        <v>100</v>
+      </c>
+      <c r="K34" t="n">
+        <v>100</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>100</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>80</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>68.75</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G34" t="n">
+      <c r="U34" t="n">
         <v>2026</v>
       </c>
-      <c r="H34" t="n">
+      <c r="V34" t="n">
         <v>12</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="Z34" t="n">
         <v>317944150000</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A35" t="n">
+        <v>32</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>666504</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>666504</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>100</v>
+      </c>
+      <c r="J35" t="n">
+        <v>100</v>
+      </c>
+      <c r="K35" t="n">
+        <v>100</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>100</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>80</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>68.75</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="U35" t="n">
         <v>2026</v>
       </c>
-      <c r="H35" t="n">
+      <c r="V35" t="n">
         <v>12</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="Z35" t="n">
         <v>3127760000</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A36" t="n">
+        <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>418462</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>418462</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" t="n">
+        <v>100</v>
+      </c>
+      <c r="K36" t="n">
+        <v>100</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>100</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>80</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>68.75</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G36" t="n">
+      <c r="U36" t="n">
         <v>2026</v>
       </c>
-      <c r="H36" t="n">
+      <c r="V36" t="n">
         <v>12</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="Z36" t="n">
         <v>5891850000</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>MTSN 2 OKUS</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>MTSN 2 OKUS</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A37" t="n">
+        <v>33</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>076</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>656574</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>656574</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>100</v>
+      </c>
+      <c r="G37" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>100</v>
+      </c>
+      <c r="J37" t="n">
+        <v>100</v>
+      </c>
+      <c r="K37" t="n">
+        <v>100</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>100</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>80</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>68.75</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="U37" t="n">
         <v>2026</v>
       </c>
-      <c r="H37" t="n">
+      <c r="V37" t="n">
         <v>12</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="Z37" t="n">
         <v>43471570000</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>KPU OKUS</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>KPU OKUS (656574)</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>KPU OKUS</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A38" t="n">
+        <v>31</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>666505</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>666505</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>100</v>
+      </c>
+      <c r="G38" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" t="n">
+        <v>100</v>
+      </c>
+      <c r="K38" t="n">
+        <v>100</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>100</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>80</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>68.75</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="U38" t="n">
         <v>2026</v>
       </c>
-      <c r="H38" t="n">
+      <c r="V38" t="n">
         <v>12</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="Z38" t="n">
         <v>3484030000</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A39" t="n">
+        <v>30</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>015</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>527975</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>527975</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>100</v>
+      </c>
+      <c r="G39" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>100</v>
+      </c>
+      <c r="J39" t="n">
+        <v>100</v>
+      </c>
+      <c r="K39" t="n">
+        <v>100</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>100</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>80</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>68.75</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="U39" t="n">
         <v>2026</v>
       </c>
-      <c r="H39" t="n">
+      <c r="V39" t="n">
         <v>12</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="Z39" t="n">
         <v>11480750000</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>KPPN BATURAJA</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>KPPN BATURAJA</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A40" t="n">
+        <v>29</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>440506</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>440506</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>100</v>
+      </c>
+      <c r="G40" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>100</v>
+      </c>
+      <c r="J40" t="n">
+        <v>100</v>
+      </c>
+      <c r="K40" t="n">
+        <v>100</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>100</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>80</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
         <v>68.75</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="U40" t="n">
         <v>2026</v>
       </c>
-      <c r="H40" t="n">
+      <c r="V40" t="n">
         <v>12</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="Z40" t="n">
         <v>970430000</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A41" t="n">
+        <v>28</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>440505</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>440505</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>100</v>
+      </c>
+      <c r="J41" t="n">
+        <v>100</v>
+      </c>
+      <c r="K41" t="n">
+        <v>100</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>100</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>80</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
         <v>68.75</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="U41" t="n">
         <v>2026</v>
       </c>
-      <c r="H41" t="n">
+      <c r="V41" t="n">
         <v>12</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L41" t="n">
+      <c r="Z41" t="n">
         <v>1001460000</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A42" t="n">
+        <v>27</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>054</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>667215</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>667215</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>100</v>
+      </c>
+      <c r="G42" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>100</v>
+      </c>
+      <c r="J42" t="n">
+        <v>100</v>
+      </c>
+      <c r="K42" t="n">
+        <v>100</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>100</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>80</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
         <v>68.75</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="U42" t="n">
         <v>2026</v>
       </c>
-      <c r="H42" t="n">
+      <c r="V42" t="n">
         <v>12</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="Z42" t="n">
         <v>40671640000</v>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>BPS OKUS</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>BPS OKUS (667215)</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>BPS OKUS</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A43" t="n">
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>076</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>656560</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>656560</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J43" t="n">
+        <v>100</v>
+      </c>
+      <c r="K43" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>100</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>80</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>68.73</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="U43" t="n">
         <v>2026</v>
       </c>
-      <c r="H43" t="n">
+      <c r="V43" t="n">
         <v>13</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L43" t="n">
+      <c r="Z43" t="n">
         <v>39931940000</v>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>KPU OKUT</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>KPU OKUT (656560)</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>KPU OKUT</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A44" t="n">
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>418456</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>418456</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>100</v>
+      </c>
+      <c r="G44" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>100</v>
+      </c>
+      <c r="J44" t="n">
+        <v>100</v>
+      </c>
+      <c r="K44" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>100</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>80</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
         <v>68.72</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="U44" t="n">
         <v>2026</v>
       </c>
-      <c r="H44" t="n">
+      <c r="V44" t="n">
         <v>14</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="Z44" t="n">
         <v>345163450000</v>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A45" t="n">
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>054</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>428258</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>428258</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>96.98999999999999</v>
+      </c>
+      <c r="G45" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>100</v>
+      </c>
+      <c r="J45" t="n">
+        <v>93.98</v>
+      </c>
+      <c r="K45" t="n">
+        <v>100</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>100</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>80</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
         <v>67.62</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="U45" t="n">
         <v>2026</v>
       </c>
-      <c r="H45" t="n">
+      <c r="V45" t="n">
         <v>15</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="Z45" t="n">
         <v>39404370000</v>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>BPS OKU</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>BPS OKU (428258)</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>BPS OKU</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A46" t="n">
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>012</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>344894</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>344894</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>87.02</v>
+      </c>
+      <c r="G46" t="n">
+        <v>100</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>100</v>
+      </c>
+      <c r="J46" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="K46" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="L46" t="n">
+        <v>100</v>
+      </c>
+      <c r="M46" t="n">
+        <v>100</v>
+      </c>
+      <c r="N46" t="n">
+        <v>100</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>90</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
         <v>67.37</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="U46" t="n">
         <v>2026</v>
       </c>
-      <c r="H46" t="n">
+      <c r="V46" t="n">
         <v>16</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L46" t="n">
+      <c r="Z46" t="n">
         <v>287629890000</v>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>RUMKIT NOESMIR</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>RUMKIT NOESMIR</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A47" t="n">
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>056</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>431142</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>431142</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>100</v>
+      </c>
+      <c r="G47" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>100</v>
+      </c>
+      <c r="J47" t="n">
+        <v>100</v>
+      </c>
+      <c r="K47" t="n">
+        <v>94.26000000000001</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>100</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>80</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="U47" t="n">
         <v>2026</v>
       </c>
-      <c r="H47" t="n">
+      <c r="V47" t="n">
         <v>17</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="Z47" t="n">
         <v>74397990000</v>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>BPN OKU</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>BPN OKU (431142)</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>BPN OKU</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A48" t="n">
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>424245</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>424245</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>100</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>100</v>
+      </c>
+      <c r="J48" t="n">
+        <v>91.63</v>
+      </c>
+      <c r="K48" t="n">
+        <v>100</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>100</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>80</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>67.18000000000001</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="U48" t="n">
         <v>2026</v>
       </c>
-      <c r="H48" t="n">
+      <c r="V48" t="n">
         <v>18</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="Z48" t="n">
         <v>15177700000</v>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>MAN 1 OKU</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>MAN 1 OKU</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A49" t="n">
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>597558</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>597558</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>100</v>
+      </c>
+      <c r="G49" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>100</v>
+      </c>
+      <c r="J49" t="n">
+        <v>100</v>
+      </c>
+      <c r="K49" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>100</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>80</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
         <v>67.15000000000001</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="U49" t="n">
         <v>2026</v>
       </c>
-      <c r="H49" t="n">
+      <c r="V49" t="n">
         <v>19</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="Z49" t="n">
         <v>3898470000</v>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>MAN 2 OKUS</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>MAN 2 OKUS</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A50" t="n">
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>666503</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>666503</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="G50" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J50" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="K50" t="n">
+        <v>92.81999999999999</v>
+      </c>
+      <c r="L50" t="n">
+        <v>100</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>100</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>90</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
         <v>65.83</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G50" t="n">
+      <c r="U50" t="n">
         <v>2026</v>
       </c>
-      <c r="H50" t="n">
+      <c r="V50" t="n">
         <v>20</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="Z50" t="n">
         <v>16133240000</v>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A51" t="n">
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>418457</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>418457</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>100</v>
+      </c>
+      <c r="G51" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>100</v>
+      </c>
+      <c r="J51" t="n">
+        <v>100</v>
+      </c>
+      <c r="K51" t="n">
+        <v>85.97</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>100</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>52.19</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>80</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
         <v>65.23999999999999</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="U51" t="n">
         <v>2026</v>
       </c>
-      <c r="H51" t="n">
+      <c r="V51" t="n">
         <v>21</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="Z51" t="n">
         <v>7789580000</v>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A52" t="n">
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>418459</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>418459</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>100</v>
+      </c>
+      <c r="G52" t="n">
+        <v>92.70999999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>100</v>
+      </c>
+      <c r="J52" t="n">
+        <v>100</v>
+      </c>
+      <c r="K52" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>100</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>80</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G52" t="n">
+      <c r="U52" t="n">
         <v>2026</v>
       </c>
-      <c r="H52" t="n">
+      <c r="V52" t="n">
         <v>22</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L52" t="n">
+      <c r="Z52" t="n">
         <v>1731600000</v>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>KEMENAG OKU</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A53" t="n">
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>553792</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>553792</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>90.06</v>
+      </c>
+      <c r="G53" t="n">
+        <v>100</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>100</v>
+      </c>
+      <c r="J53" t="n">
+        <v>80.12</v>
+      </c>
+      <c r="K53" t="n">
+        <v>100</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>100</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>80</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
         <v>65.02</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="U53" t="n">
         <v>2026</v>
       </c>
-      <c r="H53" t="n">
+      <c r="V53" t="n">
         <v>23</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L53" t="n">
+      <c r="Z53" t="n">
         <v>9731020000</v>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>MTSN 1 OKUS</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>MTSN 1 OKUS</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A54" t="n">
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>418471</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>418471</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="G54" t="n">
+        <v>94.36</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>100</v>
+      </c>
+      <c r="J54" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="K54" t="n">
+        <v>77.42</v>
+      </c>
+      <c r="L54" t="n">
+        <v>100</v>
+      </c>
+      <c r="M54" t="n">
+        <v>100</v>
+      </c>
+      <c r="N54" t="n">
+        <v>100</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
         <v>64.72</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="Q54" t="n">
+        <v>100</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="T54" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="U54" t="n">
         <v>2026</v>
       </c>
-      <c r="H54" t="n">
+      <c r="V54" t="n">
         <v>24</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L54" t="n">
+      <c r="Z54" t="n">
         <v>6368000000</v>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>MTSN 2 OKUT</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>MTSN 2 OKUT</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A55" t="n">
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>553099</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>553099</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="G55" t="n">
+        <v>100</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>100</v>
+      </c>
+      <c r="J55" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="K55" t="n">
+        <v>100</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>100</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>80</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
         <v>64.63</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="U55" t="n">
         <v>2026</v>
       </c>
-      <c r="H55" t="n">
+      <c r="V55" t="n">
         <v>25</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L55" t="n">
+      <c r="Z55" t="n">
         <v>5176090000</v>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>MTSN 3 OKUT</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="AD55" t="inlineStr">
         <is>
           <t>MTSN 3 OKUT</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A56" t="n">
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>440504</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>440504</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>97.26000000000001</v>
+      </c>
+      <c r="G56" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>100</v>
+      </c>
+      <c r="J56" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="K56" t="n">
+        <v>85.13</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>100</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>80</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
         <v>64.01000000000001</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="U56" t="n">
         <v>2026</v>
       </c>
-      <c r="H56" t="n">
+      <c r="V56" t="n">
         <v>26</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L56" t="n">
+      <c r="Z56" t="n">
         <v>10808640000</v>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="AC56" t="inlineStr">
         <is>
           <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="AD56" t="inlineStr">
         <is>
           <t>KEMENAG OKUS</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A57" t="n">
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>056</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>670561</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>670561</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>95.19</v>
+      </c>
+      <c r="G57" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>100</v>
+      </c>
+      <c r="J57" t="n">
+        <v>90.37</v>
+      </c>
+      <c r="K57" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>100</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>80</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
         <v>63.57</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="U57" t="n">
         <v>2026</v>
       </c>
-      <c r="H57" t="n">
+      <c r="V57" t="n">
         <v>27</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L57" t="n">
+      <c r="Z57" t="n">
         <v>50054370000</v>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>BPN OKUS</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>BPN OKUS (670561)</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>BPN OKUS</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A58" t="n">
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>419006</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>419006</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="G58" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>100</v>
+      </c>
+      <c r="J58" t="n">
+        <v>79.26000000000001</v>
+      </c>
+      <c r="K58" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>100</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>80</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
         <v>63.31</v>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G58" t="n">
+      <c r="U58" t="n">
         <v>2026</v>
       </c>
-      <c r="H58" t="n">
+      <c r="V58" t="n">
         <v>28</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L58" t="n">
+      <c r="Z58" t="n">
         <v>29335310000</v>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>BAWASLU OKU</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="AD58" t="inlineStr">
         <is>
           <t>BAWASLU OKU</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A59" t="n">
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>574370</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>574370</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>100</v>
+      </c>
+      <c r="G59" t="n">
+        <v>87.83</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>100</v>
+      </c>
+      <c r="J59" t="n">
+        <v>100</v>
+      </c>
+      <c r="K59" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>100</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>80</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
         <v>62.67</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="U59" t="n">
         <v>2026</v>
       </c>
-      <c r="H59" t="n">
+      <c r="V59" t="n">
         <v>29</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L59" t="n">
+      <c r="Z59" t="n">
         <v>7585360000</v>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>MTSN 3 OKUS</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="AC59" t="inlineStr">
         <is>
           <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="AD59" t="inlineStr">
         <is>
           <t>MTSN 3 OKUS</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A60" t="n">
+        <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>666502</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>666502</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>100</v>
+      </c>
+      <c r="G60" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>100</v>
+      </c>
+      <c r="J60" t="n">
+        <v>100</v>
+      </c>
+      <c r="K60" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>100</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>80</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
         <v>60.67</v>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G60" t="n">
+      <c r="U60" t="n">
         <v>2026</v>
       </c>
-      <c r="H60" t="n">
+      <c r="V60" t="n">
         <v>30</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L60" t="n">
+      <c r="Z60" t="n">
         <v>15707450000</v>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="AD60" t="inlineStr">
         <is>
           <t>KEMENAG OKUT</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A61" t="n">
+        <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>661192</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>661192</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>80.86</v>
+      </c>
+      <c r="G61" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>100</v>
+      </c>
+      <c r="J61" t="n">
+        <v>61.72</v>
+      </c>
+      <c r="K61" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>100</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>80</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
         <v>59.67</v>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="U61" t="n">
         <v>2026</v>
       </c>
-      <c r="H61" t="n">
+      <c r="V61" t="n">
         <v>31</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L61" t="n">
+      <c r="Z61" t="n">
         <v>5671610000</v>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>MTSN 4 OKUS</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="AD61" t="inlineStr">
         <is>
           <t>MTSN 4 OKUS</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A62" t="n">
+        <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>597480</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>597480</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="G62" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>100</v>
+      </c>
+      <c r="J62" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="K62" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>100</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>80</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
         <v>59.13</v>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G62" t="n">
+      <c r="U62" t="n">
         <v>2026</v>
       </c>
-      <c r="H62" t="n">
+      <c r="V62" t="n">
         <v>32</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L62" t="n">
+      <c r="Z62" t="n">
         <v>4481070000</v>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>MTSN 4 OKUT</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="AD62" t="inlineStr">
         <is>
           <t>MTSN 4 OKUT</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A63" t="n">
+        <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>025</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>662127</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>662127</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>75.73999999999999</v>
+      </c>
+      <c r="G63" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>100</v>
+      </c>
+      <c r="J63" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="K63" t="n">
+        <v>97.89</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>100</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>80</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
         <v>59.13</v>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G63" t="n">
+      <c r="U63" t="n">
         <v>2026</v>
       </c>
-      <c r="H63" t="n">
+      <c r="V63" t="n">
         <v>32</v>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L63" t="n">
+      <c r="Z63" t="n">
         <v>13489830000</v>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>SEDANG</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>MAN 1 OKUS</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="AD63" t="inlineStr">
         <is>
           <t>MAN 1 OKUS</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A64" t="n">
+        <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>000109</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>056</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>669055</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>669055</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>100</v>
+      </c>
+      <c r="G64" t="n">
+        <v>73.13</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>100</v>
+      </c>
+      <c r="J64" t="n">
+        <v>100</v>
+      </c>
+      <c r="K64" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>100</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>80</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
         <v>55.31</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="G64" t="n">
+      <c r="U64" t="n">
         <v>2026</v>
       </c>
-      <c r="H64" t="n">
+      <c r="V64" t="n">
         <v>33</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="L64" t="n">
+      <c r="Z64" t="n">
         <v>114852670000</v>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>BESAR</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>BPN OKUT</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>BPN OKUT (669055)</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>BPN OKUT</t>
         </is>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AE64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,7 +576,7 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Uraian Satker Final</t>
+          <t>Uraian Satker-RINGKAS</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
@@ -589,67 +589,71 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" t="n">
-        <v>109</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>000024</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>94.89</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>94.89</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>100</v>
+        <v>88.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>98.3</v>
+        <v>90</v>
       </c>
       <c r="R2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>98.86</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -665,70 +669,74 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>95645370000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>690801 (000024)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>109</v>
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>000060</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
@@ -746,10 +754,10 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q3" t="n">
         <v>100</v>
@@ -758,11 +766,11 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -778,70 +786,74 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>95984080000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>641681 (000060)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>109</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>000012</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
         <v>100</v>
@@ -859,10 +871,10 @@
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q4" t="n">
         <v>100</v>
@@ -871,11 +883,11 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -891,70 +903,74 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>139571760000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>685001 (000012)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>109</v>
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>000005</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
@@ -972,10 +988,10 @@
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q5" t="n">
         <v>100</v>
@@ -984,11 +1000,11 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -1004,16 +1020,16 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>9346940000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1022,52 +1038,56 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>403409 (000005)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>109</v>
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>000005</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>92.03</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
@@ -1079,29 +1099,29 @@
         <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>99.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q6" t="n">
-        <v>99.83</v>
+        <v>100</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1117,61 +1137,65 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>727218440000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>401945 (000005)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>109</v>
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>000015</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -1180,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7" t="n">
         <v>100</v>
@@ -1201,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q7" t="n">
         <v>100</v>
@@ -1210,11 +1234,11 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -1230,104 +1254,108 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>128489370000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>410574 (000015)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>25</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>109</v>
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" t="n">
         <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>76.67</v>
+        <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>88.34</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q8" t="n">
-        <v>96.78</v>
+        <v>100</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U8" t="n">
@@ -1343,61 +1371,65 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>106528210000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>426066 (000025)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>29</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>109</v>
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -1406,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
         <v>100</v>
@@ -1421,13 +1453,13 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q9" t="n">
         <v>100</v>
@@ -1436,11 +1468,11 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U9" t="n">
@@ -1456,61 +1488,65 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>105914680000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>440506 (000025)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>33</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>109</v>
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>000076</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -1519,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
         <v>100</v>
@@ -1534,13 +1570,13 @@
         <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q10" t="n">
         <v>100</v>
@@ -1549,11 +1585,11 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U10" t="n">
@@ -1569,61 +1605,65 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>405581540000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>656574 (000076)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>37</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>109</v>
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>000066</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -1632,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11" t="n">
         <v>100</v>
@@ -1647,13 +1687,13 @@
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q11" t="n">
         <v>100</v>
@@ -1662,11 +1702,11 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U11" t="n">
@@ -1682,16 +1722,16 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>64847500000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1700,43 +1740,47 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>111079 (000066)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>109</v>
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>000005</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -1745,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12" t="n">
         <v>100</v>
@@ -1760,13 +1804,13 @@
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q12" t="n">
         <v>100</v>
@@ -1775,11 +1819,11 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U12" t="n">
@@ -1795,61 +1839,65 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>42331120000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>099228 (000005)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45</v>
-      </c>
-      <c r="B13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" t="n">
-        <v>109</v>
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>000012</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -1858,28 +1906,28 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
         <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>74.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>87.02</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>97.62</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
         <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q13" t="n">
         <v>100</v>
@@ -1888,11 +1936,11 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U13" t="n">
@@ -1908,61 +1956,65 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1230000000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>344894 (000012)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>49</v>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" t="n">
-        <v>109</v>
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -1971,19 +2023,19 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14" t="n">
         <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>71.22</v>
+        <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>85.61</v>
+        <v>100</v>
       </c>
       <c r="M14" t="n">
-        <v>92.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="N14" t="n">
         <v>100</v>
@@ -1992,20 +2044,20 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>97.61</v>
+        <v>100</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U14" t="n">
@@ -2021,104 +2073,108 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1376500000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>666503 (000025)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>53</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="n">
-        <v>109</v>
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>78.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" t="n">
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>61.58</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>80.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="M15" t="n">
-        <v>77.42</v>
+        <v>100</v>
       </c>
       <c r="N15" t="n">
         <v>100</v>
       </c>
       <c r="O15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q15" t="n">
-        <v>94.36</v>
+        <v>100</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U15" t="n">
@@ -2134,61 +2190,65 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>729500000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>418471 (000025)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>57</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>109</v>
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>000115</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16" t="n">
         <v>100</v>
@@ -2197,41 +2257,41 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16" t="n">
         <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>79.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>89.63</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>93.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q16" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U16" t="n">
@@ -2247,16 +2307,16 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>574646890000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2265,86 +2325,90 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>419006 (000115)</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>61</v>
-      </c>
-      <c r="B17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" t="n">
-        <v>109</v>
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>51.48</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17" t="n">
         <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>64.54000000000001</v>
+        <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>82.27</v>
+        <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>88.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q17" t="n">
-        <v>94.05</v>
+        <v>100</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U17" t="n">
@@ -2360,16 +2424,16 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>UNKNOWN 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-00</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>819256290000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2378,20 +2442,5519 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
+          <t>POLRES OKUT</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>POLRES OKUT (665292)</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>POLRES OKUT</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>401945</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MUARADUA</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>100</v>
+      </c>
+      <c r="J18" t="n">
+        <v>100</v>
+      </c>
+      <c r="K18" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="L18" t="n">
+        <v>100</v>
+      </c>
+      <c r="M18" t="n">
+        <v>100</v>
+      </c>
+      <c r="N18" t="n">
+        <v>100</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>100</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>40484710000</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>PA MUARADUA</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>PA MUARADUA (401945)</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>PA MUARADUA</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>424967</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>96.02</v>
+      </c>
+      <c r="G19" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
+        <v>92.03</v>
+      </c>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
+      <c r="L19" t="n">
+        <v>100</v>
+      </c>
+      <c r="M19" t="n">
+        <v>100</v>
+      </c>
+      <c r="N19" t="n">
+        <v>100</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>100</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>13427580000</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUT</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUT (424967)</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUT</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>007208</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>95.48999999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" t="n">
+        <v>90.97</v>
+      </c>
+      <c r="K20" t="n">
+        <v>100</v>
+      </c>
+      <c r="L20" t="n">
+        <v>100</v>
+      </c>
+      <c r="M20" t="n">
+        <v>100</v>
+      </c>
+      <c r="N20" t="n">
+        <v>100</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>100</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>82576290000</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>KEJARI OKUS</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>KEJARI OKUS (007208)</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>KEJARI OKUS</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>007190</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>93.92</v>
+      </c>
+      <c r="G21" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>100</v>
+      </c>
+      <c r="J21" t="n">
+        <v>87.83</v>
+      </c>
+      <c r="K21" t="n">
+        <v>100</v>
+      </c>
+      <c r="L21" t="n">
+        <v>100</v>
+      </c>
+      <c r="M21" t="n">
+        <v>100</v>
+      </c>
+      <c r="N21" t="n">
+        <v>100</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>73.17</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>100</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>73.17</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>81321040000</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>KEJARI OKUT</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>KEJARI OKUT (007190)</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>KEJARI OKUT</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>410574</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>100</v>
+      </c>
+      <c r="G22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" t="n">
+        <v>100</v>
+      </c>
+      <c r="L22" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>100</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>90</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>53136840000</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>KPP BATURAJA</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>KPP BATURAJA (410574)</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>KPP BATURAJA</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>666501</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" t="n">
+        <v>100</v>
+      </c>
+      <c r="K23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L23" t="n">
+        <v>100</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>100</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>90</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>475588950000</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666501)</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>686503</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>89.04000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="K24" t="n">
+        <v>100</v>
+      </c>
+      <c r="L24" t="n">
+        <v>100</v>
+      </c>
+      <c r="M24" t="n">
+        <v>100</v>
+      </c>
+      <c r="N24" t="n">
+        <v>100</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>71.70999999999999</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>100</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>71.70999999999999</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>31225620000</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>BAWASLU OKUS</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>BAWASLU OKUS (686503)</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>BAWASLU OKUS</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>426050</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>95.94</v>
+      </c>
+      <c r="G25" t="n">
+        <v>100</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>100</v>
+      </c>
+      <c r="J25" t="n">
+        <v>91.87</v>
+      </c>
+      <c r="K25" t="n">
+        <v>100</v>
+      </c>
+      <c r="L25" t="n">
+        <v>100</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>100</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>90</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>9098870000</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKU</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKU (426050)</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKU</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>426066</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="G26" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="K26" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="L26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M26" t="n">
+        <v>100</v>
+      </c>
+      <c r="N26" t="n">
+        <v>100</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>68.92</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>100</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>68.92</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V26" t="n">
+        <v>10</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>20589110000</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUT</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUT (426066)</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUT</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>100</v>
+      </c>
+      <c r="G27" t="n">
+        <v>94.98</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>100</v>
+      </c>
+      <c r="J27" t="n">
+        <v>100</v>
+      </c>
+      <c r="K27" t="n">
+        <v>84.94</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>100</v>
+      </c>
+      <c r="N27" t="n">
+        <v>100</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>90</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V27" t="n">
+        <v>11</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>65205040000</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>BPS OKUT</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>BPS OKUT (668529)</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>BPS OKUT</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>41</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>099228</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>100</v>
+      </c>
+      <c r="J28" t="n">
+        <v>100</v>
+      </c>
+      <c r="K28" t="n">
+        <v>100</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>100</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>80</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V28" t="n">
+        <v>12</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>5127100000</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>PN BATURAJA</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>PN BATURAJA (099228)</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>PN BATURAJA</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>40</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>692625</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BAPAS KELAS II OKU INDUK</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>100</v>
+      </c>
+      <c r="G29" t="n">
+        <v>100</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" t="n">
+        <v>100</v>
+      </c>
+      <c r="K29" t="n">
+        <v>100</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>100</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>80</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V29" t="n">
+        <v>12</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>31572500000</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>BAPAS OKU INDUK</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>BAPAS OKU INDUK (692625)</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>BAPAS OKU INDUK</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>39</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" t="n">
+        <v>100</v>
+      </c>
+      <c r="K30" t="n">
+        <v>100</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>100</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>80</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V30" t="n">
+        <v>12</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>38902730000</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>KPU OKU</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>KPU OKU (656553)</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>KPU OKU</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>38</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>111071</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>100</v>
+      </c>
+      <c r="G31" t="n">
+        <v>100</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>100</v>
+      </c>
+      <c r="J31" t="n">
+        <v>100</v>
+      </c>
+      <c r="K31" t="n">
+        <v>100</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>100</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>80</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V31" t="n">
+        <v>12</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>1707230000</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (111071)</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>37</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>100</v>
+      </c>
+      <c r="G32" t="n">
+        <v>100</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>100</v>
+      </c>
+      <c r="J32" t="n">
+        <v>100</v>
+      </c>
+      <c r="K32" t="n">
+        <v>100</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>100</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>80</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V32" t="n">
+        <v>12</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>10675360000</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>BNN OKUT</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>BNN OKUT (111079)</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>BNN OKUT</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>35</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>440503</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>100</v>
+      </c>
+      <c r="G33" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>100</v>
+      </c>
+      <c r="J33" t="n">
+        <v>100</v>
+      </c>
+      <c r="K33" t="n">
+        <v>100</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>100</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>80</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V33" t="n">
+        <v>12</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>10710500000</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440503)</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>36</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>440502</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>100</v>
+      </c>
+      <c r="G34" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>100</v>
+      </c>
+      <c r="J34" t="n">
+        <v>100</v>
+      </c>
+      <c r="K34" t="n">
+        <v>100</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>100</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>80</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V34" t="n">
+        <v>12</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>317944150000</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440502)</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>666504</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>100</v>
+      </c>
+      <c r="J35" t="n">
+        <v>100</v>
+      </c>
+      <c r="K35" t="n">
+        <v>100</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>100</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>80</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V35" t="n">
+        <v>12</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>3127760000</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666504)</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>418462</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" t="n">
+        <v>100</v>
+      </c>
+      <c r="K36" t="n">
+        <v>100</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>100</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>80</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V36" t="n">
+        <v>12</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>5891850000</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUS</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUS (418462)</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUS</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>100</v>
+      </c>
+      <c r="G37" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>100</v>
+      </c>
+      <c r="J37" t="n">
+        <v>100</v>
+      </c>
+      <c r="K37" t="n">
+        <v>100</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>100</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>80</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V37" t="n">
+        <v>12</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z37" t="n">
+        <v>43471570000</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>KPU OKUS</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>KPU OKUS (656574)</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>KPU OKUS</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>666505</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>100</v>
+      </c>
+      <c r="G38" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" t="n">
+        <v>100</v>
+      </c>
+      <c r="K38" t="n">
+        <v>100</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>100</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>80</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V38" t="n">
+        <v>12</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z38" t="n">
+        <v>3484030000</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666505)</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>527975</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>100</v>
+      </c>
+      <c r="G39" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>100</v>
+      </c>
+      <c r="J39" t="n">
+        <v>100</v>
+      </c>
+      <c r="K39" t="n">
+        <v>100</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>100</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>80</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V39" t="n">
+        <v>12</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z39" t="n">
+        <v>11480750000</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA (527975)</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>29</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>440506</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>100</v>
+      </c>
+      <c r="G40" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>100</v>
+      </c>
+      <c r="J40" t="n">
+        <v>100</v>
+      </c>
+      <c r="K40" t="n">
+        <v>100</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>100</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>80</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V40" t="n">
+        <v>12</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>970430000</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440506)</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>28</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>440505</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>100</v>
+      </c>
+      <c r="J41" t="n">
+        <v>100</v>
+      </c>
+      <c r="K41" t="n">
+        <v>100</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>100</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>80</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V41" t="n">
+        <v>12</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="n">
+        <v>1001460000</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440505)</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>27</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>100</v>
+      </c>
+      <c r="G42" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>100</v>
+      </c>
+      <c r="J42" t="n">
+        <v>100</v>
+      </c>
+      <c r="K42" t="n">
+        <v>100</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>100</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>80</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V42" t="n">
+        <v>12</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z42" t="n">
+        <v>40671640000</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>BPS OKUS</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>BPS OKUS (667215)</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>BPS OKUS</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J43" t="n">
+        <v>100</v>
+      </c>
+      <c r="K43" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>100</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>80</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V43" t="n">
+        <v>13</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z43" t="n">
+        <v>39931940000</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>KPU OKUT</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>KPU OKUT (656560)</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>KPU OKUT</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>418456</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>100</v>
+      </c>
+      <c r="G44" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>100</v>
+      </c>
+      <c r="J44" t="n">
+        <v>100</v>
+      </c>
+      <c r="K44" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>100</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>80</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>68.72</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V44" t="n">
+        <v>14</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z44" t="n">
+        <v>345163450000</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418456)</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>96.98999999999999</v>
+      </c>
+      <c r="G45" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>100</v>
+      </c>
+      <c r="J45" t="n">
+        <v>93.98</v>
+      </c>
+      <c r="K45" t="n">
+        <v>100</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>100</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>80</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>67.62</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V45" t="n">
+        <v>15</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z45" t="n">
+        <v>39404370000</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>BPS OKU</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>BPS OKU (428258)</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>BPS OKU</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>344894</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>87.02</v>
+      </c>
+      <c r="G46" t="n">
+        <v>100</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>100</v>
+      </c>
+      <c r="J46" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="K46" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="L46" t="n">
+        <v>100</v>
+      </c>
+      <c r="M46" t="n">
+        <v>100</v>
+      </c>
+      <c r="N46" t="n">
+        <v>100</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>90</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V46" t="n">
+        <v>16</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z46" t="n">
+        <v>287629890000</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>RUMKIT NOESMIR</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>RUMKIT NOESMIR (344894)</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>RUMKIT NOESMIR</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>431142</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>100</v>
+      </c>
+      <c r="G47" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>100</v>
+      </c>
+      <c r="J47" t="n">
+        <v>100</v>
+      </c>
+      <c r="K47" t="n">
+        <v>94.26000000000001</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>100</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>80</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V47" t="n">
+        <v>17</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z47" t="n">
+        <v>74397990000</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>BPN OKU</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>BPN OKU (431142)</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>BPN OKU</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>100</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>100</v>
+      </c>
+      <c r="J48" t="n">
+        <v>91.63</v>
+      </c>
+      <c r="K48" t="n">
+        <v>100</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>100</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>80</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>67.18000000000001</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V48" t="n">
+        <v>18</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z48" t="n">
+        <v>15177700000</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>MAN 1 OKU</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>MAN 1 OKU (424245)</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>MAN 1 OKU</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>597558</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>100</v>
+      </c>
+      <c r="G49" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>100</v>
+      </c>
+      <c r="J49" t="n">
+        <v>100</v>
+      </c>
+      <c r="K49" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>100</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>80</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V49" t="n">
+        <v>19</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z49" t="n">
+        <v>3898470000</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>MAN 2 OKUS</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>MAN 2 OKUS (597558)</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>MAN 2 OKUS</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>666503</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="G50" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J50" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="K50" t="n">
+        <v>92.81999999999999</v>
+      </c>
+      <c r="L50" t="n">
+        <v>100</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>100</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>90</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V50" t="n">
+        <v>20</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z50" t="n">
+        <v>16133240000</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666503)</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>418457</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>100</v>
+      </c>
+      <c r="G51" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>100</v>
+      </c>
+      <c r="J51" t="n">
+        <v>100</v>
+      </c>
+      <c r="K51" t="n">
+        <v>85.97</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>100</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>52.19</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>80</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V51" t="n">
+        <v>21</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z51" t="n">
+        <v>7789580000</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418457)</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>418459</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>100</v>
+      </c>
+      <c r="G52" t="n">
+        <v>92.70999999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>100</v>
+      </c>
+      <c r="J52" t="n">
+        <v>100</v>
+      </c>
+      <c r="K52" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>100</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>80</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V52" t="n">
+        <v>22</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z52" t="n">
+        <v>1731600000</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418459)</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>553792</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>90.06</v>
+      </c>
+      <c r="G53" t="n">
+        <v>100</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>100</v>
+      </c>
+      <c r="J53" t="n">
+        <v>80.12</v>
+      </c>
+      <c r="K53" t="n">
+        <v>100</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>100</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>80</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>65.02</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V53" t="n">
+        <v>23</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z53" t="n">
+        <v>9731020000</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUS</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUS (553792)</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>MTSN 1 OKUS</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>418471</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="G54" t="n">
+        <v>94.36</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>100</v>
+      </c>
+      <c r="J54" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="K54" t="n">
+        <v>77.42</v>
+      </c>
+      <c r="L54" t="n">
+        <v>100</v>
+      </c>
+      <c r="M54" t="n">
+        <v>100</v>
+      </c>
+      <c r="N54" t="n">
+        <v>100</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>100</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V54" t="n">
+        <v>24</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z54" t="n">
+        <v>6368000000</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUT</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUT (418471)</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUT</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>553099</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="G55" t="n">
+        <v>100</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>100</v>
+      </c>
+      <c r="J55" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="K55" t="n">
+        <v>100</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>100</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>80</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>64.63</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V55" t="n">
+        <v>25</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z55" t="n">
+        <v>5176090000</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUT</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUT (553099)</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUT</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>440504</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>97.26000000000001</v>
+      </c>
+      <c r="G56" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>100</v>
+      </c>
+      <c r="J56" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="K56" t="n">
+        <v>85.13</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>100</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>80</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V56" t="n">
+        <v>26</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z56" t="n">
+        <v>10808640000</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS (440504)</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUS</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>670561</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>95.19</v>
+      </c>
+      <c r="G57" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>100</v>
+      </c>
+      <c r="J57" t="n">
+        <v>90.37</v>
+      </c>
+      <c r="K57" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>100</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>80</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V57" t="n">
+        <v>27</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z57" t="n">
+        <v>50054370000</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>BPN OKUS</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>BPN OKUS (670561)</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>BPN OKUS</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>419006</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="G58" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>100</v>
+      </c>
+      <c r="J58" t="n">
+        <v>79.26000000000001</v>
+      </c>
+      <c r="K58" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>100</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>80</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V58" t="n">
+        <v>28</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z58" t="n">
+        <v>29335310000</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>BAWASLU OKU</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>BAWASLU OKU (419006)</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>BAWASLU OKU</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>574370</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>100</v>
+      </c>
+      <c r="G59" t="n">
+        <v>87.83</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>100</v>
+      </c>
+      <c r="J59" t="n">
+        <v>100</v>
+      </c>
+      <c r="K59" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>100</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>80</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V59" t="n">
+        <v>29</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z59" t="n">
+        <v>7585360000</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUS</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUS (574370)</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUS</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>666502</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>100</v>
+      </c>
+      <c r="G60" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>100</v>
+      </c>
+      <c r="J60" t="n">
+        <v>100</v>
+      </c>
+      <c r="K60" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>100</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>80</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V60" t="n">
+        <v>30</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z60" t="n">
+        <v>15707450000</v>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666502)</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>661192</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>80.86</v>
+      </c>
+      <c r="G61" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>100</v>
+      </c>
+      <c r="J61" t="n">
+        <v>61.72</v>
+      </c>
+      <c r="K61" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>100</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>80</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>59.67</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V61" t="n">
+        <v>31</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>5671610000</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUS</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUS (661192)</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUS</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>597480</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>597480 (000025)</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>597480</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="G62" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>100</v>
+      </c>
+      <c r="J62" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="K62" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>100</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>80</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>59.13</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V62" t="n">
+        <v>32</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>4481070000</v>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUT</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUT (597480)</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>MTSN 4 OKUT</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>662127</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>75.73999999999999</v>
+      </c>
+      <c r="G63" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>100</v>
+      </c>
+      <c r="J63" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="K63" t="n">
+        <v>97.89</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>100</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>80</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>59.13</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V63" t="n">
+        <v>32</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>13489830000</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUS</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUS (662127)</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUS</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>669055</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>100</v>
+      </c>
+      <c r="G64" t="n">
+        <v>73.13</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>100</v>
+      </c>
+      <c r="J64" t="n">
+        <v>100</v>
+      </c>
+      <c r="K64" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>100</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>80</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V64" t="n">
+        <v>33</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>114852670000</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>BPN OKUT</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>BPN OKUT (669055)</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>BPN OKUT</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE64"/>
+  <dimension ref="A1:AE67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,24 +596,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
@@ -625,13 +625,13 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>94.89</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -640,16 +640,16 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>88.98</v>
+        <v>100</v>
       </c>
       <c r="Q2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>98.86</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>95645370000</v>
+        <v>95984080000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -687,24 +687,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -713,17 +713,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -733,7 +733,7 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -745,28 +745,28 @@
         <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>2026</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -795,33 +795,33 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>95984080000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -835,12 +835,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -850,7 +850,7 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
         <v>100</v>
@@ -862,28 +862,28 @@
         <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>2026</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>139571760000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -947,17 +947,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -967,7 +967,7 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
         <v>100</v>
@@ -988,10 +988,10 @@
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
         <v>100</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>2026</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1029,33 +1029,33 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>9346940000</v>
+        <v>139571760000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1084,7 +1084,7 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6" t="n">
         <v>100</v>
@@ -1105,10 +1105,10 @@
         <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="n">
         <v>100</v>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>2026</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>727218440000</v>
+        <v>106528210000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1155,24 +1155,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1201,7 +1201,7 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7" t="n">
         <v>100</v>
@@ -1222,10 +1222,10 @@
         <v>100</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q7" t="n">
         <v>100</v>
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>2026</v>
       </c>
       <c r="V7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>128489370000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1272,24 +1272,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,17 +1298,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1318,7 +1318,7 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
         <v>100</v>
@@ -1339,10 +1339,10 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="n">
         <v>100</v>
@@ -1351,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>2026</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>106528210000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1389,24 +1389,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1415,17 +1415,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1435,7 +1435,7 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
@@ -1447,28 +1447,28 @@
         <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>100</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>2026</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1497,33 +1497,33 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>105914680000</v>
+        <v>40671640000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1532,17 +1532,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1552,7 +1552,7 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -1564,28 +1564,28 @@
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>100</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>2026</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1614,33 +1614,33 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>405581540000</v>
+        <v>3484030000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1649,17 +1649,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1669,7 +1669,7 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -1681,28 +1681,28 @@
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>100</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>2026</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1731,33 +1731,33 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>64847500000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1786,7 +1786,7 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
@@ -1801,25 +1801,25 @@
         <v>100</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>100</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="Q12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>2026</v>
       </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1848,33 +1848,33 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>42331120000</v>
+        <v>475588950000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1883,17 +1883,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1903,7 +1903,7 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I13" t="n">
         <v>100</v>
@@ -1924,10 +1924,10 @@
         <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
         <v>100</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>2026</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1965,33 +1965,33 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>1230000000</v>
+        <v>574646890000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2000,17 +2000,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2020,7 +2020,7 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
         <v>100</v>
@@ -2041,10 +2041,10 @@
         <v>100</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q14" t="n">
         <v>100</v>
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>2026</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2082,33 +2082,33 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>1376500000</v>
+        <v>819256290000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2117,17 +2117,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -2137,7 +2137,7 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
         <v>100</v>
@@ -2149,28 +2149,28 @@
         <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>100</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>2026</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2199,33 +2199,33 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>729500000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -2254,7 +2254,7 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
         <v>100</v>
@@ -2266,28 +2266,28 @@
         <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>100</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>2026</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2316,33 +2316,33 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>574646890000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>POLRES OKUS (665307)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2356,12 +2356,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2371,7 +2371,7 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
         <v>100</v>
@@ -2392,10 +2392,10 @@
         <v>100</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q17" t="n">
         <v>100</v>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>2026</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>819256290000</v>
+        <v>727218440000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2442,17 +2442,17 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
@@ -2468,27 +2468,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>99.83</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
         <v>100</v>
@@ -2497,31 +2497,31 @@
         <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>99.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>100</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18" t="n">
-        <v>74.86</v>
+        <v>80</v>
       </c>
       <c r="Q18" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>74.86</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>2026</v>
       </c>
       <c r="V18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2550,33 +2550,33 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>40484710000</v>
+        <v>970430000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2585,33 +2585,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>96.02</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
         <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>92.03</v>
+        <v>100</v>
       </c>
       <c r="K19" t="n">
         <v>100</v>
@@ -2626,10 +2626,10 @@
         <v>100</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>73.8</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="n">
         <v>100</v>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>73.8</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>2026</v>
       </c>
       <c r="V19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2667,33 +2667,33 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>13427580000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2702,60 +2702,60 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>95.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="G20" t="n">
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
         <v>100</v>
       </c>
       <c r="J20" t="n">
-        <v>90.97</v>
+        <v>100</v>
       </c>
       <c r="K20" t="n">
         <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>100</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>73.65000000000001</v>
+        <v>80</v>
       </c>
       <c r="Q20" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>73.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>2026</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2784,33 +2784,33 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>82576290000</v>
+        <v>1001460000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2819,60 +2819,60 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>93.92</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>87.83</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
         <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>100</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>73.17</v>
+        <v>80</v>
       </c>
       <c r="Q21" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>73.17</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>2026</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2901,33 +2901,33 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>81321040000</v>
+        <v>10710500000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2956,7 +2956,7 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
         <v>100</v>
@@ -2977,10 +2977,10 @@
         <v>100</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="Q22" t="n">
         <v>90</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>72.22</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>2026</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3018,33 +3018,33 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>53136840000</v>
+        <v>317944150000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3058,12 +3058,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -3073,7 +3073,7 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
         <v>100</v>
@@ -3085,7 +3085,7 @@
         <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3094,19 +3094,19 @@
         <v>100</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="Q23" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>72.22</v>
+        <v>100</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>2026</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3135,33 +3135,33 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>475588950000</v>
+        <v>5891850000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3170,33 +3170,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>89.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
         <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
         <v>100</v>
       </c>
       <c r="J24" t="n">
-        <v>78.08</v>
+        <v>100</v>
       </c>
       <c r="K24" t="n">
         <v>100</v>
@@ -3211,10 +3211,10 @@
         <v>100</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>71.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q24" t="n">
         <v>100</v>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>71.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>2026</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3252,33 +3252,33 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>31225620000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3287,33 +3287,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>95.94</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
         <v>100</v>
       </c>
       <c r="J25" t="n">
-        <v>91.87</v>
+        <v>100</v>
       </c>
       <c r="K25" t="n">
         <v>100</v>
@@ -3328,10 +3328,10 @@
         <v>100</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>63.78</v>
+        <v>90</v>
       </c>
       <c r="Q25" t="n">
         <v>90</v>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>70.87</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>2026</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3369,33 +3369,33 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>9098870000</v>
+        <v>53136840000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3404,36 +3404,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>88.34</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>96.78</v>
+        <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
         <v>100</v>
       </c>
       <c r="J26" t="n">
-        <v>76.67</v>
+        <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="L26" t="n">
         <v>100</v>
@@ -3445,10 +3445,10 @@
         <v>100</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>68.92</v>
+        <v>100</v>
       </c>
       <c r="Q26" t="n">
         <v>100</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>68.92</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>2026</v>
       </c>
       <c r="V26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3486,33 +3486,33 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>20589110000</v>
+        <v>729500000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3521,27 +3521,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>94.98</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
         <v>100</v>
@@ -3550,10 +3550,10 @@
         <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>84.94</v>
+        <v>100</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
@@ -3562,19 +3562,19 @@
         <v>100</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>61.99</v>
+        <v>100</v>
       </c>
       <c r="Q27" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>68.88</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>2026</v>
       </c>
       <c r="V27" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3603,33 +3603,33 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>65205040000</v>
+        <v>1376500000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -3658,7 +3658,7 @@
         <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
@@ -3670,28 +3670,28 @@
         <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="Q28" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>2026</v>
       </c>
       <c r="V28" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>5127100000</v>
+        <v>1230000000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3729,24 +3729,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3755,17 +3755,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3775,7 +3775,7 @@
         <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
         <v>100</v>
@@ -3787,28 +3787,28 @@
         <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29" t="n">
         <v>100</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>2026</v>
       </c>
       <c r="V29" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>31572500000</v>
+        <v>42331120000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3846,24 +3846,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3872,17 +3872,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3892,7 +3892,7 @@
         <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
         <v>100</v>
@@ -3904,28 +3904,28 @@
         <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30" t="n">
         <v>100</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="Q30" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>2026</v>
       </c>
       <c r="V30" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3954,33 +3954,33 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>38902730000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3989,17 +3989,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4009,7 +4009,7 @@
         <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
         <v>100</v>
@@ -4030,10 +4030,10 @@
         <v>100</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="Q31" t="n">
         <v>80</v>
@@ -4042,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>2026</v>
       </c>
       <c r="V31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>1707230000</v>
+        <v>10675360000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4080,24 +4080,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4106,17 +4106,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4126,7 +4126,7 @@
         <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" t="n">
         <v>100</v>
@@ -4147,10 +4147,10 @@
         <v>100</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="Q32" t="n">
         <v>80</v>
@@ -4159,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>2026</v>
       </c>
       <c r="V32" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>10675360000</v>
+        <v>1707230000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4197,24 +4197,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4223,17 +4223,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4243,7 +4243,7 @@
         <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33" t="n">
         <v>100</v>
@@ -4264,10 +4264,10 @@
         <v>100</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="Q33" t="n">
         <v>80</v>
@@ -4276,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>2026</v>
       </c>
       <c r="V33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>10710500000</v>
+        <v>5127100000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -4314,24 +4314,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4340,27 +4340,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>99.95</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34" t="n">
         <v>100</v>
@@ -4369,7 +4369,7 @@
         <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4381,10 +4381,10 @@
         <v>100</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>55</v>
+        <v>79.98</v>
       </c>
       <c r="Q34" t="n">
         <v>80</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>68.75</v>
+        <v>99.98</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4422,33 +4422,33 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>317944150000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4462,22 +4462,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>100</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
         <v>100</v>
@@ -4486,7 +4486,7 @@
         <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>99.86</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4498,10 +4498,10 @@
         <v>100</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>55</v>
+        <v>79.97</v>
       </c>
       <c r="Q35" t="n">
         <v>80</v>
@@ -4510,7 +4510,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>68.75</v>
+        <v>99.97</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4539,33 +4539,33 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>3127760000</v>
+        <v>345163450000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4574,27 +4574,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>100</v>
+        <v>99.83</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I36" t="n">
         <v>100</v>
@@ -4603,31 +4603,31 @@
         <v>100</v>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N36" t="n">
         <v>100</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>55</v>
+        <v>99.86</v>
       </c>
       <c r="Q36" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>68.75</v>
+        <v>99.86</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4656,33 +4656,33 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>5891850000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4691,33 +4691,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="G37" t="n">
         <v>100</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="K37" t="n">
         <v>100</v>
@@ -4732,10 +4732,10 @@
         <v>100</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>55</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="Q37" t="n">
         <v>80</v>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>68.75</v>
+        <v>98.87</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>43471570000</v>
+        <v>39404370000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4782,24 +4782,24 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4808,27 +4808,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
         <v>100</v>
@@ -4837,10 +4837,10 @@
         <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>100</v>
+        <v>94.89</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4849,19 +4849,19 @@
         <v>100</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>55</v>
+        <v>88.98</v>
       </c>
       <c r="Q38" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>68.75</v>
+        <v>98.86</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4890,33 +4890,33 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>3484030000</v>
+        <v>95645370000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4925,60 +4925,60 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>96.02</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>99.8</v>
       </c>
       <c r="I39" t="n">
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>100</v>
+        <v>92.03</v>
       </c>
       <c r="K39" t="n">
         <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>99.8</v>
       </c>
       <c r="P39" t="n">
-        <v>55</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="Q39" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>68.75</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -5007,33 +5007,33 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>11480750000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5042,60 +5042,60 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="G40" t="n">
         <v>100</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I40" t="n">
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>100</v>
+        <v>90.97</v>
       </c>
       <c r="K40" t="n">
         <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>55</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="Q40" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>68.75</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5124,33 +5124,33 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>970430000</v>
+        <v>82576290000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5164,34 +5164,34 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
+        <v>95.94</v>
       </c>
       <c r="G41" t="n">
         <v>100</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I41" t="n">
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>100</v>
+        <v>91.87</v>
       </c>
       <c r="K41" t="n">
         <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5200,19 +5200,19 @@
         <v>100</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>55</v>
+        <v>88.78</v>
       </c>
       <c r="Q41" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>68.75</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>1001460000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -5250,24 +5250,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5276,27 +5276,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>100</v>
+        <v>97.13</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
         <v>100</v>
@@ -5305,7 +5305,7 @@
         <v>100</v>
       </c>
       <c r="K42" t="n">
-        <v>100</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5317,10 +5317,10 @@
         <v>100</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>55</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="Q42" t="n">
         <v>80</v>
@@ -5329,7 +5329,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>68.75</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5358,26 +5358,26 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>40671640000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
@@ -5393,36 +5393,36 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>100</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>99.95</v>
+        <v>100</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I43" t="n">
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>100</v>
+        <v>91.63</v>
       </c>
       <c r="K43" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5434,10 +5434,10 @@
         <v>100</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>54.98</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="Q43" t="n">
         <v>80</v>
@@ -5446,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>68.73</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>39931940000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5484,17 +5484,17 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
@@ -5515,22 +5515,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>99.93000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
         <v>100</v>
@@ -5539,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>99.86</v>
+        <v>93.59</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5551,10 +5551,10 @@
         <v>100</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>54.97</v>
+        <v>78.72</v>
       </c>
       <c r="Q44" t="n">
         <v>80</v>
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>68.72</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5592,26 +5592,26 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>345163450000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
@@ -5627,60 +5627,60 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>96.98999999999999</v>
+        <v>93.92</v>
       </c>
       <c r="G45" t="n">
         <v>100</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" t="n">
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>93.98</v>
+        <v>87.83</v>
       </c>
       <c r="K45" t="n">
         <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N45" t="n">
         <v>100</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>54.1</v>
+        <v>98.17</v>
       </c>
       <c r="Q45" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>67.62</v>
+        <v>98.17</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>2026</v>
       </c>
       <c r="V45" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5709,26 +5709,26 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>39404370000</v>
+        <v>81321040000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
@@ -5744,39 +5744,39 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>87.02</v>
+        <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>100</v>
+        <v>94.98</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I46" t="n">
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>74.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="K46" t="n">
-        <v>97.62</v>
+        <v>84.94</v>
       </c>
       <c r="L46" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>100</v>
@@ -5785,10 +5785,10 @@
         <v>100</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>60.63</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="Q46" t="n">
         <v>90</v>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>67.37</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>287629890000</v>
+        <v>65205040000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5835,17 +5835,17 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -5861,27 +5861,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>97.13</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
         <v>100</v>
@@ -5890,7 +5890,7 @@
         <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>94.26000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5902,10 +5902,10 @@
         <v>100</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>53.85</v>
+        <v>77.08</v>
       </c>
       <c r="Q47" t="n">
         <v>80</v>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>67.31999999999999</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5943,26 +5943,26 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>74397990000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
@@ -5983,28 +5983,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>95.81999999999999</v>
+        <v>90.06</v>
       </c>
       <c r="G48" t="n">
         <v>100</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I48" t="n">
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>91.63</v>
+        <v>80.12</v>
       </c>
       <c r="K48" t="n">
         <v>100</v>
@@ -6019,10 +6019,10 @@
         <v>100</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>53.74</v>
+        <v>77.02</v>
       </c>
       <c r="Q48" t="n">
         <v>80</v>
@@ -6031,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>67.18000000000001</v>
+        <v>96.27</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6060,26 +6060,26 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>15177700000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -6100,31 +6100,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>100</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>100</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>93.59</v>
+        <v>100</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6136,10 +6136,10 @@
         <v>100</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>53.72</v>
+        <v>76.7</v>
       </c>
       <c r="Q49" t="n">
         <v>80</v>
@@ -6148,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>67.15000000000001</v>
+        <v>95.88</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>3898470000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -6186,17 +6186,17 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
@@ -6217,31 +6217,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>85.61</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>97.61</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I50" t="n">
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>71.22</v>
+        <v>94.52</v>
       </c>
       <c r="K50" t="n">
-        <v>92.81999999999999</v>
+        <v>85.13</v>
       </c>
       <c r="L50" t="n">
         <v>100</v>
@@ -6253,10 +6253,10 @@
         <v>100</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>59.25</v>
+        <v>86.2</v>
       </c>
       <c r="Q50" t="n">
         <v>90</v>
@@ -6265,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>65.83</v>
+        <v>95.78</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6294,26 +6294,26 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>16133240000</v>
+        <v>10808640000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
@@ -6329,60 +6329,60 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>92.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>95.33</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>100</v>
+        <v>78.08</v>
       </c>
       <c r="K51" t="n">
-        <v>85.97</v>
+        <v>100</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N51" t="n">
         <v>100</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>95.33</v>
       </c>
       <c r="P51" t="n">
-        <v>52.19</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="Q51" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>65.23999999999999</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6411,26 +6411,26 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>7789580000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
@@ -6446,60 +6446,60 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>87.02</v>
       </c>
       <c r="G52" t="n">
-        <v>92.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>100</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>85.41</v>
+        <v>97.62</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" t="n">
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>52.08</v>
+        <v>85.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>65.09999999999999</v>
+        <v>95.14</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6528,26 +6528,26 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>1731600000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
@@ -6563,36 +6563,36 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>90.06</v>
+        <v>95.19</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>80.12</v>
+        <v>90.37</v>
       </c>
       <c r="K53" t="n">
-        <v>100</v>
+        <v>86.52</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -6604,10 +6604,10 @@
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>52.02</v>
+        <v>75.86</v>
       </c>
       <c r="Q53" t="n">
         <v>80</v>
@@ -6616,7 +6616,7 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>65.02</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6645,26 +6645,26 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>9731020000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
@@ -6680,60 +6680,60 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>80.79000000000001</v>
+        <v>89.63</v>
       </c>
       <c r="G54" t="n">
-        <v>94.36</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>61.58</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>77.42</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>100</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>64.72</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="Q54" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>64.72</v>
+        <v>94.56</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6762,26 +6762,26 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>6368000000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
@@ -6802,34 +6802,34 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>89.01000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="G55" t="n">
-        <v>100</v>
+        <v>97.61</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>78.01000000000001</v>
+        <v>71.22</v>
       </c>
       <c r="K55" t="n">
-        <v>100</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6838,19 +6838,19 @@
         <v>100</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>51.7</v>
+        <v>84.25</v>
       </c>
       <c r="Q55" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>64.63</v>
+        <v>93.61</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6879,26 +6879,26 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>5176090000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -6919,31 +6919,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>97.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>92.56999999999999</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I56" t="n">
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>94.52</v>
+        <v>100</v>
       </c>
       <c r="K56" t="n">
-        <v>85.13</v>
+        <v>85.97</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6955,10 +6955,10 @@
         <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="P56" t="n">
-        <v>51.2</v>
+        <v>73.69</v>
       </c>
       <c r="Q56" t="n">
         <v>80</v>
@@ -6967,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>64.01000000000001</v>
+        <v>92.12</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>10808640000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -7005,17 +7005,17 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
@@ -7031,36 +7031,36 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>95.19</v>
+        <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>93.26000000000001</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
         <v>100</v>
       </c>
       <c r="J57" t="n">
-        <v>90.37</v>
+        <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>86.52</v>
+        <v>67.69</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -7072,10 +7072,10 @@
         <v>100</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>50.86</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="Q57" t="n">
         <v>80</v>
@@ -7084,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>63.57</v>
+        <v>91.92</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>50054370000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -7122,17 +7122,17 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -7148,36 +7148,36 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>89.63</v>
+        <v>80.86</v>
       </c>
       <c r="G58" t="n">
-        <v>96.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>79.26000000000001</v>
+        <v>61.72</v>
       </c>
       <c r="K58" t="n">
-        <v>93.79000000000001</v>
+        <v>92.39</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>100</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>50.65</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="Q58" t="n">
         <v>80</v>
@@ -7201,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>63.31</v>
+        <v>90.92</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7230,26 +7230,26 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>29335310000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
@@ -7270,31 +7270,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>87.83</v>
+        <v>98.95</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>100</v>
+        <v>51.48</v>
       </c>
       <c r="K59" t="n">
-        <v>75.66</v>
+        <v>97.89</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -7306,10 +7306,10 @@
         <v>100</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>50.13</v>
+        <v>72.3</v>
       </c>
       <c r="Q59" t="n">
         <v>80</v>
@@ -7318,7 +7318,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>62.67</v>
+        <v>90.38</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7347,26 +7347,26 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>7585360000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7387,55 +7387,55 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>83.84999999999999</v>
+        <v>94.36</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>100</v>
+        <v>61.58</v>
       </c>
       <c r="K60" t="n">
-        <v>67.69</v>
+        <v>77.42</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N60" t="n">
         <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P60" t="n">
-        <v>48.54</v>
+        <v>89.72</v>
       </c>
       <c r="Q60" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>60.67</v>
+        <v>89.72</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7464,26 +7464,26 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>15707450000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7499,36 +7499,36 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>80.86</v>
+        <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>96.2</v>
+        <v>73.13</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>61.72</v>
+        <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>92.39</v>
+        <v>46.25</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -7540,10 +7540,10 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P61" t="n">
-        <v>47.74</v>
+        <v>69.25</v>
       </c>
       <c r="Q61" t="n">
         <v>80</v>
@@ -7552,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>59.67</v>
+        <v>86.56</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7581,26 +7581,26 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>5671610000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7621,31 +7621,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>82.27</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>94.05</v>
+        <v>87.83</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>64.54000000000001</v>
+        <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>88.09999999999999</v>
+        <v>75.66</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -7657,10 +7657,10 @@
         <v>100</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P62" t="n">
-        <v>47.3</v>
+        <v>66.38</v>
       </c>
       <c r="Q62" t="n">
         <v>80</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>59.13</v>
+        <v>82.98</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>4481070000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -7707,17 +7707,17 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7738,31 +7738,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>75.73999999999999</v>
+        <v>82.27</v>
       </c>
       <c r="G63" t="n">
-        <v>98.95</v>
+        <v>94.05</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="I63" t="n">
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>51.48</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>97.89</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -7774,10 +7774,10 @@
         <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="P63" t="n">
-        <v>47.3</v>
+        <v>64.06</v>
       </c>
       <c r="Q63" t="n">
         <v>80</v>
@@ -7786,7 +7786,7 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>59.13</v>
+        <v>80.08</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7815,26 +7815,26 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>13489830000</v>
+        <v>4481070000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7850,60 +7850,60 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>88.34</v>
       </c>
       <c r="G64" t="n">
-        <v>73.13</v>
+        <v>96.78</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>100</v>
+        <v>76.67</v>
       </c>
       <c r="K64" t="n">
-        <v>46.25</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N64" t="n">
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P64" t="n">
-        <v>44.25</v>
+        <v>76.42</v>
       </c>
       <c r="Q64" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>55.31</v>
+        <v>76.42</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7932,29 +7932,380 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>114852670000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>695176</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>50</v>
+      </c>
+      <c r="G65" t="n">
+        <v>100</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>100</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>100</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>70</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V65" t="n">
+        <v>32</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>6728240000</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU (695176)</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>695182</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>50</v>
+      </c>
+      <c r="G66" t="n">
+        <v>100</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>100</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>100</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>70</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V66" t="n">
+        <v>32</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>6314270000</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR (695182)</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>695184</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>50</v>
+      </c>
+      <c r="G67" t="n">
+        <v>100</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>100</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>100</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>70</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V67" t="n">
+        <v>32</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>6722660000</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN (695184)</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -596,24 +596,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>97.55</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
@@ -625,7 +625,7 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
@@ -640,7 +640,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>100</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="Q2" t="n">
         <v>100</v>
@@ -649,11 +649,11 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -669,42 +669,42 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>95984080000</v>
+        <v>42331120000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -713,27 +713,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>99.19</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -742,42 +742,42 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>73.38</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>99.19</v>
       </c>
       <c r="P3" t="n">
-        <v>80</v>
+        <v>94.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>94.47</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>2026</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -786,16 +786,16 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>11480750000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -804,24 +804,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -830,24 +830,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>87.48</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
@@ -859,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>80</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="Q4" t="n">
         <v>80</v>
@@ -883,18 +883,18 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>2026</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -903,42 +903,42 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>31572500000</v>
+        <v>95984080000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -947,24 +947,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>91.05</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
@@ -976,7 +976,7 @@
         <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
@@ -991,7 +991,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>92.84</v>
       </c>
       <c r="Q5" t="n">
         <v>100</v>
@@ -1000,18 +1000,18 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>92.84</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>2026</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1020,16 +1020,16 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>139571760000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1038,24 +1038,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1064,24 +1064,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
@@ -1093,7 +1093,7 @@
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>60.39</v>
       </c>
       <c r="L6" t="n">
         <v>100</v>
@@ -1108,7 +1108,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>92.08</v>
       </c>
       <c r="Q6" t="n">
         <v>100</v>
@@ -1117,18 +1117,18 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>92.08</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>2026</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1137,16 +1137,16 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>106528210000</v>
+        <v>574646890000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1155,24 +1155,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1186,19 +1186,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
@@ -1210,13 +1210,13 @@
         <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
@@ -1225,27 +1225,27 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>73.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>91.95</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U7" t="n">
         <v>2026</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1254,42 +1254,42 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>105914680000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,24 +1298,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>86.28</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
@@ -1327,13 +1327,13 @@
         <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>58.85</v>
       </c>
       <c r="L8" t="n">
         <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
@@ -1342,27 +1342,27 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>100</v>
+        <v>81.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>90.86</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U8" t="n">
         <v>2026</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1371,16 +1371,16 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>405581540000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1389,24 +1389,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1415,24 +1415,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>85.92</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -1444,10 +1444,10 @@
         <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>57.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1459,27 +1459,27 @@
         <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>80</v>
+        <v>81.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>90.61</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U9" t="n">
         <v>2026</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>40671640000</v>
+        <v>727218440000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1532,24 +1532,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>80.91</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -1561,7 +1561,7 @@
         <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>61.82</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1576,7 +1576,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>72.36</v>
       </c>
       <c r="Q10" t="n">
         <v>80</v>
@@ -1585,18 +1585,18 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U10" t="n">
         <v>2026</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1605,16 +1605,16 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>3484030000</v>
+        <v>5127100000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1623,24 +1623,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1649,24 +1649,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
@@ -1678,10 +1678,10 @@
         <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>55.11</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1693,27 +1693,27 @@
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>80</v>
+        <v>81.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>90.02</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U11" t="n">
         <v>2026</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1722,42 +1722,42 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>3127760000</v>
+        <v>139571760000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,24 +1766,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>79.77</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1795,10 +1795,10 @@
         <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>59.54</v>
       </c>
       <c r="L12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1810,27 +1810,27 @@
         <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>90</v>
+        <v>71.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>89.89</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U12" t="n">
         <v>2026</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1839,42 +1839,42 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>475588950000</v>
+        <v>10675360000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1883,24 +1883,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>79.45</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1912,13 +1912,13 @@
         <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>58.89</v>
       </c>
       <c r="L13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>100</v>
@@ -1927,27 +1927,27 @@
         <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>100</v>
+        <v>71.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>89.72</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U13" t="n">
         <v>2026</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1956,16 +1956,16 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>574646890000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1974,24 +1974,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>POLRES OKUS (665307)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2000,24 +2000,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>100</v>
+        <v>87.06</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -2029,7 +2029,7 @@
         <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>48.23</v>
       </c>
       <c r="L14" t="n">
         <v>100</v>
@@ -2044,7 +2044,7 @@
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>100</v>
@@ -2053,18 +2053,18 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U14" t="n">
         <v>2026</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2073,16 +2073,16 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>819256290000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2091,24 +2091,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2117,24 +2117,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>83.64</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -2146,10 +2146,10 @@
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>50.93</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2161,27 +2161,27 @@
         <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>80</v>
+        <v>80.19</v>
       </c>
       <c r="Q15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U15" t="n">
         <v>2026</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2190,42 +2190,42 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>43471570000</v>
+        <v>819256290000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2234,24 +2234,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>86.34</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
@@ -2263,13 +2263,13 @@
         <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>45.35</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16" t="n">
         <v>100</v>
@@ -2278,27 +2278,27 @@
         <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>80</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U16" t="n">
         <v>2026</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2307,42 +2307,42 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>38902730000</v>
+        <v>1376500000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2351,24 +2351,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>100</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
@@ -2380,13 +2380,13 @@
         <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>48.71</v>
       </c>
       <c r="L17" t="n">
         <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>100</v>
@@ -2395,27 +2395,27 @@
         <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>100</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U17" t="n">
         <v>2026</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>727218440000</v>
+        <v>106528210000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2442,17 +2442,17 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
@@ -2468,21 +2468,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>100</v>
@@ -2494,10 +2494,10 @@
         <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>100</v>
+        <v>88.58</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2512,27 +2512,27 @@
         <v>100</v>
       </c>
       <c r="P18" t="n">
-        <v>80</v>
+        <v>61.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>87.75</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U18" t="n">
         <v>2026</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2541,42 +2541,42 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>970430000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>86.45</v>
       </c>
       <c r="G19" t="n">
         <v>100</v>
@@ -2611,16 +2611,16 @@
         <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>100</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>100</v>
+        <v>67.27</v>
       </c>
       <c r="L19" t="n">
         <v>100</v>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>100</v>
@@ -2629,27 +2629,27 @@
         <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>100</v>
+        <v>69.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U19" t="n">
         <v>2026</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2658,16 +2658,16 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>128489370000</v>
+        <v>82576290000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2676,24 +2676,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2702,24 +2702,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>72.72</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
@@ -2731,7 +2731,7 @@
         <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>100</v>
+        <v>45.44</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>80</v>
+        <v>69.09</v>
       </c>
       <c r="Q20" t="n">
         <v>80</v>
@@ -2755,18 +2755,18 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>86.36</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U20" t="n">
         <v>2026</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2775,42 +2775,42 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>1001460000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2824,19 +2824,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>94.37</v>
       </c>
       <c r="G21" t="n">
-        <v>100</v>
+        <v>76.84</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -2845,10 +2845,10 @@
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>100</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>100</v>
+        <v>53.67</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>80</v>
+        <v>69.05</v>
       </c>
       <c r="Q21" t="n">
         <v>80</v>
@@ -2872,18 +2872,18 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>86.31</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U21" t="n">
         <v>2026</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2892,16 +2892,16 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>10710500000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2910,24 +2910,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,24 +2936,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>100</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
@@ -2965,10 +2965,10 @@
         <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>100</v>
+        <v>43.35</v>
       </c>
       <c r="L22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2980,27 +2980,27 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>90</v>
+        <v>68.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>85.84</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U22" t="n">
         <v>2026</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3009,42 +3009,42 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>317944150000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3053,24 +3053,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>100</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
@@ -3082,7 +3082,7 @@
         <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>100</v>
+        <v>43.2</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>80</v>
+        <v>68.64</v>
       </c>
       <c r="Q23" t="n">
         <v>80</v>
@@ -3106,18 +3106,18 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>100</v>
+        <v>85.8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U23" t="n">
         <v>2026</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3126,42 +3126,42 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>5891850000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3170,24 +3170,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
@@ -3199,13 +3199,13 @@
         <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>100</v>
+        <v>39.85</v>
       </c>
       <c r="L24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
@@ -3214,27 +3214,27 @@
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>100</v>
+        <v>67.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>100</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U24" t="n">
         <v>2026</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3243,42 +3243,42 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>9346940000</v>
+        <v>40671640000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3287,24 +3287,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>100</v>
+        <v>76.11</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
@@ -3316,7 +3316,7 @@
         <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>100</v>
+        <v>28.33</v>
       </c>
       <c r="L25" t="n">
         <v>100</v>
@@ -3331,7 +3331,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>90</v>
+        <v>75.67</v>
       </c>
       <c r="Q25" t="n">
         <v>90</v>
@@ -3340,18 +3340,18 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U25" t="n">
         <v>2026</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3360,42 +3360,42 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>53136840000</v>
+        <v>95645370000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3404,24 +3404,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>100</v>
+        <v>75.44</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
@@ -3433,13 +3433,13 @@
         <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>100</v>
+        <v>26.32</v>
       </c>
       <c r="L26" t="n">
         <v>100</v>
       </c>
       <c r="M26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>100</v>
@@ -3448,27 +3448,27 @@
         <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>100</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>83.63</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U26" t="n">
         <v>2026</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3477,42 +3477,42 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>729500000</v>
+        <v>53136840000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3521,24 +3521,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>66.75</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
@@ -3550,13 +3550,13 @@
         <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>33.49</v>
       </c>
       <c r="L27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>100</v>
@@ -3565,27 +3565,27 @@
         <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>83.37</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U27" t="n">
         <v>2026</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3594,42 +3594,42 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>1376500000</v>
+        <v>65205040000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3638,24 +3638,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>66.61</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
@@ -3667,13 +3667,13 @@
         <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>33.22</v>
       </c>
       <c r="L28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
@@ -3682,27 +3682,27 @@
         <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>100</v>
+        <v>66.64</v>
       </c>
       <c r="Q28" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>100</v>
+        <v>83.31</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U28" t="n">
         <v>2026</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3711,42 +3711,42 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>1230000000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3755,24 +3755,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>90.97</v>
       </c>
       <c r="G29" t="n">
-        <v>100</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -3781,16 +3781,16 @@
         <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>100</v>
+        <v>81.94</v>
       </c>
       <c r="K29" t="n">
-        <v>100</v>
+        <v>45.63</v>
       </c>
       <c r="L29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>100</v>
@@ -3799,27 +3799,27 @@
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>100</v>
+        <v>66.42</v>
       </c>
       <c r="Q29" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>100</v>
+        <v>83.02</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U29" t="n">
         <v>2026</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3828,16 +3828,16 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>42331120000</v>
+        <v>39404370000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3846,24 +3846,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3872,24 +3872,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>85.83</v>
       </c>
       <c r="G30" t="n">
-        <v>100</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -3898,16 +3898,16 @@
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>100</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>100</v>
+        <v>50.35</v>
       </c>
       <c r="L30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>100</v>
@@ -3916,27 +3916,27 @@
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>100</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>100</v>
+        <v>82.27</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U30" t="n">
         <v>2026</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3945,42 +3945,42 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>64847500000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3989,24 +3989,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>60.11</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
@@ -4018,7 +4018,7 @@
         <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>20.22</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>80</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="Q31" t="n">
         <v>80</v>
@@ -4042,18 +4042,18 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>100</v>
+        <v>80.06</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U31" t="n">
         <v>2026</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4062,16 +4062,16 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>10675360000</v>
+        <v>1001460000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4080,24 +4080,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4111,19 +4111,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>59.74</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -4135,7 +4135,7 @@
         <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>100</v>
+        <v>19.48</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>80</v>
+        <v>63.9</v>
       </c>
       <c r="Q32" t="n">
         <v>80</v>
@@ -4159,18 +4159,18 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>79.87</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U32" t="n">
         <v>2026</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4179,16 +4179,16 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>1707230000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4197,24 +4197,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4223,24 +4223,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>100</v>
+        <v>55.76</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -4252,7 +4252,7 @@
         <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>11.52</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4267,7 +4267,7 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>80</v>
+        <v>62.3</v>
       </c>
       <c r="Q33" t="n">
         <v>80</v>
@@ -4276,18 +4276,18 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>77.88</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U33" t="n">
         <v>2026</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4296,35 +4296,35 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>5127100000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>99.95</v>
+        <v>68.25</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4366,10 +4366,10 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>100</v>
+        <v>63.48</v>
       </c>
       <c r="K34" t="n">
-        <v>99.90000000000001</v>
+        <v>36.5</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>79.98</v>
+        <v>61.82</v>
       </c>
       <c r="Q34" t="n">
         <v>80</v>
@@ -4393,18 +4393,18 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>99.98</v>
+        <v>77.28</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U34" t="n">
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4413,35 +4413,35 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>39931940000</v>
+        <v>81321040000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4474,7 +4474,7 @@
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>99.93000000000001</v>
+        <v>52.06</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4486,7 +4486,7 @@
         <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>99.86</v>
+        <v>4.11</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>79.97</v>
+        <v>60.82</v>
       </c>
       <c r="Q35" t="n">
         <v>80</v>
@@ -4510,18 +4510,18 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>99.97</v>
+        <v>76.03</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U35" t="n">
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4530,20 +4530,20 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>345163450000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -4574,24 +4574,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>99.83</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4600,16 +4600,16 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>100</v>
+        <v>51.01</v>
       </c>
       <c r="K36" t="n">
-        <v>99.31999999999999</v>
+        <v>40.51</v>
       </c>
       <c r="L36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>100</v>
@@ -4618,27 +4618,27 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>99.86</v>
+        <v>60.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>99.86</v>
+        <v>75.94</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U36" t="n">
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4647,35 +4647,35 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>40484710000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
@@ -4691,24 +4691,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>96.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>50.62</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -4717,10 +4717,10 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>93.98</v>
+        <v>100</v>
       </c>
       <c r="K37" t="n">
-        <v>100</v>
+        <v>1.23</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>79.09999999999999</v>
+        <v>60.25</v>
       </c>
       <c r="Q37" t="n">
         <v>80</v>
@@ -4744,18 +4744,18 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>98.87</v>
+        <v>75.31</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U37" t="n">
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4764,35 +4764,35 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>39404370000</v>
+        <v>5891850000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
@@ -4808,24 +4808,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>98.3</v>
+        <v>50.19</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4837,10 +4837,10 @@
         <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>94.89</v>
+        <v>0.37</v>
       </c>
       <c r="L38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4852,27 +4852,27 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>88.98</v>
+        <v>60.07</v>
       </c>
       <c r="Q38" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>98.86</v>
+        <v>75.09</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U38" t="n">
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4881,16 +4881,16 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>95645370000</v>
+        <v>345163450000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4899,17 +4899,17 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
@@ -4930,66 +4930,66 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>96.02</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>50.04</v>
       </c>
       <c r="H39" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>92.03</v>
+        <v>100</v>
       </c>
       <c r="K39" t="n">
-        <v>100</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
       </c>
       <c r="O39" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>98.76000000000001</v>
+        <v>60.01</v>
       </c>
       <c r="Q39" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>98.76000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U39" t="n">
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4998,35 +4998,35 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>13427580000</v>
+        <v>475588950000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
@@ -5042,24 +5042,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>95.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -5068,16 +5068,16 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>90.97</v>
+        <v>100</v>
       </c>
       <c r="K40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -5086,27 +5086,27 @@
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>98.65000000000001</v>
+        <v>60</v>
       </c>
       <c r="Q40" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>98.65000000000001</v>
+        <v>75</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U40" t="n">
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5115,35 +5115,35 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>82576290000</v>
+        <v>970430000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
@@ -5159,21 +5159,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>95.94</v>
+        <v>100</v>
       </c>
       <c r="G41" t="n">
         <v>100</v>
@@ -5185,10 +5185,10 @@
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>91.87</v>
+        <v>100</v>
       </c>
       <c r="K41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>100</v>
@@ -5203,27 +5203,27 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>88.78</v>
+        <v>60</v>
       </c>
       <c r="Q41" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>98.65000000000001</v>
+        <v>75</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U41" t="n">
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5232,16 +5232,16 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>9098870000</v>
+        <v>1230000000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -5250,17 +5250,17 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
@@ -5276,24 +5276,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
+        <v>87.98</v>
       </c>
       <c r="G42" t="n">
-        <v>97.13</v>
+        <v>55.09</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5302,10 +5302,10 @@
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>100</v>
+        <v>75.95</v>
       </c>
       <c r="K42" t="n">
-        <v>94.26000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5320,7 +5320,7 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>78.84999999999999</v>
+        <v>58.43</v>
       </c>
       <c r="Q42" t="n">
         <v>80</v>
@@ -5329,18 +5329,18 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>98.56999999999999</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U42" t="n">
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5349,35 +5349,35 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>74397990000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
@@ -5393,24 +5393,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>95.81999999999999</v>
+        <v>67.13</v>
       </c>
       <c r="G43" t="n">
-        <v>100</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -5419,10 +5419,10 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>91.63</v>
+        <v>34.25</v>
       </c>
       <c r="K43" t="n">
-        <v>100</v>
+        <v>41.01</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>78.73999999999999</v>
+        <v>58.34</v>
       </c>
       <c r="Q43" t="n">
         <v>80</v>
@@ -5446,18 +5446,18 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>98.43000000000001</v>
+        <v>72.92</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U43" t="n">
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5466,16 +5466,16 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>15177700000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5484,17 +5484,17 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
@@ -5515,19 +5515,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5539,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>93.59</v>
+        <v>0.36</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5554,27 +5554,27 @@
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>78.72</v>
+        <v>50.07</v>
       </c>
       <c r="Q44" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>98.40000000000001</v>
+        <v>71.53</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U44" t="n">
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5583,35 +5583,35 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>3898470000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
@@ -5627,21 +5627,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>93.92</v>
+        <v>100</v>
       </c>
       <c r="G45" t="n">
         <v>100</v>
@@ -5653,16 +5653,16 @@
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>87.83</v>
+        <v>100</v>
       </c>
       <c r="K45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>100</v>
@@ -5671,27 +5671,27 @@
         <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>98.17</v>
+        <v>50</v>
       </c>
       <c r="Q45" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>98.17</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U45" t="n">
         <v>2026</v>
       </c>
       <c r="V45" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5700,35 +5700,35 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>81321040000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
@@ -5744,24 +5744,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>94.98</v>
+        <v>100</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -5773,13 +5773,13 @@
         <v>100</v>
       </c>
       <c r="K46" t="n">
-        <v>84.94</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>100</v>
@@ -5788,27 +5788,27 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>86.98999999999999</v>
+        <v>50</v>
       </c>
       <c r="Q46" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>96.65000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U46" t="n">
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5817,35 +5817,35 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>65205040000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -5866,19 +5866,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>92.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5890,7 +5890,7 @@
         <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>85.41</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5905,27 +5905,27 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>77.08</v>
+        <v>50</v>
       </c>
       <c r="Q47" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>96.34999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U47" t="n">
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5934,16 +5934,16 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>1731600000</v>
+        <v>3484030000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5952,17 +5952,17 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
@@ -5983,16 +5983,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>90.06</v>
+        <v>100</v>
       </c>
       <c r="G48" t="n">
         <v>100</v>
@@ -6004,10 +6004,10 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>80.12</v>
+        <v>100</v>
       </c>
       <c r="K48" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6022,27 +6022,27 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>77.02</v>
+        <v>50</v>
       </c>
       <c r="Q48" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>96.27</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U48" t="n">
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6051,16 +6051,16 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>9731020000</v>
+        <v>1707230000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6069,17 +6069,17 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -6095,21 +6095,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>89.01000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G49" t="n">
         <v>100</v>
@@ -6121,10 +6121,10 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>78.01000000000001</v>
+        <v>37.79</v>
       </c>
       <c r="K49" t="n">
-        <v>100</v>
+        <v>38.84</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6139,27 +6139,27 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>76.7</v>
+        <v>48.44</v>
       </c>
       <c r="Q49" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>95.88</v>
+        <v>69.2</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U49" t="n">
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6168,35 +6168,35 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>5176090000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
@@ -6226,25 +6226,25 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>97.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>95.04000000000001</v>
+        <v>55.33</v>
       </c>
       <c r="H50" t="n">
-        <v>100</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="I50" t="n">
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>94.52</v>
+        <v>100</v>
       </c>
       <c r="K50" t="n">
-        <v>85.13</v>
+        <v>10.66</v>
       </c>
       <c r="L50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -6253,30 +6253,30 @@
         <v>100</v>
       </c>
       <c r="O50" t="n">
-        <v>100</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="P50" t="n">
-        <v>86.2</v>
+        <v>54.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>95.78</v>
+        <v>68.12</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U50" t="n">
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6285,12 +6285,12 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z50" t="n">
@@ -6329,71 +6329,71 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>89.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>100</v>
+        <v>50.22</v>
       </c>
       <c r="H51" t="n">
-        <v>95.33</v>
+        <v>77.23</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>78.08</v>
+        <v>100</v>
       </c>
       <c r="K51" t="n">
-        <v>100</v>
+        <v>0.44</v>
       </c>
       <c r="L51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>100</v>
       </c>
       <c r="O51" t="n">
-        <v>95.33</v>
+        <v>77.23</v>
       </c>
       <c r="P51" t="n">
-        <v>95.54000000000001</v>
+        <v>54.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>95.54000000000001</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U51" t="n">
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6402,35 +6402,35 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>31225620000</v>
+        <v>317944150000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
@@ -6446,71 +6446,71 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>87.02</v>
+        <v>97.44</v>
       </c>
       <c r="G52" t="n">
-        <v>100</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>47.5</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>74.04000000000001</v>
+        <v>94.88</v>
       </c>
       <c r="K52" t="n">
-        <v>97.62</v>
+        <v>39.29</v>
       </c>
       <c r="L52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>100</v>
+        <v>47.5</v>
       </c>
       <c r="P52" t="n">
-        <v>85.63</v>
+        <v>53.97</v>
       </c>
       <c r="Q52" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>95.14</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U52" t="n">
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6519,35 +6519,35 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>287629890000</v>
+        <v>10710500000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
@@ -6563,24 +6563,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>95.19</v>
+        <v>64.7</v>
       </c>
       <c r="G53" t="n">
-        <v>93.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
@@ -6589,10 +6589,10 @@
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>90.37</v>
+        <v>29.4</v>
       </c>
       <c r="K53" t="n">
-        <v>86.52</v>
+        <v>29.05</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -6607,27 +6607,27 @@
         <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>75.86</v>
+        <v>45.22</v>
       </c>
       <c r="Q53" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>94.81999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U53" t="n">
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6636,35 +6636,35 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>50054370000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
@@ -6680,39 +6680,39 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>89.63</v>
+        <v>94.59</v>
       </c>
       <c r="G54" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I54" t="n">
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>79.26000000000001</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>93.79000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6721,10 +6721,10 @@
         <v>100</v>
       </c>
       <c r="O54" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="P54" t="n">
-        <v>75.65000000000001</v>
+        <v>49.74</v>
       </c>
       <c r="Q54" t="n">
         <v>80</v>
@@ -6733,18 +6733,18 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>94.56</v>
+        <v>62.17</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>29335310000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -6771,17 +6771,17 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
@@ -6802,19 +6802,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>85.61</v>
+        <v>50.75</v>
       </c>
       <c r="G55" t="n">
-        <v>97.61</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,10 +6823,10 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>71.22</v>
+        <v>1.49</v>
       </c>
       <c r="K55" t="n">
-        <v>92.81999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="L55" t="n">
         <v>100</v>
@@ -6841,7 +6841,7 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>84.25</v>
+        <v>55.33</v>
       </c>
       <c r="Q55" t="n">
         <v>90</v>
@@ -6850,18 +6850,18 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>93.61</v>
+        <v>61.48</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U55" t="n">
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6870,35 +6870,35 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>16133240000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -6919,31 +6919,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>56.83</v>
       </c>
       <c r="G56" t="n">
-        <v>92.98999999999999</v>
+        <v>54.07</v>
       </c>
       <c r="H56" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>100</v>
+        <v>13.66</v>
       </c>
       <c r="K56" t="n">
-        <v>85.97</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6955,10 +6955,10 @@
         <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>73.69</v>
+        <v>48.68</v>
       </c>
       <c r="Q56" t="n">
         <v>80</v>
@@ -6967,18 +6967,18 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>92.12</v>
+        <v>60.85</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U56" t="n">
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6987,35 +6987,35 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>7789580000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
@@ -7036,22 +7036,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>83.84999999999999</v>
+        <v>100</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I57" t="n">
         <v>100</v>
@@ -7060,7 +7060,7 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>67.69</v>
+        <v>0.33</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -7072,30 +7072,30 @@
         <v>100</v>
       </c>
       <c r="O57" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="P57" t="n">
-        <v>73.54000000000001</v>
+        <v>41.32</v>
       </c>
       <c r="Q57" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>91.92</v>
+        <v>59.02</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U57" t="n">
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7104,35 +7104,35 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>15707450000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -7153,31 +7153,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>80.86</v>
+        <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>96.2</v>
+        <v>51.36</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="I58" t="n">
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>61.72</v>
+        <v>100</v>
       </c>
       <c r="K58" t="n">
-        <v>92.39</v>
+        <v>2.71</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>100</v>
       </c>
       <c r="O58" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="P58" t="n">
-        <v>72.73999999999999</v>
+        <v>46.54</v>
       </c>
       <c r="Q58" t="n">
         <v>80</v>
@@ -7201,18 +7201,18 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>90.92</v>
+        <v>58.18</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U58" t="n">
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7221,16 +7221,16 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>5671610000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -7239,17 +7239,17 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
@@ -7270,31 +7270,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>75.73999999999999</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>98.95</v>
+        <v>56.22</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>67.94</v>
       </c>
       <c r="I59" t="n">
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>51.48</v>
+        <v>34.02</v>
       </c>
       <c r="K59" t="n">
-        <v>97.89</v>
+        <v>12.43</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -7306,10 +7306,10 @@
         <v>100</v>
       </c>
       <c r="O59" t="n">
-        <v>100</v>
+        <v>67.94</v>
       </c>
       <c r="P59" t="n">
-        <v>72.3</v>
+        <v>44.57</v>
       </c>
       <c r="Q59" t="n">
         <v>80</v>
@@ -7318,18 +7318,18 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>90.38</v>
+        <v>55.72</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U59" t="n">
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7338,35 +7338,35 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>13489830000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7382,71 +7382,71 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>80.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>94.36</v>
+        <v>100</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>61.58</v>
+        <v>100</v>
       </c>
       <c r="K60" t="n">
-        <v>77.42</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>100</v>
       </c>
       <c r="M60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="P60" t="n">
-        <v>89.72</v>
+        <v>42.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>89.72</v>
+        <v>53.13</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U60" t="n">
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7455,16 +7455,16 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>6368000000</v>
+        <v>729500000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7499,39 +7499,39 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>80.69</v>
       </c>
       <c r="G61" t="n">
-        <v>73.13</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>100</v>
+        <v>61.37</v>
       </c>
       <c r="K61" t="n">
-        <v>46.25</v>
+        <v>4.86</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -7540,30 +7540,30 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="P61" t="n">
-        <v>69.25</v>
+        <v>47.68</v>
       </c>
       <c r="Q61" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>86.56</v>
+        <v>52.98</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U61" t="n">
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7572,35 +7572,35 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>114852670000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7621,19 +7621,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>54.04</v>
       </c>
       <c r="G62" t="n">
-        <v>87.83</v>
+        <v>51.27</v>
       </c>
       <c r="H62" t="n">
         <v>65</v>
@@ -7642,10 +7642,10 @@
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>100</v>
+        <v>8.07</v>
       </c>
       <c r="K62" t="n">
-        <v>75.66</v>
+        <v>2.53</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
         <v>65</v>
       </c>
       <c r="P62" t="n">
-        <v>66.38</v>
+        <v>37.97</v>
       </c>
       <c r="Q62" t="n">
         <v>80</v>
@@ -7669,18 +7669,18 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>82.98</v>
+        <v>47.46</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U62" t="n">
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7689,16 +7689,16 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>7585360000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -7707,17 +7707,17 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7738,31 +7738,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>82.27</v>
+        <v>50.65</v>
       </c>
       <c r="G63" t="n">
-        <v>94.05</v>
+        <v>100</v>
       </c>
       <c r="H63" t="n">
-        <v>67.04000000000001</v>
+        <v>65</v>
       </c>
       <c r="I63" t="n">
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>64.54000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="K63" t="n">
-        <v>88.09999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -7774,30 +7774,30 @@
         <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>67.04000000000001</v>
+        <v>65</v>
       </c>
       <c r="P63" t="n">
-        <v>64.06</v>
+        <v>26.56</v>
       </c>
       <c r="Q63" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>80.08</v>
+        <v>37.94</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U63" t="n">
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7806,35 +7806,35 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>4481070000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7855,66 +7855,66 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>88.34</v>
+        <v>50.34</v>
       </c>
       <c r="G64" t="n">
-        <v>96.78</v>
+        <v>50.17</v>
       </c>
       <c r="H64" t="n">
-        <v>30</v>
+        <v>30.46</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>76.67</v>
+        <v>0.68</v>
       </c>
       <c r="K64" t="n">
-        <v>87.09999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="L64" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>30</v>
+        <v>30.46</v>
       </c>
       <c r="P64" t="n">
-        <v>76.42</v>
+        <v>27.78</v>
       </c>
       <c r="Q64" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>76.42</v>
+        <v>34.73</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U64" t="n">
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7923,35 +7923,35 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>20589110000</v>
+        <v>4481070000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -7972,12 +7972,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695184</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -8024,14 +8024,14 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U65" t="n">
         <v>2026</v>
       </c>
       <c r="V65" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8040,16 +8040,16 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>6728240000</v>
+        <v>6722660000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -8058,17 +8058,17 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU (695176)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN (695184)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
@@ -8089,12 +8089,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8141,14 +8141,14 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U66" t="n">
         <v>2026</v>
       </c>
       <c r="V66" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8157,16 +8157,16 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>6314270000</v>
+        <v>6728240000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -8175,17 +8175,17 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR (695182)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU (695176)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -8206,12 +8206,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8258,14 +8258,14 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U67" t="n">
         <v>2026</v>
       </c>
       <c r="V67" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -8274,16 +8274,16 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>MARET 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>6722660000</v>
+        <v>6314270000</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -8292,17 +8292,17 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN (695184)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR (695182)</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -596,24 +596,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>97.55</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
@@ -625,13 +625,13 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>90.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -640,20 +640,20 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>98.04000000000001</v>
+        <v>80</v>
       </c>
       <c r="Q2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>98.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -669,16 +669,16 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>42331120000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -687,17 +687,17 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -713,27 +713,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>93.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>99.19</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -742,7 +742,7 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>73.38</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
         <v>100</v>
@@ -754,10 +754,10 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>99.19</v>
+        <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>94.47</v>
+        <v>100</v>
       </c>
       <c r="Q3" t="n">
         <v>100</v>
@@ -766,18 +766,18 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>94.47</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>2026</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -786,35 +786,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>40484710000</v>
+        <v>574646890000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -830,24 +830,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>87.48</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
@@ -859,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>74.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>74.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q4" t="n">
         <v>80</v>
@@ -883,18 +883,18 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>93.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>2026</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -903,35 +903,35 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>95984080000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
@@ -947,24 +947,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>91.05</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
@@ -976,13 +976,13 @@
         <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>64.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -991,27 +991,27 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>92.84</v>
+        <v>80</v>
       </c>
       <c r="Q5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>92.84</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>2026</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1020,35 +1020,35 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>64847500000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
@@ -1064,24 +1064,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>90.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
@@ -1093,7 +1093,7 @@
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>60.39</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
         <v>100</v>
@@ -1108,7 +1108,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>92.08</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="n">
         <v>100</v>
@@ -1117,18 +1117,18 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>92.08</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>2026</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1137,35 +1137,35 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>574646890000</v>
+        <v>1376500000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>POLRES OKUS (665307)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -1186,19 +1186,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>83.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
@@ -1210,13 +1210,13 @@
         <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>67.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
@@ -1225,27 +1225,27 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>73.56</v>
+        <v>100</v>
       </c>
       <c r="Q7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>91.95</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U7" t="n">
         <v>2026</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1254,35 +1254,35 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>31572500000</v>
+        <v>106528210000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -1303,19 +1303,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>86.28</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
@@ -1327,13 +1327,13 @@
         <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>58.85</v>
+        <v>100</v>
       </c>
       <c r="L8" t="n">
         <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
@@ -1342,27 +1342,27 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>81.77</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>90.86</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U8" t="n">
         <v>2026</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1371,35 +1371,35 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>128489370000</v>
+        <v>42331120000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -1415,24 +1415,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>85.92</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -1444,10 +1444,10 @@
         <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>57.75</v>
+        <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1459,27 +1459,27 @@
         <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>81.55</v>
+        <v>80</v>
       </c>
       <c r="Q9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>90.61</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U9" t="n">
         <v>2026</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1488,35 +1488,35 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>727218440000</v>
+        <v>10675360000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
@@ -1532,24 +1532,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>80.91</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -1561,13 +1561,13 @@
         <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>61.82</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
         <v>100</v>
@@ -1576,27 +1576,27 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>72.36</v>
+        <v>100</v>
       </c>
       <c r="Q10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>90.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U10" t="n">
         <v>2026</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1605,35 +1605,35 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>5127100000</v>
+        <v>139571760000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -1649,24 +1649,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>85.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
@@ -1678,10 +1678,10 @@
         <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>55.11</v>
+        <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1693,27 +1693,27 @@
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>81.02</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>90.02</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U11" t="n">
         <v>2026</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1722,35 +1722,35 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>139571760000</v>
+        <v>5127100000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -1766,24 +1766,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>79.77</v>
+        <v>100</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1795,13 +1795,13 @@
         <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>59.54</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
         <v>100</v>
@@ -1810,27 +1810,27 @@
         <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>71.91</v>
+        <v>100</v>
       </c>
       <c r="Q12" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>89.89</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U12" t="n">
         <v>2026</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1839,35 +1839,35 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>10675360000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
@@ -1883,24 +1883,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>79.45</v>
+        <v>99.83</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1912,13 +1912,13 @@
         <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>58.89</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
         <v>100</v>
@@ -1927,27 +1927,27 @@
         <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>71.78</v>
+        <v>99.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>89.72</v>
+        <v>99.86</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U13" t="n">
         <v>2026</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1956,35 +1956,35 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>74397990000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -2000,24 +2000,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>87.06</v>
+        <v>99.77</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -2029,7 +2029,7 @@
         <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>48.23</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>100</v>
@@ -2044,7 +2044,7 @@
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>89.65000000000001</v>
+        <v>99.81</v>
       </c>
       <c r="Q14" t="n">
         <v>100</v>
@@ -2053,18 +2053,18 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>89.65000000000001</v>
+        <v>99.81</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U14" t="n">
         <v>2026</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2073,16 +2073,16 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>105914680000</v>
+        <v>727218440000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2091,17 +2091,17 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
@@ -2117,24 +2117,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>83.64</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -2146,13 +2146,13 @@
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>50.93</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>100</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" t="n">
         <v>100</v>
@@ -2161,27 +2161,27 @@
         <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>80.19</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>89.09999999999999</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U15" t="n">
         <v>2026</v>
       </c>
       <c r="V15" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>819256290000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2208,17 +2208,17 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
@@ -2234,24 +2234,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>86.34</v>
+        <v>99.66</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
@@ -2263,7 +2263,7 @@
         <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>45.35</v>
+        <v>98.64</v>
       </c>
       <c r="L16" t="n">
         <v>100</v>
@@ -2278,7 +2278,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>89.06999999999999</v>
+        <v>99.73</v>
       </c>
       <c r="Q16" t="n">
         <v>100</v>
@@ -2287,18 +2287,18 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>89.06999999999999</v>
+        <v>99.73</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U16" t="n">
         <v>2026</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2307,35 +2307,35 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>1376500000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
@@ -2351,24 +2351,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>82.90000000000001</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
@@ -2380,13 +2380,13 @@
         <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>48.71</v>
+        <v>98.03</v>
       </c>
       <c r="L17" t="n">
         <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17" t="n">
         <v>100</v>
@@ -2395,27 +2395,27 @@
         <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>79.73999999999999</v>
+        <v>99.61</v>
       </c>
       <c r="Q17" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>88.59999999999999</v>
+        <v>99.61</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U17" t="n">
         <v>2026</v>
       </c>
       <c r="V17" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>106528210000</v>
+        <v>819256290000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2442,17 +2442,17 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
@@ -2468,24 +2468,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="H18" t="n">
         <v>100</v>
@@ -2494,10 +2494,10 @@
         <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>88.58</v>
+        <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>65.68000000000001</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2512,27 +2512,27 @@
         <v>100</v>
       </c>
       <c r="P18" t="n">
-        <v>61.42</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>87.75</v>
+        <v>99.02</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U18" t="n">
         <v>2026</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2541,35 +2541,35 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>405581540000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
@@ -2590,19 +2590,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>86.45</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="H19" t="n">
         <v>100</v>
@@ -2611,16 +2611,16 @@
         <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>72.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K19" t="n">
-        <v>67.27</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="L19" t="n">
         <v>100</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19" t="n">
         <v>100</v>
@@ -2629,27 +2629,27 @@
         <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>69.39</v>
+        <v>98.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>86.73999999999999</v>
+        <v>98.78</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U19" t="n">
         <v>2026</v>
       </c>
       <c r="V19" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2658,16 +2658,16 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>82576290000</v>
+        <v>95984080000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2676,17 +2676,17 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
@@ -2702,24 +2702,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>72.72</v>
+        <v>96.8</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
@@ -2731,7 +2731,7 @@
         <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>45.44</v>
+        <v>93.59</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>69.09</v>
+        <v>78.72</v>
       </c>
       <c r="Q20" t="n">
         <v>80</v>
@@ -2755,18 +2755,18 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>86.36</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U20" t="n">
         <v>2026</v>
       </c>
       <c r="V20" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2775,35 +2775,35 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>38902730000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
@@ -2819,24 +2819,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>94.37</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>76.84</v>
+        <v>98.56</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -2845,10 +2845,10 @@
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>88.73999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>53.67</v>
+        <v>97.11</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>69.05</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>80</v>
@@ -2872,18 +2872,18 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>86.31</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U21" t="n">
         <v>2026</v>
       </c>
       <c r="V21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2892,35 +2892,35 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>9098870000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
@@ -2936,24 +2936,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
+        <v>93.23</v>
       </c>
       <c r="G22" t="n">
-        <v>71.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
@@ -2962,16 +2962,16 @@
         <v>100</v>
       </c>
       <c r="J22" t="n">
-        <v>100</v>
+        <v>86.45</v>
       </c>
       <c r="K22" t="n">
-        <v>43.35</v>
+        <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" t="n">
         <v>100</v>
@@ -2980,27 +2980,27 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>68.67</v>
+        <v>97.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>85.84</v>
+        <v>97.97</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U22" t="n">
         <v>2026</v>
       </c>
       <c r="V22" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3009,35 +3009,35 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>43471570000</v>
+        <v>82576290000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
@@ -3053,24 +3053,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>71.59999999999999</v>
+        <v>96.89</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
@@ -3082,10 +3082,10 @@
         <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>43.2</v>
+        <v>90.67</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3097,27 +3097,27 @@
         <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>68.64</v>
+        <v>88.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>85.8</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U23" t="n">
         <v>2026</v>
       </c>
       <c r="V23" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3126,35 +3126,35 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>39931940000</v>
+        <v>95645370000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
@@ -3170,24 +3170,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>90.87</v>
       </c>
       <c r="G24" t="n">
-        <v>69.93000000000001</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
@@ -3196,16 +3196,16 @@
         <v>100</v>
       </c>
       <c r="J24" t="n">
-        <v>100</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>39.85</v>
+        <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
@@ -3214,27 +3214,27 @@
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>67.97</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>84.95999999999999</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U24" t="n">
         <v>2026</v>
       </c>
       <c r="V24" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3243,35 +3243,35 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>40671640000</v>
+        <v>81321040000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
@@ -3287,24 +3287,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>76.11</v>
+        <v>96</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
@@ -3316,13 +3316,13 @@
         <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>28.33</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="L25" t="n">
         <v>100</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
         <v>100</v>
@@ -3331,27 +3331,27 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>75.67</v>
+        <v>96.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>84.06999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U25" t="n">
         <v>2026</v>
       </c>
       <c r="V25" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3360,35 +3360,35 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>95645370000</v>
+        <v>1230000000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
@@ -3404,24 +3404,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>75.44</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
@@ -3433,10 +3433,10 @@
         <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>26.32</v>
+        <v>86.8</v>
       </c>
       <c r="L26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3448,27 +3448,27 @@
         <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>75.26000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>83.63</v>
+        <v>96.7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U26" t="n">
         <v>2026</v>
       </c>
       <c r="V26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3477,35 +3477,35 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>53136840000</v>
+        <v>1707230000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
@@ -3521,27 +3521,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>66.75</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I27" t="n">
         <v>100</v>
@@ -3550,42 +3550,42 @@
         <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>33.49</v>
+        <v>100</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27" t="n">
         <v>100</v>
       </c>
       <c r="O27" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="P27" t="n">
-        <v>66.7</v>
+        <v>96.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>83.37</v>
+        <v>96.5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U27" t="n">
         <v>2026</v>
       </c>
       <c r="V27" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3594,35 +3594,35 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>65205040000</v>
+        <v>729500000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
@@ -3638,24 +3638,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>66.61</v>
+        <v>91.53</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
@@ -3667,7 +3667,7 @@
         <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>33.22</v>
+        <v>83.05</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3682,7 +3682,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>66.64</v>
+        <v>76.61</v>
       </c>
       <c r="Q28" t="n">
         <v>80</v>
@@ -3691,18 +3691,18 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>83.31</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U28" t="n">
         <v>2026</v>
       </c>
       <c r="V28" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3711,35 +3711,35 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>114852670000</v>
+        <v>1001460000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
@@ -3755,24 +3755,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>90.97</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>72.81999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -3781,10 +3781,10 @@
         <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>81.94</v>
+        <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>45.63</v>
+        <v>81</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>66.42</v>
+        <v>76.2</v>
       </c>
       <c r="Q29" t="n">
         <v>80</v>
@@ -3808,18 +3808,18 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>83.02</v>
+        <v>95.25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U29" t="n">
         <v>2026</v>
       </c>
       <c r="V29" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3828,16 +3828,16 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>39404370000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3846,17 +3846,17 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
@@ -3872,24 +3872,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>85.83</v>
+        <v>96.59</v>
       </c>
       <c r="G30" t="n">
-        <v>75.18000000000001</v>
+        <v>94.33</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -3898,13 +3898,13 @@
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>71.65000000000001</v>
+        <v>93.17</v>
       </c>
       <c r="K30" t="n">
-        <v>50.35</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3916,27 +3916,27 @@
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>65.81999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>82.27</v>
+        <v>95.08</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U30" t="n">
         <v>2026</v>
       </c>
       <c r="V30" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3945,35 +3945,35 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>50054370000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
@@ -3989,24 +3989,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>83.56</v>
       </c>
       <c r="G31" t="n">
-        <v>60.11</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
@@ -4015,16 +4015,16 @@
         <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>100</v>
+        <v>67.12</v>
       </c>
       <c r="K31" t="n">
-        <v>20.22</v>
+        <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N31" t="n">
         <v>100</v>
@@ -4033,27 +4033,27 @@
         <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>64.04000000000001</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>80.06</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U31" t="n">
         <v>2026</v>
       </c>
       <c r="V31" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4062,35 +4062,35 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>1001460000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
@@ -4111,19 +4111,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>59.74</v>
+        <v>88.88</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -4135,7 +4135,7 @@
         <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>19.48</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>63.9</v>
+        <v>75.55</v>
       </c>
       <c r="Q32" t="n">
         <v>80</v>
@@ -4159,18 +4159,18 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>79.87</v>
+        <v>94.44</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U32" t="n">
         <v>2026</v>
       </c>
       <c r="V32" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4179,16 +4179,16 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>3898470000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4197,17 +4197,17 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
@@ -4223,24 +4223,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>55.76</v>
+        <v>88.7</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -4252,7 +4252,7 @@
         <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>11.52</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4267,7 +4267,7 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>62.3</v>
+        <v>75.48</v>
       </c>
       <c r="Q33" t="n">
         <v>80</v>
@@ -4276,18 +4276,18 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>77.88</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U33" t="n">
         <v>2026</v>
       </c>
       <c r="V33" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4296,35 +4296,35 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>11480750000</v>
+        <v>3484030000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>81.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>68.25</v>
+        <v>88</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4366,10 +4366,10 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>63.48</v>
+        <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>36.5</v>
+        <v>76</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>61.82</v>
+        <v>75.2</v>
       </c>
       <c r="Q34" t="n">
         <v>80</v>
@@ -4393,18 +4393,18 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>77.28</v>
+        <v>94</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U34" t="n">
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4413,16 +4413,16 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>81321040000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -4431,17 +4431,17 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
@@ -4457,24 +4457,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>52.06</v>
+        <v>85.89</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4486,7 +4486,7 @@
         <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>4.11</v>
+        <v>71.77</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>60.82</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="Q35" t="n">
         <v>80</v>
@@ -4510,18 +4510,18 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>76.03</v>
+        <v>92.94</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U35" t="n">
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4530,35 +4530,35 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>9346940000</v>
+        <v>40671640000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
@@ -4579,19 +4579,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>75.51000000000001</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>70.26000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4600,10 +4600,10 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>51.01</v>
+        <v>100</v>
       </c>
       <c r="K36" t="n">
-        <v>40.51</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>60.75</v>
+        <v>73.48</v>
       </c>
       <c r="Q36" t="n">
         <v>80</v>
@@ -4627,18 +4627,18 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>75.94</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U36" t="n">
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4647,16 +4647,16 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>9731020000</v>
+        <v>970430000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4665,17 +4665,17 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
@@ -4691,24 +4691,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>84.45</v>
       </c>
       <c r="G37" t="n">
-        <v>50.62</v>
+        <v>93.86</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -4717,10 +4717,10 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>100</v>
+        <v>68.89</v>
       </c>
       <c r="K37" t="n">
-        <v>1.23</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>60.25</v>
+        <v>72.88</v>
       </c>
       <c r="Q37" t="n">
         <v>80</v>
@@ -4744,18 +4744,18 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>75.31</v>
+        <v>91.09</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U37" t="n">
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4764,35 +4764,35 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>5891850000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
@@ -4808,24 +4808,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
+        <v>92.91</v>
       </c>
       <c r="G38" t="n">
-        <v>50.19</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4834,10 +4834,10 @@
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>100</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>0.37</v>
+        <v>74.97</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>60.07</v>
+        <v>72.87</v>
       </c>
       <c r="Q38" t="n">
         <v>80</v>
@@ -4861,18 +4861,18 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>75.09</v>
+        <v>91.08</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U38" t="n">
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4881,35 +4881,35 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>345163450000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
@@ -4925,24 +4925,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>50.04</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
@@ -4954,13 +4954,13 @@
         <v>100</v>
       </c>
       <c r="K39" t="n">
-        <v>0.07000000000000001</v>
+        <v>58.31</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
@@ -4969,27 +4969,27 @@
         <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>60.01</v>
+        <v>81.66</v>
       </c>
       <c r="Q39" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>75.02</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U39" t="n">
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4998,16 +4998,16 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>475588950000</v>
+        <v>65205040000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -5016,17 +5016,17 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
@@ -5042,24 +5042,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>50</v>
+        <v>84.12</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -5068,10 +5068,10 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>100</v>
+        <v>90.97</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -5086,7 +5086,7 @@
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>60</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="Q40" t="n">
         <v>80</v>
@@ -5095,18 +5095,18 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>75</v>
+        <v>90.37</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U40" t="n">
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5115,35 +5115,35 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>970430000</v>
+        <v>39404370000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
@@ -5159,24 +5159,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>100</v>
       </c>
       <c r="G41" t="n">
-        <v>100</v>
+        <v>79.17</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
@@ -5188,10 +5188,10 @@
         <v>100</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>58.34</v>
       </c>
       <c r="L41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5203,7 +5203,7 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>60</v>
+        <v>71.67</v>
       </c>
       <c r="Q41" t="n">
         <v>80</v>
@@ -5212,18 +5212,18 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>75</v>
+        <v>89.59</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U41" t="n">
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5232,35 +5232,35 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>1230000000</v>
+        <v>475588950000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
@@ -5276,24 +5276,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>87.98</v>
+        <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>55.09</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5302,13 +5302,13 @@
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>75.95</v>
+        <v>100</v>
       </c>
       <c r="K42" t="n">
-        <v>10.18</v>
+        <v>52.02</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5320,27 +5320,27 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>58.43</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="Q42" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>73.04000000000001</v>
+        <v>89.34</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U42" t="n">
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5349,16 +5349,16 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>15177700000</v>
+        <v>53136840000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -5367,17 +5367,17 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
@@ -5393,24 +5393,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>67.13</v>
+        <v>93.77</v>
       </c>
       <c r="G43" t="n">
-        <v>70.51000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -5419,10 +5419,10 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>34.25</v>
+        <v>87.53</v>
       </c>
       <c r="K43" t="n">
-        <v>41.01</v>
+        <v>64.27</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>58.34</v>
+        <v>70.98</v>
       </c>
       <c r="Q43" t="n">
         <v>80</v>
@@ -5446,18 +5446,18 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>72.92</v>
+        <v>88.73</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U43" t="n">
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5466,16 +5466,16 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>31225620000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5484,17 +5484,17 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
@@ -5515,19 +5515,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>100</v>
+        <v>77.25</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5539,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>0.36</v>
+        <v>54.49</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5554,27 +5554,27 @@
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>50.07</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="Q44" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>71.53</v>
+        <v>88.62</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U44" t="n">
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5583,35 +5583,35 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>15707450000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
@@ -5632,22 +5632,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>100</v>
       </c>
       <c r="G45" t="n">
-        <v>100</v>
+        <v>96.81</v>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I45" t="n">
         <v>100</v>
@@ -5656,7 +5656,7 @@
         <v>100</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>93.61</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5668,30 +5668,30 @@
         <v>100</v>
       </c>
       <c r="O45" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="P45" t="n">
-        <v>50</v>
+        <v>69.97</v>
       </c>
       <c r="Q45" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>71.43000000000001</v>
+        <v>87.47</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U45" t="n">
         <v>2026</v>
       </c>
       <c r="V45" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5700,16 +5700,16 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>1731600000</v>
+        <v>10710500000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5718,17 +5718,17 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
@@ -5744,24 +5744,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>100</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -5773,7 +5773,7 @@
         <v>100</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>39.29</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5788,27 +5788,27 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>50</v>
+        <v>67.86</v>
       </c>
       <c r="Q46" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>71.43000000000001</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U46" t="n">
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5817,35 +5817,35 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>3127760000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -5866,19 +5866,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>100</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>100</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5887,10 +5887,10 @@
         <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>100</v>
+        <v>72.08</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>55.64</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5905,27 +5905,27 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>50</v>
+        <v>66.94</v>
       </c>
       <c r="Q47" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>71.43000000000001</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U47" t="n">
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5934,16 +5934,16 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>3484030000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5952,17 +5952,17 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
@@ -5978,21 +5978,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>80.58</v>
       </c>
       <c r="G48" t="n">
         <v>100</v>
@@ -6004,10 +6004,10 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>100</v>
+        <v>61.15</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>70.05</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>50</v>
+        <v>58.18</v>
       </c>
       <c r="Q48" t="n">
         <v>70</v>
@@ -6031,18 +6031,18 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>71.43000000000001</v>
+        <v>83.12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U48" t="n">
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6051,35 +6051,35 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>1707230000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -6095,24 +6095,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>68.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>100</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -6121,10 +6121,10 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>37.79</v>
+        <v>100</v>
       </c>
       <c r="K49" t="n">
-        <v>38.84</v>
+        <v>32.14</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6139,27 +6139,27 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>48.44</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="Q49" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>69.2</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U49" t="n">
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6168,35 +6168,35 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>29335310000</v>
+        <v>5891850000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
@@ -6217,22 +6217,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>55.33</v>
+        <v>65.39</v>
       </c>
       <c r="H50" t="n">
-        <v>69.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="I50" t="n">
         <v>100</v>
@@ -6241,7 +6241,7 @@
         <v>100</v>
       </c>
       <c r="K50" t="n">
-        <v>10.66</v>
+        <v>30.78</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -6253,10 +6253,10 @@
         <v>100</v>
       </c>
       <c r="O50" t="n">
-        <v>69.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>54.5</v>
+        <v>66.16</v>
       </c>
       <c r="Q50" t="n">
         <v>80</v>
@@ -6265,18 +6265,18 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>68.12</v>
+        <v>82.7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U50" t="n">
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6285,35 +6285,35 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>10808640000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
@@ -6334,31 +6334,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>78.42</v>
       </c>
       <c r="G51" t="n">
-        <v>50.22</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>77.23</v>
+        <v>100</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>100</v>
+        <v>56.83</v>
       </c>
       <c r="K51" t="n">
-        <v>0.44</v>
+        <v>62.29</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -6370,10 +6370,10 @@
         <v>100</v>
       </c>
       <c r="O51" t="n">
-        <v>77.23</v>
+        <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>54.4</v>
+        <v>65.98</v>
       </c>
       <c r="Q51" t="n">
         <v>80</v>
@@ -6382,18 +6382,18 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>67.98999999999999</v>
+        <v>82.48</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U51" t="n">
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6402,35 +6402,35 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>317944150000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
@@ -6451,31 +6451,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>97.44</v>
+        <v>100</v>
       </c>
       <c r="G52" t="n">
-        <v>69.65000000000001</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>47.5</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>94.88</v>
+        <v>100</v>
       </c>
       <c r="K52" t="n">
-        <v>39.29</v>
+        <v>28.41</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6487,10 +6487,10 @@
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>47.5</v>
+        <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>53.97</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="Q52" t="n">
         <v>80</v>
@@ -6499,18 +6499,18 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>67.45999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U52" t="n">
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6519,35 +6519,35 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>10710500000</v>
+        <v>345163450000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
@@ -6563,39 +6563,39 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>64.7</v>
+        <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>82.27</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>29.4</v>
+        <v>100</v>
       </c>
       <c r="K53" t="n">
-        <v>29.05</v>
+        <v>46.8</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6604,30 +6604,30 @@
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>100</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="P53" t="n">
-        <v>45.22</v>
+        <v>73.36</v>
       </c>
       <c r="Q53" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>64.59999999999999</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U53" t="n">
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6636,35 +6636,35 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>287629890000</v>
+        <v>10808640000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
@@ -6685,31 +6685,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="G54" t="n">
-        <v>100</v>
+        <v>72.2</v>
       </c>
       <c r="H54" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>89.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="K54" t="n">
-        <v>0.54</v>
+        <v>16.6</v>
       </c>
       <c r="L54" t="n">
         <v>100</v>
@@ -6721,30 +6721,30 @@
         <v>100</v>
       </c>
       <c r="O54" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>49.74</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="Q54" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>62.17</v>
+        <v>81.47</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6753,35 +6753,35 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>13427580000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
@@ -6802,19 +6802,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>50.75</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>66.84999999999999</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,13 +6823,13 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>1.49</v>
+        <v>48.3</v>
       </c>
       <c r="K55" t="n">
-        <v>0.55</v>
+        <v>62.58</v>
       </c>
       <c r="L55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6841,27 +6841,27 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>55.33</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="Q55" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>61.48</v>
+        <v>80.95</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U55" t="n">
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6870,16 +6870,16 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>6368000000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -6888,17 +6888,17 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -6919,31 +6919,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>56.83</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>54.07</v>
+        <v>80.59</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="I56" t="n">
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>13.66</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>8.140000000000001</v>
+        <v>61.18</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6955,10 +6955,10 @@
         <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>100</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="P56" t="n">
-        <v>48.68</v>
+        <v>62.9</v>
       </c>
       <c r="Q56" t="n">
         <v>80</v>
@@ -6967,18 +6967,18 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>60.85</v>
+        <v>78.63</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U56" t="n">
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6987,35 +6987,35 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>16133240000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
@@ -7036,22 +7036,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>100</v>
+        <v>79.72</v>
       </c>
       <c r="H57" t="n">
-        <v>65</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="I57" t="n">
         <v>100</v>
@@ -7060,10 +7060,10 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>0.33</v>
+        <v>39.15</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -7072,30 +7072,30 @@
         <v>100</v>
       </c>
       <c r="O57" t="n">
-        <v>65</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="P57" t="n">
-        <v>41.32</v>
+        <v>70.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>59.02</v>
+        <v>78.55</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U57" t="n">
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7104,35 +7104,35 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>7585360000</v>
+        <v>317944150000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -7153,31 +7153,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>69.47</v>
       </c>
       <c r="G58" t="n">
-        <v>51.36</v>
+        <v>75.73</v>
       </c>
       <c r="H58" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>38.93</v>
       </c>
       <c r="K58" t="n">
-        <v>2.71</v>
+        <v>51.45</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>100</v>
       </c>
       <c r="O58" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>46.54</v>
+        <v>61.13</v>
       </c>
       <c r="Q58" t="n">
         <v>80</v>
@@ -7201,18 +7201,18 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>58.18</v>
+        <v>76.41</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U58" t="n">
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7221,35 +7221,35 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>7789580000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
@@ -7270,34 +7270,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>67.01000000000001</v>
+        <v>73.28</v>
       </c>
       <c r="G59" t="n">
-        <v>56.22</v>
+        <v>76.91</v>
       </c>
       <c r="H59" t="n">
-        <v>67.94</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>34.02</v>
+        <v>46.56</v>
       </c>
       <c r="K59" t="n">
-        <v>12.43</v>
+        <v>30.74</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -7306,30 +7306,30 @@
         <v>100</v>
       </c>
       <c r="O59" t="n">
-        <v>67.94</v>
+        <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>44.57</v>
+        <v>68.13</v>
       </c>
       <c r="Q59" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>55.72</v>
+        <v>75.7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U59" t="n">
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7338,16 +7338,16 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>5176090000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -7356,17 +7356,17 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7382,27 +7382,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
@@ -7411,10 +7411,10 @@
         <v>100</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>46.69</v>
       </c>
       <c r="L60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -7423,10 +7423,10 @@
         <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="P60" t="n">
-        <v>42.5</v>
+        <v>58.84</v>
       </c>
       <c r="Q60" t="n">
         <v>80</v>
@@ -7435,18 +7435,18 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>53.13</v>
+        <v>73.55</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U60" t="n">
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7455,16 +7455,16 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>729500000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7504,31 +7504,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>80.69</v>
+        <v>95.66</v>
       </c>
       <c r="G61" t="n">
-        <v>68.29000000000001</v>
+        <v>73.98</v>
       </c>
       <c r="H61" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>61.37</v>
+        <v>91.31</v>
       </c>
       <c r="K61" t="n">
-        <v>4.86</v>
+        <v>21.94</v>
       </c>
       <c r="L61" t="n">
         <v>100</v>
@@ -7540,10 +7540,10 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P61" t="n">
-        <v>47.68</v>
+        <v>64.33</v>
       </c>
       <c r="Q61" t="n">
         <v>90</v>
@@ -7552,18 +7552,18 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>52.98</v>
+        <v>71.48</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U61" t="n">
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7572,16 +7572,16 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>20589110000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -7590,17 +7590,17 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7621,66 +7621,66 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>54.04</v>
+        <v>85.62</v>
       </c>
       <c r="G62" t="n">
-        <v>51.27</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>8.07</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>2.53</v>
+        <v>45.83</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N62" t="n">
         <v>100</v>
       </c>
       <c r="O62" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="P62" t="n">
-        <v>37.97</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="Q62" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>47.46</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U62" t="n">
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7689,35 +7689,35 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>5671610000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7738,19 +7738,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>50.65</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>100</v>
+        <v>50.33</v>
       </c>
       <c r="H63" t="n">
         <v>65</v>
@@ -7759,10 +7759,10 @@
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>1.29</v>
+        <v>93.41</v>
       </c>
       <c r="K63" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -7777,27 +7777,27 @@
         <v>65</v>
       </c>
       <c r="P63" t="n">
-        <v>26.56</v>
+        <v>50.39</v>
       </c>
       <c r="Q63" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>37.94</v>
+        <v>62.99</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U63" t="n">
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7806,35 +7806,35 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>13489830000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7864,22 +7864,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>50.34</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>50.17</v>
+        <v>69.09</v>
       </c>
       <c r="H64" t="n">
-        <v>30.46</v>
+        <v>58.99</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>0.68</v>
+        <v>48.57</v>
       </c>
       <c r="K64" t="n">
-        <v>0.33</v>
+        <v>38.17</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -7891,10 +7891,10 @@
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>30.46</v>
+        <v>58.99</v>
       </c>
       <c r="P64" t="n">
-        <v>27.78</v>
+        <v>49.67</v>
       </c>
       <c r="Q64" t="n">
         <v>80</v>
@@ -7903,18 +7903,18 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>34.73</v>
+        <v>62.09</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U64" t="n">
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z64" t="n">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -8024,14 +8024,14 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U65" t="n">
         <v>2026</v>
       </c>
       <c r="V65" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8040,16 +8040,16 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>6722660000</v>
+        <v>6728240000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -8058,17 +8058,17 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN (695184)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU (695176)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
@@ -8089,12 +8089,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8141,14 +8141,14 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U66" t="n">
         <v>2026</v>
       </c>
       <c r="V66" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8157,16 +8157,16 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>6728240000</v>
+        <v>6314270000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -8175,17 +8175,17 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU (695176)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR (695182)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -8206,12 +8206,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>695184</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8258,14 +8258,14 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>FEBRUARI</t>
         </is>
       </c>
       <c r="U67" t="n">
         <v>2026</v>
       </c>
       <c r="V67" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -8274,16 +8274,16 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>FEBRUARI 2026</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>6314270000</v>
+        <v>6722660000</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -8292,17 +8292,17 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR (695182)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN (695184)</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -596,24 +596,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>97.55</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
@@ -625,13 +625,13 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -640,20 +640,20 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>80</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -669,16 +669,16 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>31572500000</v>
+        <v>42331120000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -687,17 +687,17 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -713,27 +713,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>99.19</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -742,7 +742,7 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>73.38</v>
       </c>
       <c r="L3" t="n">
         <v>100</v>
@@ -754,10 +754,10 @@
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>99.19</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>94.47</v>
       </c>
       <c r="Q3" t="n">
         <v>100</v>
@@ -766,18 +766,18 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>94.47</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>2026</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -786,35 +786,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>574646890000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>POLRES OKUS (665307)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -830,24 +830,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>87.48</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
@@ -859,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>80</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="Q4" t="n">
         <v>80</v>
@@ -883,18 +883,18 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>2026</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -903,35 +903,35 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>43471570000</v>
+        <v>95984080000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
@@ -947,24 +947,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>91.05</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
@@ -976,13 +976,13 @@
         <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -991,27 +991,27 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>80</v>
+        <v>92.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>92.84</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>2026</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1020,35 +1020,35 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>38902730000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
@@ -1064,24 +1064,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
@@ -1093,7 +1093,7 @@
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>60.39</v>
       </c>
       <c r="L6" t="n">
         <v>100</v>
@@ -1108,7 +1108,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>92.08</v>
       </c>
       <c r="Q6" t="n">
         <v>100</v>
@@ -1117,18 +1117,18 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>92.08</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>2026</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1137,35 +1137,35 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>1376500000</v>
+        <v>574646890000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -1186,19 +1186,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
@@ -1210,13 +1210,13 @@
         <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
@@ -1225,27 +1225,27 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>73.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>91.95</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U7" t="n">
         <v>2026</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1254,35 +1254,35 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>106528210000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -1303,19 +1303,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>86.28</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
@@ -1327,13 +1327,13 @@
         <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>58.85</v>
       </c>
       <c r="L8" t="n">
         <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
@@ -1342,27 +1342,27 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>100</v>
+        <v>81.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>90.86</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U8" t="n">
         <v>2026</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1371,35 +1371,35 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>42331120000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -1415,24 +1415,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>85.92</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -1444,10 +1444,10 @@
         <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>57.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1459,27 +1459,27 @@
         <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>80</v>
+        <v>81.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>90.61</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U9" t="n">
         <v>2026</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1488,35 +1488,35 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>10675360000</v>
+        <v>727218440000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
@@ -1532,24 +1532,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>80.91</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -1561,13 +1561,13 @@
         <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>61.82</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>100</v>
@@ -1576,27 +1576,27 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>72.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U10" t="n">
         <v>2026</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1605,35 +1605,35 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>139571760000</v>
+        <v>5127100000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -1649,24 +1649,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
@@ -1678,10 +1678,10 @@
         <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>55.11</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1693,27 +1693,27 @@
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>80</v>
+        <v>81.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>90.02</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U11" t="n">
         <v>2026</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1722,35 +1722,35 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>5127100000</v>
+        <v>139571760000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -1766,24 +1766,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>79.77</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1795,13 +1795,13 @@
         <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>59.54</v>
       </c>
       <c r="L12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>100</v>
@@ -1810,27 +1810,27 @@
         <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>100</v>
+        <v>71.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>89.89</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U12" t="n">
         <v>2026</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1839,35 +1839,35 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>128489370000</v>
+        <v>10675360000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
@@ -1883,24 +1883,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>99.83</v>
+        <v>79.45</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1912,13 +1912,13 @@
         <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>99.31999999999999</v>
+        <v>58.89</v>
       </c>
       <c r="L13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>100</v>
@@ -1927,27 +1927,27 @@
         <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>99.86</v>
+        <v>71.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>99.86</v>
+        <v>89.72</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U13" t="n">
         <v>2026</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1956,35 +1956,35 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>40484710000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -2000,24 +2000,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>99.77</v>
+        <v>87.06</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -2029,7 +2029,7 @@
         <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>99.06999999999999</v>
+        <v>48.23</v>
       </c>
       <c r="L14" t="n">
         <v>100</v>
@@ -2044,7 +2044,7 @@
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>99.81</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>100</v>
@@ -2053,18 +2053,18 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>99.81</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U14" t="n">
         <v>2026</v>
       </c>
       <c r="V14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2073,16 +2073,16 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>727218440000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2091,17 +2091,17 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
@@ -2117,24 +2117,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>99.68000000000001</v>
+        <v>83.64</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -2146,13 +2146,13 @@
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>98.70999999999999</v>
+        <v>50.93</v>
       </c>
       <c r="L15" t="n">
         <v>100</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>100</v>
@@ -2161,27 +2161,27 @@
         <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>99.73999999999999</v>
+        <v>80.19</v>
       </c>
       <c r="Q15" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>99.73999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U15" t="n">
         <v>2026</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>64847500000</v>
+        <v>819256290000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2208,17 +2208,17 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
@@ -2234,24 +2234,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>99.66</v>
+        <v>86.34</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
@@ -2263,7 +2263,7 @@
         <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>98.64</v>
+        <v>45.35</v>
       </c>
       <c r="L16" t="n">
         <v>100</v>
@@ -2278,7 +2278,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>99.73</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>100</v>
@@ -2287,18 +2287,18 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>99.73</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U16" t="n">
         <v>2026</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2307,35 +2307,35 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>105914680000</v>
+        <v>1376500000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
@@ -2351,24 +2351,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>99.51000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
@@ -2380,13 +2380,13 @@
         <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>98.03</v>
+        <v>48.71</v>
       </c>
       <c r="L17" t="n">
         <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>100</v>
@@ -2395,27 +2395,27 @@
         <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>99.61</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>99.61</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U17" t="n">
         <v>2026</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>819256290000</v>
+        <v>106528210000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2442,17 +2442,17 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
@@ -2468,24 +2468,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>98.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
         <v>100</v>
@@ -2494,10 +2494,10 @@
         <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>100</v>
+        <v>88.58</v>
       </c>
       <c r="K18" t="n">
-        <v>96.06999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2512,27 +2512,27 @@
         <v>100</v>
       </c>
       <c r="P18" t="n">
-        <v>79.20999999999999</v>
+        <v>61.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>99.02</v>
+        <v>87.75</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U18" t="n">
         <v>2026</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2541,35 +2541,35 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>39931940000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
@@ -2590,19 +2590,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>86.45</v>
       </c>
       <c r="G19" t="n">
-        <v>98.48</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
         <v>100</v>
@@ -2611,16 +2611,16 @@
         <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>100</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>93.90000000000001</v>
+        <v>67.27</v>
       </c>
       <c r="L19" t="n">
         <v>100</v>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>100</v>
@@ -2629,27 +2629,27 @@
         <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>98.78</v>
+        <v>69.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>98.78</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U19" t="n">
         <v>2026</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2658,16 +2658,16 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>95984080000</v>
+        <v>82576290000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2676,17 +2676,17 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
@@ -2702,24 +2702,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>96.8</v>
+        <v>72.72</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
@@ -2731,7 +2731,7 @@
         <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>93.59</v>
+        <v>45.44</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>78.72</v>
+        <v>69.09</v>
       </c>
       <c r="Q20" t="n">
         <v>80</v>
@@ -2755,18 +2755,18 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>98.40000000000001</v>
+        <v>86.36</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U20" t="n">
         <v>2026</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2775,35 +2775,35 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>3898470000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
@@ -2819,24 +2819,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>97.15000000000001</v>
+        <v>94.37</v>
       </c>
       <c r="G21" t="n">
-        <v>98.56</v>
+        <v>76.84</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -2845,10 +2845,10 @@
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>94.29000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>97.11</v>
+        <v>53.67</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>78.56999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="Q21" t="n">
         <v>80</v>
@@ -2872,18 +2872,18 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>98.20999999999999</v>
+        <v>86.31</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U21" t="n">
         <v>2026</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2892,35 +2892,35 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>405581540000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
@@ -2936,24 +2936,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>93.23</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>100</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
@@ -2962,16 +2962,16 @@
         <v>100</v>
       </c>
       <c r="J22" t="n">
-        <v>86.45</v>
+        <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>100</v>
+        <v>43.35</v>
       </c>
       <c r="L22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>100</v>
@@ -2980,27 +2980,27 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>97.97</v>
+        <v>68.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>97.97</v>
+        <v>85.84</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U22" t="n">
         <v>2026</v>
       </c>
       <c r="V22" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3009,35 +3009,35 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>82576290000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
@@ -3053,24 +3053,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>96.89</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
@@ -3082,10 +3082,10 @@
         <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>90.67</v>
+        <v>43.2</v>
       </c>
       <c r="L23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3097,27 +3097,27 @@
         <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>88.13</v>
+        <v>68.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>97.93000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U23" t="n">
         <v>2026</v>
       </c>
       <c r="V23" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3126,35 +3126,35 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>95645370000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
@@ -3170,24 +3170,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>90.87</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
@@ -3196,16 +3196,16 @@
         <v>100</v>
       </c>
       <c r="J24" t="n">
-        <v>81.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>100</v>
+        <v>39.85</v>
       </c>
       <c r="L24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
@@ -3214,27 +3214,27 @@
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>97.26000000000001</v>
+        <v>67.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>97.26000000000001</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U24" t="n">
         <v>2026</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3243,35 +3243,35 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>81321040000</v>
+        <v>40671640000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
@@ -3287,24 +3287,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>96</v>
+        <v>76.11</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
@@ -3316,13 +3316,13 @@
         <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>84.01000000000001</v>
+        <v>28.33</v>
       </c>
       <c r="L25" t="n">
         <v>100</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>100</v>
@@ -3331,27 +3331,27 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>96.8</v>
+        <v>75.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>96.8</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U25" t="n">
         <v>2026</v>
       </c>
       <c r="V25" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3360,35 +3360,35 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>1230000000</v>
+        <v>95645370000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
@@ -3404,24 +3404,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>93.40000000000001</v>
+        <v>75.44</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
@@ -3433,10 +3433,10 @@
         <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>86.8</v>
+        <v>26.32</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3448,27 +3448,27 @@
         <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>77.36</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>96.7</v>
+        <v>83.63</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U26" t="n">
         <v>2026</v>
       </c>
       <c r="V26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3477,35 +3477,35 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>1707230000</v>
+        <v>53136840000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
@@ -3521,27 +3521,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>66.75</v>
       </c>
       <c r="H27" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
         <v>100</v>
@@ -3550,42 +3550,42 @@
         <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>33.49</v>
       </c>
       <c r="L27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>100</v>
       </c>
       <c r="O27" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>96.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>96.5</v>
+        <v>83.37</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U27" t="n">
         <v>2026</v>
       </c>
       <c r="V27" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3594,35 +3594,35 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>729500000</v>
+        <v>65205040000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
@@ -3638,24 +3638,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>91.53</v>
+        <v>66.61</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
@@ -3667,7 +3667,7 @@
         <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>83.05</v>
+        <v>33.22</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3682,7 +3682,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>76.61</v>
+        <v>66.64</v>
       </c>
       <c r="Q28" t="n">
         <v>80</v>
@@ -3691,18 +3691,18 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>95.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U28" t="n">
         <v>2026</v>
       </c>
       <c r="V28" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3711,35 +3711,35 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>1001460000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
@@ -3755,24 +3755,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>90.97</v>
       </c>
       <c r="G29" t="n">
-        <v>90.5</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -3781,10 +3781,10 @@
         <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>100</v>
+        <v>81.94</v>
       </c>
       <c r="K29" t="n">
-        <v>81</v>
+        <v>45.63</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>76.2</v>
+        <v>66.42</v>
       </c>
       <c r="Q29" t="n">
         <v>80</v>
@@ -3808,18 +3808,18 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>95.25</v>
+        <v>83.02</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U29" t="n">
         <v>2026</v>
       </c>
       <c r="V29" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3828,16 +3828,16 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>11480750000</v>
+        <v>39404370000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3846,17 +3846,17 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
@@ -3872,24 +3872,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>96.59</v>
+        <v>85.83</v>
       </c>
       <c r="G30" t="n">
-        <v>94.33</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -3898,13 +3898,13 @@
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>93.17</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>82.98999999999999</v>
+        <v>50.35</v>
       </c>
       <c r="L30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3916,27 +3916,27 @@
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>85.56999999999999</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>95.08</v>
+        <v>82.27</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U30" t="n">
         <v>2026</v>
       </c>
       <c r="V30" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3945,35 +3945,35 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>9098870000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
@@ -3989,24 +3989,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>83.56</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>60.11</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
@@ -4015,16 +4015,16 @@
         <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>67.12</v>
+        <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>20.22</v>
       </c>
       <c r="L31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>100</v>
@@ -4033,27 +4033,27 @@
         <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>95.06999999999999</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>95.06999999999999</v>
+        <v>80.06</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U31" t="n">
         <v>2026</v>
       </c>
       <c r="V31" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4062,35 +4062,35 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>31225620000</v>
+        <v>1001460000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
@@ -4111,19 +4111,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>88.88</v>
+        <v>59.74</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -4135,7 +4135,7 @@
         <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>77.76000000000001</v>
+        <v>19.48</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>75.55</v>
+        <v>63.9</v>
       </c>
       <c r="Q32" t="n">
         <v>80</v>
@@ -4159,18 +4159,18 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>94.44</v>
+        <v>79.87</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U32" t="n">
         <v>2026</v>
       </c>
       <c r="V32" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4179,16 +4179,16 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>3127760000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4197,17 +4197,17 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
@@ -4223,24 +4223,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>88.7</v>
+        <v>55.76</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -4252,7 +4252,7 @@
         <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>77.40000000000001</v>
+        <v>11.52</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4267,7 +4267,7 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>75.48</v>
+        <v>62.3</v>
       </c>
       <c r="Q33" t="n">
         <v>80</v>
@@ -4276,18 +4276,18 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>94.34999999999999</v>
+        <v>77.88</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U33" t="n">
         <v>2026</v>
       </c>
       <c r="V33" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4296,35 +4296,35 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>3484030000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>88</v>
+        <v>68.25</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4366,10 +4366,10 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>100</v>
+        <v>63.48</v>
       </c>
       <c r="K34" t="n">
-        <v>76</v>
+        <v>36.5</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>75.2</v>
+        <v>61.82</v>
       </c>
       <c r="Q34" t="n">
         <v>80</v>
@@ -4393,18 +4393,18 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>94</v>
+        <v>77.28</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U34" t="n">
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4413,16 +4413,16 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>74397990000</v>
+        <v>81321040000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -4431,17 +4431,17 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
@@ -4457,24 +4457,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>85.89</v>
+        <v>52.06</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4486,7 +4486,7 @@
         <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>71.77</v>
+        <v>4.11</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>74.34999999999999</v>
+        <v>60.82</v>
       </c>
       <c r="Q35" t="n">
         <v>80</v>
@@ -4510,18 +4510,18 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>92.94</v>
+        <v>76.03</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U35" t="n">
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4530,35 +4530,35 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>40671640000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
@@ -4579,19 +4579,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>83.7</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4600,10 +4600,10 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>100</v>
+        <v>51.01</v>
       </c>
       <c r="K36" t="n">
-        <v>67.40000000000001</v>
+        <v>40.51</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>73.48</v>
+        <v>60.75</v>
       </c>
       <c r="Q36" t="n">
         <v>80</v>
@@ -4627,18 +4627,18 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>91.84999999999999</v>
+        <v>75.94</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U36" t="n">
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4647,16 +4647,16 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>970430000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4665,17 +4665,17 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
@@ -4691,24 +4691,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>84.45</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>93.86</v>
+        <v>50.62</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -4717,10 +4717,10 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>68.89</v>
+        <v>100</v>
       </c>
       <c r="K37" t="n">
-        <v>87.70999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>72.88</v>
+        <v>60.25</v>
       </c>
       <c r="Q37" t="n">
         <v>80</v>
@@ -4744,18 +4744,18 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>91.09</v>
+        <v>75.31</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U37" t="n">
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4764,35 +4764,35 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>29335310000</v>
+        <v>5891850000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
@@ -4808,24 +4808,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>92.91</v>
+        <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>87.48999999999999</v>
+        <v>50.19</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4834,10 +4834,10 @@
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>85.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>74.97</v>
+        <v>0.37</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>72.87</v>
+        <v>60.07</v>
       </c>
       <c r="Q38" t="n">
         <v>80</v>
@@ -4861,18 +4861,18 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>91.08</v>
+        <v>75.09</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U38" t="n">
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4881,35 +4881,35 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>50054370000</v>
+        <v>345163450000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
@@ -4925,24 +4925,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>86.09999999999999</v>
+        <v>50.04</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
@@ -4954,13 +4954,13 @@
         <v>100</v>
       </c>
       <c r="K39" t="n">
-        <v>58.31</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
@@ -4969,27 +4969,27 @@
         <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>81.66</v>
+        <v>60.01</v>
       </c>
       <c r="Q39" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>90.73999999999999</v>
+        <v>75.02</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U39" t="n">
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4998,16 +4998,16 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>65205040000</v>
+        <v>475588950000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -5016,17 +5016,17 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
@@ -5042,24 +5042,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>95.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>84.12</v>
+        <v>50</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -5068,10 +5068,10 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>90.97</v>
+        <v>100</v>
       </c>
       <c r="K40" t="n">
-        <v>68.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -5086,7 +5086,7 @@
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>72.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="Q40" t="n">
         <v>80</v>
@@ -5095,18 +5095,18 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>90.37</v>
+        <v>75</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U40" t="n">
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5115,35 +5115,35 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>39404370000</v>
+        <v>970430000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
@@ -5159,24 +5159,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>100</v>
       </c>
       <c r="G41" t="n">
-        <v>79.17</v>
+        <v>100</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
@@ -5188,10 +5188,10 @@
         <v>100</v>
       </c>
       <c r="K41" t="n">
-        <v>58.34</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5203,7 +5203,7 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>71.67</v>
+        <v>60</v>
       </c>
       <c r="Q41" t="n">
         <v>80</v>
@@ -5212,18 +5212,18 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>89.59</v>
+        <v>75</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U41" t="n">
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5232,35 +5232,35 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>475588950000</v>
+        <v>1230000000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
@@ -5276,24 +5276,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
+        <v>87.98</v>
       </c>
       <c r="G42" t="n">
-        <v>84.01000000000001</v>
+        <v>55.09</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5302,13 +5302,13 @@
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>100</v>
+        <v>75.95</v>
       </c>
       <c r="K42" t="n">
-        <v>52.02</v>
+        <v>10.18</v>
       </c>
       <c r="L42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5320,27 +5320,27 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>80.40000000000001</v>
+        <v>58.43</v>
       </c>
       <c r="Q42" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>89.34</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U42" t="n">
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5349,16 +5349,16 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>53136840000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -5367,17 +5367,17 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
@@ -5393,24 +5393,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>93.77</v>
+        <v>67.13</v>
       </c>
       <c r="G43" t="n">
-        <v>82.14</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -5419,10 +5419,10 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>87.53</v>
+        <v>34.25</v>
       </c>
       <c r="K43" t="n">
-        <v>64.27</v>
+        <v>41.01</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>70.98</v>
+        <v>58.34</v>
       </c>
       <c r="Q43" t="n">
         <v>80</v>
@@ -5446,18 +5446,18 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>88.73</v>
+        <v>72.92</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U43" t="n">
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5466,16 +5466,16 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>15177700000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5484,17 +5484,17 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
@@ -5515,19 +5515,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>77.25</v>
+        <v>100</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5539,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>54.49</v>
+        <v>0.36</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5554,27 +5554,27 @@
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>70.90000000000001</v>
+        <v>50.07</v>
       </c>
       <c r="Q44" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>88.62</v>
+        <v>71.53</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U44" t="n">
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5583,35 +5583,35 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>1731600000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
@@ -5632,22 +5632,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>100</v>
       </c>
       <c r="G45" t="n">
-        <v>96.81</v>
+        <v>100</v>
       </c>
       <c r="H45" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I45" t="n">
         <v>100</v>
@@ -5656,7 +5656,7 @@
         <v>100</v>
       </c>
       <c r="K45" t="n">
-        <v>93.61</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5668,30 +5668,30 @@
         <v>100</v>
       </c>
       <c r="O45" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>69.97</v>
+        <v>50</v>
       </c>
       <c r="Q45" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>87.47</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U45" t="n">
         <v>2026</v>
       </c>
       <c r="V45" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5700,16 +5700,16 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>10710500000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5718,17 +5718,17 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
@@ -5744,24 +5744,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>69.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -5773,7 +5773,7 @@
         <v>100</v>
       </c>
       <c r="K46" t="n">
-        <v>39.29</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5788,27 +5788,27 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>67.86</v>
+        <v>50</v>
       </c>
       <c r="Q46" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>84.81999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U46" t="n">
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5817,35 +5817,35 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>114852670000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -5866,19 +5866,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>86.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>77.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5887,10 +5887,10 @@
         <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>72.08</v>
+        <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>55.64</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5905,27 +5905,27 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>66.94</v>
+        <v>50</v>
       </c>
       <c r="Q47" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>83.68000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U47" t="n">
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5934,16 +5934,16 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>9731020000</v>
+        <v>3484030000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5952,17 +5952,17 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
@@ -5978,21 +5978,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>80.58</v>
+        <v>100</v>
       </c>
       <c r="G48" t="n">
         <v>100</v>
@@ -6004,10 +6004,10 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>61.15</v>
+        <v>100</v>
       </c>
       <c r="K48" t="n">
-        <v>70.05</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>58.18</v>
+        <v>50</v>
       </c>
       <c r="Q48" t="n">
         <v>70</v>
@@ -6031,18 +6031,18 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>83.12</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U48" t="n">
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6051,35 +6051,35 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>287629890000</v>
+        <v>1707230000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -6095,24 +6095,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>100</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>66.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -6121,10 +6121,10 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>100</v>
+        <v>37.79</v>
       </c>
       <c r="K49" t="n">
-        <v>32.14</v>
+        <v>38.84</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6139,27 +6139,27 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>66.43000000000001</v>
+        <v>48.44</v>
       </c>
       <c r="Q49" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>83.04000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U49" t="n">
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6168,35 +6168,35 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>5891850000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
@@ -6217,22 +6217,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>65.39</v>
+        <v>55.33</v>
       </c>
       <c r="H50" t="n">
-        <v>100</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="I50" t="n">
         <v>100</v>
@@ -6241,7 +6241,7 @@
         <v>100</v>
       </c>
       <c r="K50" t="n">
-        <v>30.78</v>
+        <v>10.66</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -6253,10 +6253,10 @@
         <v>100</v>
       </c>
       <c r="O50" t="n">
-        <v>100</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="P50" t="n">
-        <v>66.16</v>
+        <v>54.5</v>
       </c>
       <c r="Q50" t="n">
         <v>80</v>
@@ -6265,18 +6265,18 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>82.7</v>
+        <v>68.12</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U50" t="n">
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6285,35 +6285,35 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>15707450000</v>
+        <v>10808640000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
@@ -6334,31 +6334,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>78.42</v>
+        <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>81.15000000000001</v>
+        <v>50.22</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>77.23</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>56.83</v>
+        <v>100</v>
       </c>
       <c r="K51" t="n">
-        <v>62.29</v>
+        <v>0.44</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -6370,10 +6370,10 @@
         <v>100</v>
       </c>
       <c r="O51" t="n">
-        <v>100</v>
+        <v>77.23</v>
       </c>
       <c r="P51" t="n">
-        <v>65.98</v>
+        <v>54.4</v>
       </c>
       <c r="Q51" t="n">
         <v>80</v>
@@ -6382,18 +6382,18 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>82.48</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U51" t="n">
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6402,35 +6402,35 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>16133240000</v>
+        <v>317944150000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
@@ -6451,31 +6451,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>97.44</v>
       </c>
       <c r="G52" t="n">
-        <v>64.20999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>47.5</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>100</v>
+        <v>94.88</v>
       </c>
       <c r="K52" t="n">
-        <v>28.41</v>
+        <v>39.29</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6487,10 +6487,10 @@
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>100</v>
+        <v>47.5</v>
       </c>
       <c r="P52" t="n">
-        <v>65.68000000000001</v>
+        <v>53.97</v>
       </c>
       <c r="Q52" t="n">
         <v>80</v>
@@ -6499,18 +6499,18 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>82.09999999999999</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U52" t="n">
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6519,35 +6519,35 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>345163450000</v>
+        <v>10710500000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
@@ -6563,39 +6563,39 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>64.7</v>
       </c>
       <c r="G53" t="n">
-        <v>82.27</v>
+        <v>100</v>
       </c>
       <c r="H53" t="n">
-        <v>75.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>29.4</v>
       </c>
       <c r="K53" t="n">
-        <v>46.8</v>
+        <v>29.05</v>
       </c>
       <c r="L53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6604,30 +6604,30 @@
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>75.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>73.36</v>
+        <v>45.22</v>
       </c>
       <c r="Q53" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>81.51000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U53" t="n">
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6636,35 +6636,35 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>10808640000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
@@ -6685,31 +6685,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>94.59</v>
       </c>
       <c r="G54" t="n">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I54" t="n">
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>100</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>16.6</v>
+        <v>0.54</v>
       </c>
       <c r="L54" t="n">
         <v>100</v>
@@ -6721,30 +6721,30 @@
         <v>100</v>
       </c>
       <c r="O54" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="P54" t="n">
-        <v>73.31999999999999</v>
+        <v>49.74</v>
       </c>
       <c r="Q54" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>81.47</v>
+        <v>62.17</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6753,35 +6753,35 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>9346940000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
@@ -6802,19 +6802,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>74.15000000000001</v>
+        <v>50.75</v>
       </c>
       <c r="G55" t="n">
-        <v>81.29000000000001</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,13 +6823,13 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>48.3</v>
+        <v>1.49</v>
       </c>
       <c r="K55" t="n">
-        <v>62.58</v>
+        <v>0.55</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6841,27 +6841,27 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>64.76000000000001</v>
+        <v>55.33</v>
       </c>
       <c r="Q55" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>80.95</v>
+        <v>61.48</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U55" t="n">
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6870,16 +6870,16 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>5671610000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -6888,17 +6888,17 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -6919,31 +6919,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>83.51000000000001</v>
+        <v>56.83</v>
       </c>
       <c r="G56" t="n">
-        <v>80.59</v>
+        <v>54.07</v>
       </c>
       <c r="H56" t="n">
-        <v>82.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>67.01000000000001</v>
+        <v>13.66</v>
       </c>
       <c r="K56" t="n">
-        <v>61.18</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6955,10 +6955,10 @@
         <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>82.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>62.9</v>
+        <v>48.68</v>
       </c>
       <c r="Q56" t="n">
         <v>80</v>
@@ -6967,18 +6967,18 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>78.63</v>
+        <v>60.85</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U56" t="n">
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6987,35 +6987,35 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>5176090000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
@@ -7036,22 +7036,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>79.72</v>
+        <v>100</v>
       </c>
       <c r="H57" t="n">
-        <v>71.45999999999999</v>
+        <v>65</v>
       </c>
       <c r="I57" t="n">
         <v>100</v>
@@ -7060,10 +7060,10 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>39.15</v>
+        <v>0.33</v>
       </c>
       <c r="L57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -7072,30 +7072,30 @@
         <v>100</v>
       </c>
       <c r="O57" t="n">
-        <v>71.45999999999999</v>
+        <v>65</v>
       </c>
       <c r="P57" t="n">
-        <v>70.7</v>
+        <v>41.32</v>
       </c>
       <c r="Q57" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>78.55</v>
+        <v>59.02</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U57" t="n">
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7104,35 +7104,35 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>317944150000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -7153,31 +7153,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>69.47</v>
+        <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>75.73</v>
+        <v>51.36</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="I58" t="n">
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>38.93</v>
+        <v>100</v>
       </c>
       <c r="K58" t="n">
-        <v>51.45</v>
+        <v>2.71</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>100</v>
       </c>
       <c r="O58" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="P58" t="n">
-        <v>61.13</v>
+        <v>46.54</v>
       </c>
       <c r="Q58" t="n">
         <v>80</v>
@@ -7201,18 +7201,18 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>76.41</v>
+        <v>58.18</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U58" t="n">
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7221,35 +7221,35 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>13489830000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
@@ -7270,34 +7270,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>73.28</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>76.91</v>
+        <v>56.22</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>67.94</v>
       </c>
       <c r="I59" t="n">
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>46.56</v>
+        <v>34.02</v>
       </c>
       <c r="K59" t="n">
-        <v>30.74</v>
+        <v>12.43</v>
       </c>
       <c r="L59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -7306,30 +7306,30 @@
         <v>100</v>
       </c>
       <c r="O59" t="n">
-        <v>100</v>
+        <v>67.94</v>
       </c>
       <c r="P59" t="n">
-        <v>68.13</v>
+        <v>44.57</v>
       </c>
       <c r="Q59" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>75.7</v>
+        <v>55.72</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U59" t="n">
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7338,16 +7338,16 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>6368000000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -7356,17 +7356,17 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7382,27 +7382,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>73.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="H60" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
@@ -7411,10 +7411,10 @@
         <v>100</v>
       </c>
       <c r="K60" t="n">
-        <v>46.69</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -7423,10 +7423,10 @@
         <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="P60" t="n">
-        <v>58.84</v>
+        <v>42.5</v>
       </c>
       <c r="Q60" t="n">
         <v>80</v>
@@ -7435,18 +7435,18 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>73.55</v>
+        <v>53.13</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U60" t="n">
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7455,16 +7455,16 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>7789580000</v>
+        <v>729500000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7504,31 +7504,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>95.66</v>
+        <v>80.69</v>
       </c>
       <c r="G61" t="n">
-        <v>73.98</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>91.31</v>
+        <v>61.37</v>
       </c>
       <c r="K61" t="n">
-        <v>21.94</v>
+        <v>4.86</v>
       </c>
       <c r="L61" t="n">
         <v>100</v>
@@ -7540,10 +7540,10 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="P61" t="n">
-        <v>64.33</v>
+        <v>47.68</v>
       </c>
       <c r="Q61" t="n">
         <v>90</v>
@@ -7552,18 +7552,18 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>71.48</v>
+        <v>52.98</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U61" t="n">
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7572,16 +7572,16 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>13427580000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -7590,17 +7590,17 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7621,66 +7621,66 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>85.62</v>
+        <v>54.04</v>
       </c>
       <c r="G62" t="n">
-        <v>86.45999999999999</v>
+        <v>51.27</v>
       </c>
       <c r="H62" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>71.23999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="K62" t="n">
-        <v>45.83</v>
+        <v>2.53</v>
       </c>
       <c r="L62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>100</v>
       </c>
       <c r="O62" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P62" t="n">
-        <v>67.34999999999999</v>
+        <v>37.97</v>
       </c>
       <c r="Q62" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>67.34999999999999</v>
+        <v>47.46</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U62" t="n">
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7689,35 +7689,35 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>20589110000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7738,19 +7738,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>96.70999999999999</v>
+        <v>50.65</v>
       </c>
       <c r="G63" t="n">
-        <v>50.33</v>
+        <v>100</v>
       </c>
       <c r="H63" t="n">
         <v>65</v>
@@ -7759,10 +7759,10 @@
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>93.41</v>
+        <v>1.29</v>
       </c>
       <c r="K63" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -7777,27 +7777,27 @@
         <v>65</v>
       </c>
       <c r="P63" t="n">
-        <v>50.39</v>
+        <v>26.56</v>
       </c>
       <c r="Q63" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>62.99</v>
+        <v>37.94</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U63" t="n">
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7806,35 +7806,35 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>7585360000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7864,22 +7864,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>74.29000000000001</v>
+        <v>50.34</v>
       </c>
       <c r="G64" t="n">
-        <v>69.09</v>
+        <v>50.17</v>
       </c>
       <c r="H64" t="n">
-        <v>58.99</v>
+        <v>30.46</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>48.57</v>
+        <v>0.68</v>
       </c>
       <c r="K64" t="n">
-        <v>38.17</v>
+        <v>0.33</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -7891,10 +7891,10 @@
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>58.99</v>
+        <v>30.46</v>
       </c>
       <c r="P64" t="n">
-        <v>49.67</v>
+        <v>27.78</v>
       </c>
       <c r="Q64" t="n">
         <v>80</v>
@@ -7903,18 +7903,18 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>62.09</v>
+        <v>34.73</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U64" t="n">
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z64" t="n">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695184</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -8024,14 +8024,14 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U65" t="n">
         <v>2026</v>
       </c>
       <c r="V65" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8040,16 +8040,16 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>6728240000</v>
+        <v>6722660000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -8058,17 +8058,17 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU (695176)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN (695184)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
@@ -8089,12 +8089,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8141,14 +8141,14 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U66" t="n">
         <v>2026</v>
       </c>
       <c r="V66" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8157,16 +8157,16 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>6314270000</v>
+        <v>6728240000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -8175,17 +8175,17 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR (695182)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU (695176)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -8206,12 +8206,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8258,14 +8258,14 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U67" t="n">
         <v>2026</v>
       </c>
       <c r="V67" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -8274,16 +8274,16 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>6722660000</v>
+        <v>6314270000</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -8292,17 +8292,17 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN (695184)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR (695182)</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -596,17 +596,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -628,10 +628,10 @@
         <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -640,10 +640,10 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -669,42 +669,42 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>31572500000</v>
+        <v>95984080000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -713,17 +713,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -745,10 +745,10 @@
         <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
@@ -757,10 +757,10 @@
         <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -786,42 +786,42 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>574646890000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>POLRES OKUS (665307)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -830,17 +830,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -903,16 +903,16 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>43471570000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -921,24 +921,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -947,17 +947,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -979,10 +979,10 @@
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -991,10 +991,10 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -1020,42 +1020,42 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>38902730000</v>
+        <v>139571760000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1137,42 +1137,42 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>1376500000</v>
+        <v>106528210000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -1254,16 +1254,16 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>106528210000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1272,24 +1272,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,17 +1298,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U8" t="n">
@@ -1371,42 +1371,42 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>42331120000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1415,17 +1415,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U9" t="n">
@@ -1488,42 +1488,42 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>10675360000</v>
+        <v>40671640000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1532,17 +1532,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1564,10 +1564,10 @@
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>100</v>
@@ -1576,10 +1576,10 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U10" t="n">
@@ -1605,42 +1605,42 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>139571760000</v>
+        <v>3484030000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1649,17 +1649,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U11" t="n">
@@ -1722,16 +1722,16 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>5127100000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1740,24 +1740,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1801,7 +1801,7 @@
         <v>100</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>100</v>
@@ -1810,10 +1810,10 @@
         <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U12" t="n">
@@ -1839,16 +1839,16 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>128489370000</v>
+        <v>475588950000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1857,24 +1857,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1883,24 +1883,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>99.83</v>
+        <v>100</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1912,7 +1912,7 @@
         <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>99.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
         <v>100</v>
@@ -1927,7 +1927,7 @@
         <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>99.86</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
         <v>100</v>
@@ -1936,18 +1936,18 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>99.86</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U13" t="n">
         <v>2026</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1956,42 +1956,42 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>40484710000</v>
+        <v>574646890000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2005,19 +2005,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>99.77</v>
+        <v>100</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -2029,7 +2029,7 @@
         <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>99.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="L14" t="n">
         <v>100</v>
@@ -2044,7 +2044,7 @@
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>99.81</v>
+        <v>100</v>
       </c>
       <c r="Q14" t="n">
         <v>100</v>
@@ -2053,18 +2053,18 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>99.81</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U14" t="n">
         <v>2026</v>
       </c>
       <c r="V14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2073,16 +2073,16 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>727218440000</v>
+        <v>819256290000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2091,24 +2091,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2117,24 +2117,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>99.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -2146,13 +2146,13 @@
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>98.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>100</v>
@@ -2161,27 +2161,27 @@
         <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>99.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>99.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U15" t="n">
         <v>2026</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2190,42 +2190,42 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>64847500000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2234,24 +2234,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>99.66</v>
+        <v>100</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
@@ -2263,13 +2263,13 @@
         <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>98.64</v>
+        <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>100</v>
@@ -2278,27 +2278,27 @@
         <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>99.73</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>99.73</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U16" t="n">
         <v>2026</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2307,42 +2307,42 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>105914680000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2356,19 +2356,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>99.51000000000001</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
@@ -2380,7 +2380,7 @@
         <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>98.03</v>
+        <v>100</v>
       </c>
       <c r="L17" t="n">
         <v>100</v>
@@ -2395,7 +2395,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>99.61</v>
+        <v>100</v>
       </c>
       <c r="Q17" t="n">
         <v>100</v>
@@ -2404,18 +2404,18 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>99.61</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U17" t="n">
         <v>2026</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>819256290000</v>
+        <v>727218440000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2442,17 +2442,17 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
@@ -2468,24 +2468,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>98.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
         <v>100</v>
@@ -2497,7 +2497,7 @@
         <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>96.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>100</v>
       </c>
       <c r="P18" t="n">
-        <v>79.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q18" t="n">
         <v>80</v>
@@ -2521,18 +2521,18 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>99.02</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U18" t="n">
         <v>2026</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2541,42 +2541,42 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>39931940000</v>
+        <v>970430000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2585,24 +2585,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>98.48</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
         <v>100</v>
@@ -2614,7 +2614,7 @@
         <v>100</v>
       </c>
       <c r="K19" t="n">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="L19" t="n">
         <v>100</v>
@@ -2629,7 +2629,7 @@
         <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>98.78</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="n">
         <v>100</v>
@@ -2638,18 +2638,18 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>98.78</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U19" t="n">
         <v>2026</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2658,16 +2658,16 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>95984080000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2676,24 +2676,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2707,19 +2707,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
@@ -2731,7 +2731,7 @@
         <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>93.59</v>
+        <v>100</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>78.72</v>
+        <v>80</v>
       </c>
       <c r="Q20" t="n">
         <v>80</v>
@@ -2755,18 +2755,18 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U20" t="n">
         <v>2026</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2775,16 +2775,16 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>3898470000</v>
+        <v>1001460000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2793,24 +2793,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2819,24 +2819,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>97.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>98.56</v>
+        <v>100</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -2845,10 +2845,10 @@
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>97.11</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q21" t="n">
         <v>80</v>
@@ -2872,18 +2872,18 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>98.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U21" t="n">
         <v>2026</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2892,42 +2892,42 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>405581540000</v>
+        <v>10710500000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>93.23</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
         <v>100</v>
@@ -2962,7 +2962,7 @@
         <v>100</v>
       </c>
       <c r="J22" t="n">
-        <v>86.45</v>
+        <v>100</v>
       </c>
       <c r="K22" t="n">
         <v>100</v>
@@ -2971,7 +2971,7 @@
         <v>100</v>
       </c>
       <c r="M22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>100</v>
@@ -2980,27 +2980,27 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>97.97</v>
+        <v>90</v>
       </c>
       <c r="Q22" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>97.97</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U22" t="n">
         <v>2026</v>
       </c>
       <c r="V22" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3009,16 +3009,16 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>82576290000</v>
+        <v>317944150000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3027,24 +3027,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3053,24 +3053,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>96.89</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
@@ -3082,10 +3082,10 @@
         <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>90.67</v>
+        <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3097,27 +3097,27 @@
         <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>88.13</v>
+        <v>80</v>
       </c>
       <c r="Q23" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>97.93000000000001</v>
+        <v>100</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U23" t="n">
         <v>2026</v>
       </c>
       <c r="V23" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3126,42 +3126,42 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>95645370000</v>
+        <v>5891850000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>90.87</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
         <v>100</v>
@@ -3196,7 +3196,7 @@
         <v>100</v>
       </c>
       <c r="J24" t="n">
-        <v>81.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="K24" t="n">
         <v>100</v>
@@ -3214,7 +3214,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>97.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q24" t="n">
         <v>100</v>
@@ -3223,18 +3223,18 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>97.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U24" t="n">
         <v>2026</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3243,42 +3243,42 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>81321040000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3287,24 +3287,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
@@ -3316,13 +3316,13 @@
         <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>84.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="L25" t="n">
         <v>100</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>100</v>
@@ -3331,27 +3331,27 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>96.8</v>
+        <v>90</v>
       </c>
       <c r="Q25" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U25" t="n">
         <v>2026</v>
       </c>
       <c r="V25" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3360,42 +3360,42 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>1230000000</v>
+        <v>53136840000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3404,24 +3404,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>93.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
@@ -3433,13 +3433,13 @@
         <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>86.8</v>
+        <v>100</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N26" t="n">
         <v>100</v>
@@ -3448,27 +3448,27 @@
         <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>77.36</v>
+        <v>100</v>
       </c>
       <c r="Q26" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U26" t="n">
         <v>2026</v>
       </c>
       <c r="V26" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3477,16 +3477,16 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>1707230000</v>
+        <v>729500000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3495,24 +3495,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -3541,7 +3541,7 @@
         <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
         <v>100</v>
@@ -3562,10 +3562,10 @@
         <v>100</v>
       </c>
       <c r="O27" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>96.5</v>
+        <v>100</v>
       </c>
       <c r="Q27" t="n">
         <v>100</v>
@@ -3574,18 +3574,18 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>96.5</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U27" t="n">
         <v>2026</v>
       </c>
       <c r="V27" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3594,16 +3594,16 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>729500000</v>
+        <v>1376500000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3612,24 +3612,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3638,24 +3638,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>91.53</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
@@ -3667,13 +3667,13 @@
         <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>83.05</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
@@ -3682,27 +3682,27 @@
         <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>76.61</v>
+        <v>100</v>
       </c>
       <c r="Q28" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>95.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U28" t="n">
         <v>2026</v>
       </c>
       <c r="V28" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3711,16 +3711,16 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>1001460000</v>
+        <v>1230000000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3729,24 +3729,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3755,24 +3755,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>90.5</v>
+        <v>100</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -3784,13 +3784,13 @@
         <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29" t="n">
         <v>100</v>
@@ -3799,27 +3799,27 @@
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>76.2</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>95.25</v>
+        <v>100</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U29" t="n">
         <v>2026</v>
       </c>
       <c r="V29" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3828,16 +3828,16 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>11480750000</v>
+        <v>42331120000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3846,24 +3846,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3872,24 +3872,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>96.59</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>94.33</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -3898,16 +3898,16 @@
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>93.17</v>
+        <v>100</v>
       </c>
       <c r="K30" t="n">
-        <v>82.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="L30" t="n">
         <v>100</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30" t="n">
         <v>100</v>
@@ -3916,27 +3916,27 @@
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>85.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q30" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>95.08</v>
+        <v>100</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U30" t="n">
         <v>2026</v>
       </c>
       <c r="V30" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3945,42 +3945,42 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>9098870000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3989,21 +3989,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>83.56</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -4015,16 +4015,16 @@
         <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>67.12</v>
+        <v>100</v>
       </c>
       <c r="K31" t="n">
         <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>100</v>
@@ -4033,27 +4033,27 @@
         <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>95.06999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q31" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>95.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U31" t="n">
         <v>2026</v>
       </c>
       <c r="V31" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4062,42 +4062,42 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>31225620000</v>
+        <v>10675360000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4123,7 +4123,7 @@
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>88.88</v>
+        <v>100</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -4135,7 +4135,7 @@
         <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>77.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>75.55</v>
+        <v>80</v>
       </c>
       <c r="Q32" t="n">
         <v>80</v>
@@ -4159,18 +4159,18 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U32" t="n">
         <v>2026</v>
       </c>
       <c r="V32" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4179,16 +4179,16 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>3127760000</v>
+        <v>1707230000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -4214,7 +4214,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4223,24 +4223,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -4252,7 +4252,7 @@
         <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>77.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4267,7 +4267,7 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>75.48</v>
+        <v>80</v>
       </c>
       <c r="Q33" t="n">
         <v>80</v>
@@ -4276,18 +4276,18 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>94.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U33" t="n">
         <v>2026</v>
       </c>
       <c r="V33" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4296,16 +4296,16 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>3484030000</v>
+        <v>5127100000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -4314,17 +4314,17 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>88</v>
+        <v>99.95</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4369,7 +4369,7 @@
         <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>76</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>75.2</v>
+        <v>79.98</v>
       </c>
       <c r="Q34" t="n">
         <v>80</v>
@@ -4393,18 +4393,18 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>94</v>
+        <v>99.98</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U34" t="n">
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4413,35 +4413,35 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>74397990000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
@@ -4457,24 +4457,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>85.89</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4486,7 +4486,7 @@
         <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>71.77</v>
+        <v>99.86</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>74.34999999999999</v>
+        <v>79.97</v>
       </c>
       <c r="Q35" t="n">
         <v>80</v>
@@ -4510,18 +4510,18 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>92.94</v>
+        <v>99.97</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U35" t="n">
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4530,35 +4530,35 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>40671640000</v>
+        <v>345163450000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
@@ -4574,24 +4574,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>83.7</v>
+        <v>99.83</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4603,13 +4603,13 @@
         <v>100</v>
       </c>
       <c r="K36" t="n">
-        <v>67.40000000000001</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N36" t="n">
         <v>100</v>
@@ -4618,27 +4618,27 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>73.48</v>
+        <v>99.86</v>
       </c>
       <c r="Q36" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>91.84999999999999</v>
+        <v>99.86</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U36" t="n">
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4647,35 +4647,35 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>970430000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
@@ -4691,24 +4691,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>84.45</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>93.86</v>
+        <v>100</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -4717,10 +4717,10 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>68.89</v>
+        <v>93.98</v>
       </c>
       <c r="K37" t="n">
-        <v>87.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>72.88</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="Q37" t="n">
         <v>80</v>
@@ -4744,18 +4744,18 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>91.09</v>
+        <v>98.87</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U37" t="n">
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4764,16 +4764,16 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>29335310000</v>
+        <v>39404370000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4782,17 +4782,17 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
@@ -4808,24 +4808,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>92.91</v>
+        <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>87.48999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4834,13 +4834,13 @@
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>85.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>74.97</v>
+        <v>94.89</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4852,27 +4852,27 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>72.87</v>
+        <v>88.98</v>
       </c>
       <c r="Q38" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>91.08</v>
+        <v>98.86</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U38" t="n">
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4881,35 +4881,35 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>50054370000</v>
+        <v>95645370000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
@@ -4925,39 +4925,39 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>96.02</v>
       </c>
       <c r="G39" t="n">
-        <v>86.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I39" t="n">
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>100</v>
+        <v>92.03</v>
       </c>
       <c r="K39" t="n">
-        <v>58.31</v>
+        <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39" t="n">
         <v>100</v>
@@ -4966,30 +4966,30 @@
         <v>100</v>
       </c>
       <c r="O39" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="P39" t="n">
-        <v>81.66</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="Q39" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>90.73999999999999</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U39" t="n">
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4998,35 +4998,35 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>65205040000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
@@ -5042,24 +5042,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>95.48999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>84.12</v>
+        <v>100</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -5071,13 +5071,13 @@
         <v>90.97</v>
       </c>
       <c r="K40" t="n">
-        <v>68.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -5086,27 +5086,27 @@
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>72.29000000000001</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="Q40" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>90.37</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U40" t="n">
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5115,35 +5115,35 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>39404370000</v>
+        <v>82576290000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
@@ -5164,19 +5164,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
+        <v>95.94</v>
       </c>
       <c r="G41" t="n">
-        <v>79.17</v>
+        <v>100</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
@@ -5185,13 +5185,13 @@
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>100</v>
+        <v>91.87</v>
       </c>
       <c r="K41" t="n">
-        <v>58.34</v>
+        <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5203,27 +5203,27 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>71.67</v>
+        <v>88.78</v>
       </c>
       <c r="Q41" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>89.59</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U41" t="n">
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5232,35 +5232,35 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>475588950000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
@@ -5276,24 +5276,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>84.01000000000001</v>
+        <v>97.13</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5305,10 +5305,10 @@
         <v>100</v>
       </c>
       <c r="K42" t="n">
-        <v>52.02</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5320,27 +5320,27 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>80.40000000000001</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>89.34</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U42" t="n">
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5349,35 +5349,35 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>53136840000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>93.77</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>82.14</v>
+        <v>100</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -5419,10 +5419,10 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>87.53</v>
+        <v>91.63</v>
       </c>
       <c r="K43" t="n">
-        <v>64.27</v>
+        <v>100</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>70.98</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="Q43" t="n">
         <v>80</v>
@@ -5446,18 +5446,18 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>88.73</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U43" t="n">
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z43" t="n">
@@ -5515,19 +5515,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>77.25</v>
+        <v>96.8</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5539,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>54.49</v>
+        <v>93.59</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5554,7 +5554,7 @@
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>70.90000000000001</v>
+        <v>78.72</v>
       </c>
       <c r="Q44" t="n">
         <v>80</v>
@@ -5563,18 +5563,18 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>88.62</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U44" t="n">
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5583,16 +5583,16 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>1731600000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -5601,17 +5601,17 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
@@ -5627,71 +5627,71 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>93.92</v>
       </c>
       <c r="G45" t="n">
-        <v>96.81</v>
+        <v>100</v>
       </c>
       <c r="H45" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I45" t="n">
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>87.83</v>
       </c>
       <c r="K45" t="n">
-        <v>93.61</v>
+        <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N45" t="n">
         <v>100</v>
       </c>
       <c r="O45" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>69.97</v>
+        <v>98.17</v>
       </c>
       <c r="Q45" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>87.47</v>
+        <v>98.17</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U45" t="n">
         <v>2026</v>
       </c>
       <c r="V45" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5700,35 +5700,35 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>10710500000</v>
+        <v>81321040000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
@@ -5744,24 +5744,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>69.65000000000001</v>
+        <v>94.98</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -5773,13 +5773,13 @@
         <v>100</v>
       </c>
       <c r="K46" t="n">
-        <v>39.29</v>
+        <v>84.94</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N46" t="n">
         <v>100</v>
@@ -5788,27 +5788,27 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>67.86</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="Q46" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>84.81999999999999</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U46" t="n">
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5817,16 +5817,16 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>114852670000</v>
+        <v>65205040000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5835,17 +5835,17 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -5866,19 +5866,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>86.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>77.81999999999999</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5887,10 +5887,10 @@
         <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>72.08</v>
+        <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>55.64</v>
+        <v>85.41</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5905,7 +5905,7 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>66.94</v>
+        <v>77.08</v>
       </c>
       <c r="Q47" t="n">
         <v>80</v>
@@ -5914,18 +5914,18 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>83.68000000000001</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U47" t="n">
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5934,16 +5934,16 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>9731020000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5952,17 +5952,17 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
@@ -5978,21 +5978,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>80.58</v>
+        <v>90.06</v>
       </c>
       <c r="G48" t="n">
         <v>100</v>
@@ -6004,10 +6004,10 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>61.15</v>
+        <v>80.12</v>
       </c>
       <c r="K48" t="n">
-        <v>70.05</v>
+        <v>100</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6022,27 +6022,27 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>58.18</v>
+        <v>77.02</v>
       </c>
       <c r="Q48" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>83.12</v>
+        <v>96.27</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U48" t="n">
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6051,35 +6051,35 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>287629890000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -6100,19 +6100,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>100</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>66.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -6121,10 +6121,10 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>100</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>32.14</v>
+        <v>100</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>66.43000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="Q49" t="n">
         <v>80</v>
@@ -6148,18 +6148,18 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>83.04000000000001</v>
+        <v>95.88</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U49" t="n">
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6168,16 +6168,16 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>5891850000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -6186,17 +6186,17 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
@@ -6217,19 +6217,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>65.39</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
@@ -6238,13 +6238,13 @@
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>100</v>
+        <v>94.52</v>
       </c>
       <c r="K50" t="n">
-        <v>30.78</v>
+        <v>85.13</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -6256,27 +6256,27 @@
         <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>66.16</v>
+        <v>86.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>82.7</v>
+        <v>95.78</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U50" t="n">
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6285,35 +6285,35 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>15707450000</v>
+        <v>10808640000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
@@ -6329,71 +6329,71 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>78.42</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>81.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>95.33</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>56.83</v>
+        <v>78.08</v>
       </c>
       <c r="K51" t="n">
-        <v>62.29</v>
+        <v>100</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N51" t="n">
         <v>100</v>
       </c>
       <c r="O51" t="n">
-        <v>100</v>
+        <v>95.33</v>
       </c>
       <c r="P51" t="n">
-        <v>65.98</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="Q51" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>82.48</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U51" t="n">
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6402,16 +6402,16 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>16133240000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -6420,17 +6420,17 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
@@ -6446,24 +6446,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>87.02</v>
       </c>
       <c r="G52" t="n">
-        <v>64.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -6472,16 +6472,16 @@
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>100</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>28.41</v>
+        <v>97.62</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" t="n">
         <v>100</v>
@@ -6490,27 +6490,27 @@
         <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>65.68000000000001</v>
+        <v>85.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>82.09999999999999</v>
+        <v>95.14</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U52" t="n">
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6519,16 +6519,16 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>345163450000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -6537,17 +6537,17 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
@@ -6563,39 +6563,39 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>95.19</v>
       </c>
       <c r="G53" t="n">
-        <v>82.27</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>75.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>90.37</v>
       </c>
       <c r="K53" t="n">
-        <v>46.8</v>
+        <v>86.52</v>
       </c>
       <c r="L53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6604,30 +6604,30 @@
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>75.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>73.36</v>
+        <v>75.86</v>
       </c>
       <c r="Q53" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>81.51000000000001</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U53" t="n">
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6636,35 +6636,35 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>10808640000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
@@ -6680,24 +6680,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>89.63</v>
       </c>
       <c r="G54" t="n">
-        <v>72.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -6706,13 +6706,13 @@
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>100</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>16.6</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6724,27 +6724,27 @@
         <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>73.31999999999999</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="Q54" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>81.47</v>
+        <v>94.56</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6753,35 +6753,35 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>9346940000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
@@ -6802,19 +6802,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>74.15000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="G55" t="n">
-        <v>81.29000000000001</v>
+        <v>97.61</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,13 +6823,13 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>48.3</v>
+        <v>71.22</v>
       </c>
       <c r="K55" t="n">
-        <v>62.58</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6841,27 +6841,27 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>64.76000000000001</v>
+        <v>84.25</v>
       </c>
       <c r="Q55" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>80.95</v>
+        <v>93.61</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U55" t="n">
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6870,35 +6870,35 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>5671610000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -6919,31 +6919,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>83.51000000000001</v>
+        <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>80.59</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>82.45999999999999</v>
+        <v>86</v>
       </c>
       <c r="I56" t="n">
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>67.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="K56" t="n">
-        <v>61.18</v>
+        <v>85.97</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6955,10 +6955,10 @@
         <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>82.45999999999999</v>
+        <v>86</v>
       </c>
       <c r="P56" t="n">
-        <v>62.9</v>
+        <v>73.69</v>
       </c>
       <c r="Q56" t="n">
         <v>80</v>
@@ -6967,18 +6967,18 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>78.63</v>
+        <v>92.12</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U56" t="n">
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6987,16 +6987,16 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>5176090000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -7005,17 +7005,17 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
@@ -7036,22 +7036,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>79.72</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>71.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
         <v>100</v>
@@ -7060,10 +7060,10 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>39.15</v>
+        <v>67.69</v>
       </c>
       <c r="L57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -7072,30 +7072,30 @@
         <v>100</v>
       </c>
       <c r="O57" t="n">
-        <v>71.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>70.7</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="Q57" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>78.55</v>
+        <v>91.92</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U57" t="n">
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7104,35 +7104,35 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>317944150000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -7153,19 +7153,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>69.47</v>
+        <v>80.86</v>
       </c>
       <c r="G58" t="n">
-        <v>75.73</v>
+        <v>96.2</v>
       </c>
       <c r="H58" t="n">
         <v>100</v>
@@ -7174,10 +7174,10 @@
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>38.93</v>
+        <v>61.72</v>
       </c>
       <c r="K58" t="n">
-        <v>51.45</v>
+        <v>92.39</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
         <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>61.13</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="Q58" t="n">
         <v>80</v>
@@ -7201,18 +7201,18 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>76.41</v>
+        <v>90.92</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U58" t="n">
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7221,35 +7221,35 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>13489830000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
@@ -7270,19 +7270,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>73.28</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>76.91</v>
+        <v>98.95</v>
       </c>
       <c r="H59" t="n">
         <v>100</v>
@@ -7291,13 +7291,13 @@
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>46.56</v>
+        <v>51.48</v>
       </c>
       <c r="K59" t="n">
-        <v>30.74</v>
+        <v>97.89</v>
       </c>
       <c r="L59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -7309,27 +7309,27 @@
         <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>68.13</v>
+        <v>72.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>75.7</v>
+        <v>90.38</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U59" t="n">
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7338,35 +7338,35 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>6368000000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7387,66 +7387,66 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>73.34999999999999</v>
+        <v>94.36</v>
       </c>
       <c r="H60" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>100</v>
+        <v>61.58</v>
       </c>
       <c r="K60" t="n">
-        <v>46.69</v>
+        <v>77.42</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N60" t="n">
         <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="P60" t="n">
-        <v>58.84</v>
+        <v>89.72</v>
       </c>
       <c r="Q60" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>73.55</v>
+        <v>89.72</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U60" t="n">
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7455,16 +7455,16 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>7789580000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7499,39 +7499,39 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>95.66</v>
+        <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>73.98</v>
+        <v>73.13</v>
       </c>
       <c r="H61" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>91.31</v>
+        <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>21.94</v>
+        <v>46.25</v>
       </c>
       <c r="L61" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -7540,30 +7540,30 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P61" t="n">
-        <v>64.33</v>
+        <v>69.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>71.48</v>
+        <v>86.56</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U61" t="n">
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7572,35 +7572,35 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>13427580000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7621,66 +7621,66 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>85.62</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>86.45999999999999</v>
+        <v>87.83</v>
       </c>
       <c r="H62" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>71.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>45.83</v>
+        <v>75.66</v>
       </c>
       <c r="L62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>100</v>
       </c>
       <c r="O62" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P62" t="n">
-        <v>67.34999999999999</v>
+        <v>66.38</v>
       </c>
       <c r="Q62" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>67.34999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U62" t="n">
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7689,35 +7689,35 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>20589110000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7738,31 +7738,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>96.70999999999999</v>
+        <v>82.27</v>
       </c>
       <c r="G63" t="n">
-        <v>50.33</v>
+        <v>94.05</v>
       </c>
       <c r="H63" t="n">
-        <v>65</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="I63" t="n">
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>93.41</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>0.65</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -7774,10 +7774,10 @@
         <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>65</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="P63" t="n">
-        <v>50.39</v>
+        <v>64.06</v>
       </c>
       <c r="Q63" t="n">
         <v>80</v>
@@ -7786,18 +7786,18 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>62.99</v>
+        <v>80.08</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U63" t="n">
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7806,16 +7806,16 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>7585360000</v>
+        <v>4481070000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7855,66 +7855,66 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>74.29000000000001</v>
+        <v>88.34</v>
       </c>
       <c r="G64" t="n">
-        <v>69.09</v>
+        <v>96.78</v>
       </c>
       <c r="H64" t="n">
-        <v>58.99</v>
+        <v>30</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>48.57</v>
+        <v>76.67</v>
       </c>
       <c r="K64" t="n">
-        <v>38.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N64" t="n">
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>58.99</v>
+        <v>30</v>
       </c>
       <c r="P64" t="n">
-        <v>49.67</v>
+        <v>76.42</v>
       </c>
       <c r="Q64" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>62.09</v>
+        <v>76.42</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U64" t="n">
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7923,35 +7923,35 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>4481070000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -8024,14 +8024,14 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U65" t="n">
         <v>2026</v>
       </c>
       <c r="V65" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z65" t="n">
@@ -8141,14 +8141,14 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U66" t="n">
         <v>2026</v>
       </c>
       <c r="V66" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8157,12 +8157,12 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z66" t="n">
@@ -8258,14 +8258,14 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>FEBRUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U67" t="n">
         <v>2026</v>
       </c>
       <c r="V67" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -8274,12 +8274,12 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>FEBRUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z67" t="n">

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -596,24 +596,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>97.55</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
@@ -625,7 +625,7 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>90.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
@@ -640,7 +640,7 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>98.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q2" t="n">
         <v>100</v>
@@ -649,11 +649,11 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>98.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -669,42 +669,42 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>42331120000</v>
+        <v>95984080000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -713,27 +713,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>93.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>99.19</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -742,42 +742,42 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>73.38</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>99.19</v>
+        <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>94.47</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>94.47</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>2026</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -786,16 +786,16 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>40484710000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -804,24 +804,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -830,24 +830,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>87.48</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
@@ -859,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>74.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>74.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q4" t="n">
         <v>80</v>
@@ -883,18 +883,18 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>93.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>2026</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -903,42 +903,42 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>95984080000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -947,24 +947,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>91.05</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
@@ -976,7 +976,7 @@
         <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>64.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
@@ -991,7 +991,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>92.84</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
         <v>100</v>
@@ -1000,18 +1000,18 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>92.84</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>2026</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1020,16 +1020,16 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>64847500000</v>
+        <v>139571760000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1038,24 +1038,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1064,24 +1064,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>90.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
@@ -1093,7 +1093,7 @@
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>60.39</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
         <v>100</v>
@@ -1108,7 +1108,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>92.08</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="n">
         <v>100</v>
@@ -1117,18 +1117,18 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>92.08</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>2026</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1137,16 +1137,16 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>574646890000</v>
+        <v>106528210000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1155,24 +1155,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>POLRES OKUS (665307)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1186,19 +1186,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>83.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
@@ -1210,13 +1210,13 @@
         <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>67.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
@@ -1225,27 +1225,27 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>73.56</v>
+        <v>100</v>
       </c>
       <c r="Q7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>91.95</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U7" t="n">
         <v>2026</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1254,42 +1254,42 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>31572500000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,24 +1298,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>86.28</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
@@ -1327,13 +1327,13 @@
         <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>58.85</v>
+        <v>100</v>
       </c>
       <c r="L8" t="n">
         <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
         <v>100</v>
@@ -1342,27 +1342,27 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>81.77</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>90.86</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U8" t="n">
         <v>2026</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1371,16 +1371,16 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>128489370000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1389,24 +1389,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1415,24 +1415,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>85.92</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -1444,10 +1444,10 @@
         <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>57.75</v>
+        <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1459,27 +1459,27 @@
         <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>81.55</v>
+        <v>80</v>
       </c>
       <c r="Q9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>90.61</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U9" t="n">
         <v>2026</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>727218440000</v>
+        <v>40671640000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1532,24 +1532,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>80.91</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -1561,7 +1561,7 @@
         <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>61.82</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1576,7 +1576,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>72.36</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="n">
         <v>80</v>
@@ -1585,18 +1585,18 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>90.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U10" t="n">
         <v>2026</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1605,16 +1605,16 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>5127100000</v>
+        <v>3484030000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1623,24 +1623,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1649,24 +1649,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>85.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
@@ -1678,10 +1678,10 @@
         <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>55.11</v>
+        <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1693,27 +1693,27 @@
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>81.02</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>90.02</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U11" t="n">
         <v>2026</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1722,42 +1722,42 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>139571760000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,24 +1766,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>79.77</v>
+        <v>100</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1795,10 +1795,10 @@
         <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>59.54</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1810,27 +1810,27 @@
         <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>71.91</v>
+        <v>90</v>
       </c>
       <c r="Q12" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>89.89</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U12" t="n">
         <v>2026</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1839,42 +1839,42 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>10675360000</v>
+        <v>475588950000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1883,24 +1883,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>79.45</v>
+        <v>100</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1912,13 +1912,13 @@
         <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>58.89</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
         <v>100</v>
@@ -1927,27 +1927,27 @@
         <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>71.78</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>89.72</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U13" t="n">
         <v>2026</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1956,16 +1956,16 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>74397990000</v>
+        <v>574646890000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1974,24 +1974,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2000,24 +2000,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>87.06</v>
+        <v>100</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -2029,7 +2029,7 @@
         <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>48.23</v>
+        <v>100</v>
       </c>
       <c r="L14" t="n">
         <v>100</v>
@@ -2044,7 +2044,7 @@
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>89.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q14" t="n">
         <v>100</v>
@@ -2053,18 +2053,18 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>89.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U14" t="n">
         <v>2026</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2073,16 +2073,16 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>105914680000</v>
+        <v>819256290000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2091,24 +2091,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2117,24 +2117,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>83.64</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -2146,10 +2146,10 @@
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>50.93</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2161,27 +2161,27 @@
         <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>80.19</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>89.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U15" t="n">
         <v>2026</v>
       </c>
       <c r="V15" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2190,42 +2190,42 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>819256290000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2234,24 +2234,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>86.34</v>
+        <v>100</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
@@ -2263,13 +2263,13 @@
         <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>45.35</v>
+        <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>100</v>
@@ -2278,27 +2278,27 @@
         <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>89.06999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>89.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U16" t="n">
         <v>2026</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2307,42 +2307,42 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>1376500000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2351,24 +2351,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>82.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
@@ -2380,13 +2380,13 @@
         <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>48.71</v>
+        <v>100</v>
       </c>
       <c r="L17" t="n">
         <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17" t="n">
         <v>100</v>
@@ -2395,27 +2395,27 @@
         <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>79.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q17" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>88.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U17" t="n">
         <v>2026</v>
       </c>
       <c r="V17" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>106528210000</v>
+        <v>727218440000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2442,17 +2442,17 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
@@ -2468,21 +2468,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
         <v>100</v>
@@ -2494,10 +2494,10 @@
         <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>88.58</v>
+        <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>65.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2512,27 +2512,27 @@
         <v>100</v>
       </c>
       <c r="P18" t="n">
-        <v>61.42</v>
+        <v>80</v>
       </c>
       <c r="Q18" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>87.75</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U18" t="n">
         <v>2026</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2541,42 +2541,42 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>405581540000</v>
+        <v>970430000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>86.45</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
         <v>100</v>
@@ -2611,16 +2611,16 @@
         <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>72.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K19" t="n">
-        <v>67.27</v>
+        <v>100</v>
       </c>
       <c r="L19" t="n">
         <v>100</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19" t="n">
         <v>100</v>
@@ -2629,27 +2629,27 @@
         <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>69.39</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>86.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U19" t="n">
         <v>2026</v>
       </c>
       <c r="V19" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2658,16 +2658,16 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>82576290000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2676,24 +2676,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2702,24 +2702,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>72.72</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
@@ -2731,7 +2731,7 @@
         <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>45.44</v>
+        <v>100</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>69.09</v>
+        <v>80</v>
       </c>
       <c r="Q20" t="n">
         <v>80</v>
@@ -2755,18 +2755,18 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>86.36</v>
+        <v>100</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U20" t="n">
         <v>2026</v>
       </c>
       <c r="V20" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2775,42 +2775,42 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>38902730000</v>
+        <v>1001460000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2824,19 +2824,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>94.37</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>76.84</v>
+        <v>100</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -2845,10 +2845,10 @@
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>88.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>53.67</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>69.05</v>
+        <v>80</v>
       </c>
       <c r="Q21" t="n">
         <v>80</v>
@@ -2872,18 +2872,18 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>86.31</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U21" t="n">
         <v>2026</v>
       </c>
       <c r="V21" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2892,16 +2892,16 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>9098870000</v>
+        <v>10710500000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2910,24 +2910,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,24 +2936,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>71.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
@@ -2965,10 +2965,10 @@
         <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>43.35</v>
+        <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2980,27 +2980,27 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>68.67</v>
+        <v>90</v>
       </c>
       <c r="Q22" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>85.84</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U22" t="n">
         <v>2026</v>
       </c>
       <c r="V22" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3009,42 +3009,42 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>43471570000</v>
+        <v>317944150000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3053,24 +3053,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>71.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
@@ -3082,7 +3082,7 @@
         <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>43.2</v>
+        <v>100</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>68.64</v>
+        <v>80</v>
       </c>
       <c r="Q23" t="n">
         <v>80</v>
@@ -3106,18 +3106,18 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>85.8</v>
+        <v>100</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U23" t="n">
         <v>2026</v>
       </c>
       <c r="V23" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3126,42 +3126,42 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>39931940000</v>
+        <v>5891850000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3170,24 +3170,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>69.93000000000001</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
@@ -3199,13 +3199,13 @@
         <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>39.85</v>
+        <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
@@ -3214,27 +3214,27 @@
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>67.97</v>
+        <v>100</v>
       </c>
       <c r="Q24" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>84.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U24" t="n">
         <v>2026</v>
       </c>
       <c r="V24" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3243,42 +3243,42 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>40671640000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3287,24 +3287,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>76.11</v>
+        <v>100</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
@@ -3316,7 +3316,7 @@
         <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>28.33</v>
+        <v>100</v>
       </c>
       <c r="L25" t="n">
         <v>100</v>
@@ -3331,7 +3331,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>75.67</v>
+        <v>90</v>
       </c>
       <c r="Q25" t="n">
         <v>90</v>
@@ -3340,18 +3340,18 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>84.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U25" t="n">
         <v>2026</v>
       </c>
       <c r="V25" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3360,42 +3360,42 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>95645370000</v>
+        <v>53136840000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3404,24 +3404,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>75.44</v>
+        <v>100</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
@@ -3433,13 +3433,13 @@
         <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>26.32</v>
+        <v>100</v>
       </c>
       <c r="L26" t="n">
         <v>100</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N26" t="n">
         <v>100</v>
@@ -3448,27 +3448,27 @@
         <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>75.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q26" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>83.63</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U26" t="n">
         <v>2026</v>
       </c>
       <c r="V26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3477,42 +3477,42 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>53136840000</v>
+        <v>729500000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3521,24 +3521,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>66.75</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
@@ -3550,13 +3550,13 @@
         <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>33.49</v>
+        <v>100</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27" t="n">
         <v>100</v>
@@ -3565,27 +3565,27 @@
         <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q27" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>83.37</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U27" t="n">
         <v>2026</v>
       </c>
       <c r="V27" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3594,42 +3594,42 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>65205040000</v>
+        <v>1376500000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3638,24 +3638,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>66.61</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
@@ -3667,13 +3667,13 @@
         <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>33.22</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
@@ -3682,27 +3682,27 @@
         <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>66.64</v>
+        <v>100</v>
       </c>
       <c r="Q28" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>83.31</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U28" t="n">
         <v>2026</v>
       </c>
       <c r="V28" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3711,42 +3711,42 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>114852670000</v>
+        <v>1230000000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3755,24 +3755,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>90.97</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>72.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -3781,16 +3781,16 @@
         <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>81.94</v>
+        <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>45.63</v>
+        <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29" t="n">
         <v>100</v>
@@ -3799,27 +3799,27 @@
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>66.42</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>83.02</v>
+        <v>100</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U29" t="n">
         <v>2026</v>
       </c>
       <c r="V29" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3828,16 +3828,16 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>39404370000</v>
+        <v>42331120000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3846,24 +3846,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3872,24 +3872,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>85.83</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>75.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -3898,16 +3898,16 @@
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>71.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="K30" t="n">
-        <v>50.35</v>
+        <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30" t="n">
         <v>100</v>
@@ -3916,27 +3916,27 @@
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>65.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q30" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>82.27</v>
+        <v>100</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U30" t="n">
         <v>2026</v>
       </c>
       <c r="V30" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3945,42 +3945,42 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>50054370000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3989,24 +3989,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>60.11</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
@@ -4018,7 +4018,7 @@
         <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>20.22</v>
+        <v>100</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>64.04000000000001</v>
+        <v>80</v>
       </c>
       <c r="Q31" t="n">
         <v>80</v>
@@ -4042,18 +4042,18 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>80.06</v>
+        <v>100</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U31" t="n">
         <v>2026</v>
       </c>
       <c r="V31" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4062,16 +4062,16 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>1001460000</v>
+        <v>10675360000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4080,24 +4080,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4111,19 +4111,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>59.74</v>
+        <v>100</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -4135,7 +4135,7 @@
         <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>19.48</v>
+        <v>100</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>63.9</v>
+        <v>80</v>
       </c>
       <c r="Q32" t="n">
         <v>80</v>
@@ -4159,18 +4159,18 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>79.87</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U32" t="n">
         <v>2026</v>
       </c>
       <c r="V32" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4179,16 +4179,16 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>3898470000</v>
+        <v>1707230000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4197,24 +4197,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4223,24 +4223,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>55.76</v>
+        <v>100</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -4252,7 +4252,7 @@
         <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>11.52</v>
+        <v>100</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4267,7 +4267,7 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>62.3</v>
+        <v>80</v>
       </c>
       <c r="Q33" t="n">
         <v>80</v>
@@ -4276,18 +4276,18 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>77.88</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U33" t="n">
         <v>2026</v>
       </c>
       <c r="V33" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4296,35 +4296,35 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>11480750000</v>
+        <v>5127100000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>81.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>68.25</v>
+        <v>99.95</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4366,10 +4366,10 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>63.48</v>
+        <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>36.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>61.82</v>
+        <v>79.98</v>
       </c>
       <c r="Q34" t="n">
         <v>80</v>
@@ -4393,18 +4393,18 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>77.28</v>
+        <v>99.98</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U34" t="n">
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4413,35 +4413,35 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>81321040000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4474,7 +4474,7 @@
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>52.06</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4486,7 +4486,7 @@
         <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>4.11</v>
+        <v>99.86</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>60.82</v>
+        <v>79.97</v>
       </c>
       <c r="Q35" t="n">
         <v>80</v>
@@ -4510,18 +4510,18 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>76.03</v>
+        <v>99.97</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U35" t="n">
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4530,20 +4530,20 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>9346940000</v>
+        <v>345163450000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -4574,24 +4574,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>75.51000000000001</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>70.26000000000001</v>
+        <v>99.83</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4600,16 +4600,16 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>51.01</v>
+        <v>100</v>
       </c>
       <c r="K36" t="n">
-        <v>40.51</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N36" t="n">
         <v>100</v>
@@ -4618,27 +4618,27 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>60.75</v>
+        <v>99.86</v>
       </c>
       <c r="Q36" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>75.94</v>
+        <v>99.86</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U36" t="n">
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4647,35 +4647,35 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>9731020000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
@@ -4691,24 +4691,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>50.62</v>
+        <v>100</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -4717,10 +4717,10 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="K37" t="n">
-        <v>1.23</v>
+        <v>100</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>60.25</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="Q37" t="n">
         <v>80</v>
@@ -4744,18 +4744,18 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>75.31</v>
+        <v>98.87</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U37" t="n">
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4764,35 +4764,35 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>5891850000</v>
+        <v>39404370000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
@@ -4808,24 +4808,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>50.19</v>
+        <v>98.3</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4837,10 +4837,10 @@
         <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>0.37</v>
+        <v>94.89</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4852,27 +4852,27 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>60.07</v>
+        <v>88.98</v>
       </c>
       <c r="Q38" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>75.09</v>
+        <v>98.86</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U38" t="n">
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4881,16 +4881,16 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>345163450000</v>
+        <v>95645370000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4899,17 +4899,17 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
@@ -4930,66 +4930,66 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>96.02</v>
       </c>
       <c r="G39" t="n">
-        <v>50.04</v>
+        <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I39" t="n">
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>100</v>
+        <v>92.03</v>
       </c>
       <c r="K39" t="n">
-        <v>0.07000000000000001</v>
+        <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
       </c>
       <c r="O39" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="P39" t="n">
-        <v>60.01</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="Q39" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>75.02</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U39" t="n">
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4998,35 +4998,35 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>475588950000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
@@ -5042,24 +5042,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -5068,16 +5068,16 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>100</v>
+        <v>90.97</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -5086,27 +5086,27 @@
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>60</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="Q40" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>75</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U40" t="n">
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5115,35 +5115,35 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>970430000</v>
+        <v>82576290000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
@@ -5159,21 +5159,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
+        <v>95.94</v>
       </c>
       <c r="G41" t="n">
         <v>100</v>
@@ -5185,10 +5185,10 @@
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>100</v>
+        <v>91.87</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L41" t="n">
         <v>100</v>
@@ -5203,27 +5203,27 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>60</v>
+        <v>88.78</v>
       </c>
       <c r="Q41" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>75</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U41" t="n">
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5232,16 +5232,16 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>1230000000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -5250,17 +5250,17 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
@@ -5276,24 +5276,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>87.98</v>
+        <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>55.09</v>
+        <v>97.13</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5302,10 +5302,10 @@
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>75.95</v>
+        <v>100</v>
       </c>
       <c r="K42" t="n">
-        <v>10.18</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5320,7 +5320,7 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>58.43</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="Q42" t="n">
         <v>80</v>
@@ -5329,18 +5329,18 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>73.04000000000001</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U42" t="n">
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5349,35 +5349,35 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>15177700000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
@@ -5393,24 +5393,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>67.13</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>70.51000000000001</v>
+        <v>100</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -5419,10 +5419,10 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>34.25</v>
+        <v>91.63</v>
       </c>
       <c r="K43" t="n">
-        <v>41.01</v>
+        <v>100</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>58.34</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="Q43" t="n">
         <v>80</v>
@@ -5446,18 +5446,18 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>72.92</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U43" t="n">
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5466,16 +5466,16 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>31225620000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5484,17 +5484,17 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
@@ -5515,19 +5515,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5539,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>0.36</v>
+        <v>93.59</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5554,27 +5554,27 @@
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>50.07</v>
+        <v>78.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>71.53</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U44" t="n">
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5583,35 +5583,35 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>15707450000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
@@ -5627,21 +5627,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>93.92</v>
       </c>
       <c r="G45" t="n">
         <v>100</v>
@@ -5653,16 +5653,16 @@
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>87.83</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N45" t="n">
         <v>100</v>
@@ -5671,27 +5671,27 @@
         <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>50</v>
+        <v>98.17</v>
       </c>
       <c r="Q45" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>71.43000000000001</v>
+        <v>98.17</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U45" t="n">
         <v>2026</v>
       </c>
       <c r="V45" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5700,35 +5700,35 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>1731600000</v>
+        <v>81321040000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
@@ -5744,24 +5744,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>100</v>
+        <v>94.98</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -5773,13 +5773,13 @@
         <v>100</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>84.94</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N46" t="n">
         <v>100</v>
@@ -5788,27 +5788,27 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>50</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="Q46" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>71.43000000000001</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U46" t="n">
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5817,35 +5817,35 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>3127760000</v>
+        <v>65205040000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -5866,19 +5866,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>100</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5890,7 +5890,7 @@
         <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>85.41</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5905,27 +5905,27 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>50</v>
+        <v>77.08</v>
       </c>
       <c r="Q47" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>71.43000000000001</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U47" t="n">
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5934,16 +5934,16 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>3484030000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5952,17 +5952,17 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
@@ -5983,16 +5983,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>90.06</v>
       </c>
       <c r="G48" t="n">
         <v>100</v>
@@ -6004,10 +6004,10 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>100</v>
+        <v>80.12</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6022,27 +6022,27 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>50</v>
+        <v>77.02</v>
       </c>
       <c r="Q48" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>71.43000000000001</v>
+        <v>96.27</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U48" t="n">
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6051,16 +6051,16 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>1707230000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6069,17 +6069,17 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -6095,21 +6095,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>68.90000000000001</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="G49" t="n">
         <v>100</v>
@@ -6121,10 +6121,10 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>37.79</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>38.84</v>
+        <v>100</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6139,27 +6139,27 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>48.44</v>
+        <v>76.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>69.2</v>
+        <v>95.88</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U49" t="n">
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6168,35 +6168,35 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>29335310000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
@@ -6226,25 +6226,25 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>55.33</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>69.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="I50" t="n">
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>100</v>
+        <v>94.52</v>
       </c>
       <c r="K50" t="n">
-        <v>10.66</v>
+        <v>85.13</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -6253,30 +6253,30 @@
         <v>100</v>
       </c>
       <c r="O50" t="n">
-        <v>69.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>54.5</v>
+        <v>86.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>68.12</v>
+        <v>95.78</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U50" t="n">
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6285,12 +6285,12 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z50" t="n">
@@ -6329,71 +6329,71 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>50.22</v>
+        <v>100</v>
       </c>
       <c r="H51" t="n">
-        <v>77.23</v>
+        <v>95.33</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>100</v>
+        <v>78.08</v>
       </c>
       <c r="K51" t="n">
-        <v>0.44</v>
+        <v>100</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N51" t="n">
         <v>100</v>
       </c>
       <c r="O51" t="n">
-        <v>77.23</v>
+        <v>95.33</v>
       </c>
       <c r="P51" t="n">
-        <v>54.4</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="Q51" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>67.98999999999999</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U51" t="n">
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6402,35 +6402,35 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>317944150000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
@@ -6446,71 +6446,71 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>97.44</v>
+        <v>87.02</v>
       </c>
       <c r="G52" t="n">
-        <v>69.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H52" t="n">
-        <v>47.5</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>94.88</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>39.29</v>
+        <v>97.62</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" t="n">
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>47.5</v>
+        <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>53.97</v>
+        <v>85.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>67.45999999999999</v>
+        <v>95.14</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U52" t="n">
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6519,35 +6519,35 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>10710500000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
@@ -6563,24 +6563,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>64.7</v>
+        <v>95.19</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
@@ -6589,10 +6589,10 @@
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>29.4</v>
+        <v>90.37</v>
       </c>
       <c r="K53" t="n">
-        <v>29.05</v>
+        <v>86.52</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -6607,27 +6607,27 @@
         <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>45.22</v>
+        <v>75.86</v>
       </c>
       <c r="Q53" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>64.59999999999999</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U53" t="n">
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6636,35 +6636,35 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>287629890000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
@@ -6680,39 +6680,39 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>94.59</v>
+        <v>89.63</v>
       </c>
       <c r="G54" t="n">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>89.18000000000001</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>0.54</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6721,10 +6721,10 @@
         <v>100</v>
       </c>
       <c r="O54" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>49.74</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="Q54" t="n">
         <v>80</v>
@@ -6733,18 +6733,18 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>62.17</v>
+        <v>94.56</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>13427580000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -6771,17 +6771,17 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
@@ -6802,19 +6802,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>50.75</v>
+        <v>85.61</v>
       </c>
       <c r="G55" t="n">
-        <v>66.84999999999999</v>
+        <v>97.61</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,10 +6823,10 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>1.49</v>
+        <v>71.22</v>
       </c>
       <c r="K55" t="n">
-        <v>0.55</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="L55" t="n">
         <v>100</v>
@@ -6841,7 +6841,7 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>55.33</v>
+        <v>84.25</v>
       </c>
       <c r="Q55" t="n">
         <v>90</v>
@@ -6850,18 +6850,18 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>61.48</v>
+        <v>93.61</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U55" t="n">
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6870,35 +6870,35 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>6368000000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -6919,31 +6919,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>56.83</v>
+        <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>54.07</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I56" t="n">
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>13.66</v>
+        <v>100</v>
       </c>
       <c r="K56" t="n">
-        <v>8.140000000000001</v>
+        <v>85.97</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6955,10 +6955,10 @@
         <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="P56" t="n">
-        <v>48.68</v>
+        <v>73.69</v>
       </c>
       <c r="Q56" t="n">
         <v>80</v>
@@ -6967,18 +6967,18 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>60.85</v>
+        <v>92.12</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U56" t="n">
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6987,35 +6987,35 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>16133240000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
@@ -7036,22 +7036,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>100</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
         <v>100</v>
@@ -7060,7 +7060,7 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>0.33</v>
+        <v>67.69</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -7072,30 +7072,30 @@
         <v>100</v>
       </c>
       <c r="O57" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>41.32</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="Q57" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>59.02</v>
+        <v>91.92</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U57" t="n">
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7104,35 +7104,35 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>7585360000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -7153,31 +7153,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>80.86</v>
       </c>
       <c r="G58" t="n">
-        <v>51.36</v>
+        <v>96.2</v>
       </c>
       <c r="H58" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>61.72</v>
       </c>
       <c r="K58" t="n">
-        <v>2.71</v>
+        <v>92.39</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>100</v>
       </c>
       <c r="O58" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>46.54</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="Q58" t="n">
         <v>80</v>
@@ -7201,18 +7201,18 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>58.18</v>
+        <v>90.92</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U58" t="n">
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7221,16 +7221,16 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>7789580000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -7239,17 +7239,17 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
@@ -7270,31 +7270,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>67.01000000000001</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>56.22</v>
+        <v>98.95</v>
       </c>
       <c r="H59" t="n">
-        <v>67.94</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>34.02</v>
+        <v>51.48</v>
       </c>
       <c r="K59" t="n">
-        <v>12.43</v>
+        <v>97.89</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -7306,10 +7306,10 @@
         <v>100</v>
       </c>
       <c r="O59" t="n">
-        <v>67.94</v>
+        <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>44.57</v>
+        <v>72.3</v>
       </c>
       <c r="Q59" t="n">
         <v>80</v>
@@ -7318,18 +7318,18 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>55.72</v>
+        <v>90.38</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U59" t="n">
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7338,35 +7338,35 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>5176090000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7382,71 +7382,71 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>94.36</v>
       </c>
       <c r="H60" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>100</v>
+        <v>61.58</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>77.42</v>
       </c>
       <c r="L60" t="n">
         <v>100</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N60" t="n">
         <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="P60" t="n">
-        <v>42.5</v>
+        <v>89.72</v>
       </c>
       <c r="Q60" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>53.13</v>
+        <v>89.72</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U60" t="n">
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7455,16 +7455,16 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>729500000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7499,39 +7499,39 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>80.69</v>
+        <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>68.29000000000001</v>
+        <v>73.13</v>
       </c>
       <c r="H61" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>61.37</v>
+        <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>4.86</v>
+        <v>46.25</v>
       </c>
       <c r="L61" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -7540,30 +7540,30 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="P61" t="n">
-        <v>47.68</v>
+        <v>69.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>52.98</v>
+        <v>86.56</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U61" t="n">
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7572,35 +7572,35 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>20589110000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7621,19 +7621,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>54.04</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>51.27</v>
+        <v>87.83</v>
       </c>
       <c r="H62" t="n">
         <v>65</v>
@@ -7642,10 +7642,10 @@
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>8.07</v>
+        <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>2.53</v>
+        <v>75.66</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
         <v>65</v>
       </c>
       <c r="P62" t="n">
-        <v>37.97</v>
+        <v>66.38</v>
       </c>
       <c r="Q62" t="n">
         <v>80</v>
@@ -7669,18 +7669,18 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>47.46</v>
+        <v>82.98</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U62" t="n">
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7689,16 +7689,16 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>5671610000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -7707,17 +7707,17 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7738,31 +7738,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>50.65</v>
+        <v>82.27</v>
       </c>
       <c r="G63" t="n">
-        <v>100</v>
+        <v>94.05</v>
       </c>
       <c r="H63" t="n">
-        <v>65</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="I63" t="n">
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>1.29</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>0.57</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -7774,30 +7774,30 @@
         <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>65</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="P63" t="n">
-        <v>26.56</v>
+        <v>64.06</v>
       </c>
       <c r="Q63" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>37.94</v>
+        <v>80.08</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U63" t="n">
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7806,35 +7806,35 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>13489830000</v>
+        <v>4481070000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7855,66 +7855,66 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>50.34</v>
+        <v>88.34</v>
       </c>
       <c r="G64" t="n">
-        <v>50.17</v>
+        <v>96.78</v>
       </c>
       <c r="H64" t="n">
-        <v>30.46</v>
+        <v>30</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>0.68</v>
+        <v>76.67</v>
       </c>
       <c r="K64" t="n">
-        <v>0.33</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N64" t="n">
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>30.46</v>
+        <v>30</v>
       </c>
       <c r="P64" t="n">
-        <v>27.78</v>
+        <v>76.42</v>
       </c>
       <c r="Q64" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>34.73</v>
+        <v>76.42</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U64" t="n">
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7923,35 +7923,35 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>4481070000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -7972,12 +7972,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -8024,14 +8024,14 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U65" t="n">
         <v>2026</v>
       </c>
       <c r="V65" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8040,16 +8040,16 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>6722660000</v>
+        <v>6728240000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -8058,17 +8058,17 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN (695184)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU (695176)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
@@ -8089,12 +8089,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8141,14 +8141,14 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U66" t="n">
         <v>2026</v>
       </c>
       <c r="V66" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8157,16 +8157,16 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>6728240000</v>
+        <v>6314270000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -8175,17 +8175,17 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU (695176)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR (695182)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -8206,12 +8206,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>695184</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8258,14 +8258,14 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U67" t="n">
         <v>2026</v>
       </c>
       <c r="V67" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -8274,16 +8274,16 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>MARET 2026</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>6314270000</v>
+        <v>6722660000</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -8292,17 +8292,17 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR (695182)</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN (695184)</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -4945,7 +4945,7 @@
         <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
         <v>100</v>
@@ -4966,10 +4966,10 @@
         <v>100</v>
       </c>
       <c r="O39" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>98.76000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="Q39" t="n">
         <v>100</v>
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>98.76000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5042,21 +5042,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>95.48999999999999</v>
+        <v>95.94</v>
       </c>
       <c r="G40" t="n">
         <v>100</v>
@@ -5068,7 +5068,7 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>90.97</v>
+        <v>91.87</v>
       </c>
       <c r="K40" t="n">
         <v>100</v>
@@ -5077,7 +5077,7 @@
         <v>100</v>
       </c>
       <c r="M40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -5086,10 +5086,10 @@
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>98.65000000000001</v>
+        <v>88.78</v>
       </c>
       <c r="Q40" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5124,26 +5124,26 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>82576290000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
@@ -5159,21 +5159,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>95.94</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="G41" t="n">
         <v>100</v>
@@ -5185,7 +5185,7 @@
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>91.87</v>
+        <v>90.97</v>
       </c>
       <c r="K41" t="n">
         <v>100</v>
@@ -5194,7 +5194,7 @@
         <v>100</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41" t="n">
         <v>100</v>
@@ -5203,10 +5203,10 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>88.78</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="Q41" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5241,26 +5241,26 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>9098870000</v>
+        <v>82576290000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
@@ -5744,24 +5744,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>100</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>94.98</v>
+        <v>100</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -5770,13 +5770,13 @@
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>100</v>
+        <v>78.08</v>
       </c>
       <c r="K46" t="n">
-        <v>84.94</v>
+        <v>100</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M46" t="n">
         <v>100</v>
@@ -5788,16 +5788,16 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>86.98999999999999</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="Q46" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>96.65000000000001</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5826,26 +5826,26 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>65205040000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -5861,24 +5861,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>92.70999999999999</v>
+        <v>94.98</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5890,13 +5890,13 @@
         <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>85.41</v>
+        <v>84.94</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N47" t="n">
         <v>100</v>
@@ -5905,16 +5905,16 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>77.08</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="Q47" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>96.34999999999999</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5943,26 +5943,26 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>1731600000</v>
+        <v>65205040000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
@@ -5983,19 +5983,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>90.06</v>
+        <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>100</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="H48" t="n">
         <v>100</v>
@@ -6004,10 +6004,10 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>80.12</v>
+        <v>100</v>
       </c>
       <c r="K48" t="n">
-        <v>100</v>
+        <v>85.97</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>77.02</v>
+        <v>77.19</v>
       </c>
       <c r="Q48" t="n">
         <v>80</v>
@@ -6031,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>96.27</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>9731020000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6069,17 +6069,17 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -6100,19 +6100,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>89.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>100</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -6121,10 +6121,10 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>78.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="K49" t="n">
-        <v>100</v>
+        <v>85.41</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>76.7</v>
+        <v>77.08</v>
       </c>
       <c r="Q49" t="n">
         <v>80</v>
@@ -6148,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>95.88</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>5176090000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -6186,17 +6186,17 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
@@ -6217,19 +6217,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>97.26000000000001</v>
+        <v>90.06</v>
       </c>
       <c r="G50" t="n">
-        <v>95.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
@@ -6238,13 +6238,13 @@
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>94.52</v>
+        <v>80.12</v>
       </c>
       <c r="K50" t="n">
-        <v>85.13</v>
+        <v>100</v>
       </c>
       <c r="L50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -6256,16 +6256,16 @@
         <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>86.2</v>
+        <v>77.02</v>
       </c>
       <c r="Q50" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>95.78</v>
+        <v>96.27</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>10808640000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -6303,17 +6303,17 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
@@ -6329,60 +6329,60 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>89.04000000000001</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="G51" t="n">
         <v>100</v>
       </c>
       <c r="H51" t="n">
-        <v>95.33</v>
+        <v>100</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>78.08</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="K51" t="n">
         <v>100</v>
       </c>
       <c r="L51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>100</v>
       </c>
       <c r="O51" t="n">
-        <v>95.33</v>
+        <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>95.54000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>95.54000000000001</v>
+        <v>95.88</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6411,26 +6411,26 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>31225620000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
@@ -6446,24 +6446,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>87.02</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>100</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -6472,16 +6472,16 @@
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>74.04000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="K52" t="n">
-        <v>97.62</v>
+        <v>85.13</v>
       </c>
       <c r="L52" t="n">
         <v>100</v>
       </c>
       <c r="M52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
         <v>100</v>
@@ -6490,7 +6490,7 @@
         <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>85.63</v>
+        <v>86.2</v>
       </c>
       <c r="Q52" t="n">
         <v>90</v>
@@ -6499,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>95.14</v>
+        <v>95.78</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6528,26 +6528,26 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>287629890000</v>
+        <v>10808640000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
@@ -6563,24 +6563,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>95.19</v>
+        <v>87.02</v>
       </c>
       <c r="G53" t="n">
-        <v>93.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
@@ -6589,16 +6589,16 @@
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>90.37</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>86.52</v>
+        <v>97.62</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
@@ -6607,16 +6607,16 @@
         <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>75.86</v>
+        <v>85.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>94.81999999999999</v>
+        <v>95.14</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6645,26 +6645,26 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>50054370000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
@@ -6680,24 +6680,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>89.63</v>
+        <v>95.19</v>
       </c>
       <c r="G54" t="n">
-        <v>96.90000000000001</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -6706,10 +6706,10 @@
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>79.26000000000001</v>
+        <v>90.37</v>
       </c>
       <c r="K54" t="n">
-        <v>93.79000000000001</v>
+        <v>86.52</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -6724,7 +6724,7 @@
         <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>75.65000000000001</v>
+        <v>75.86</v>
       </c>
       <c r="Q54" t="n">
         <v>80</v>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>94.56</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>29335310000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -6771,17 +6771,17 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
@@ -6797,24 +6797,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>85.61</v>
+        <v>89.63</v>
       </c>
       <c r="G55" t="n">
-        <v>97.61</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,13 +6823,13 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>71.22</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>92.81999999999999</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6841,16 +6841,16 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>84.25</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="Q55" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>93.61</v>
+        <v>94.56</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>16133240000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -6888,17 +6888,17 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -6919,55 +6919,55 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>88.34</v>
       </c>
       <c r="G56" t="n">
-        <v>92.98999999999999</v>
+        <v>96.78</v>
       </c>
       <c r="H56" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>100</v>
+        <v>76.67</v>
       </c>
       <c r="K56" t="n">
-        <v>85.97</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N56" t="n">
         <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>73.69</v>
+        <v>93.92</v>
       </c>
       <c r="Q56" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>92.12</v>
+        <v>93.92</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,26 +6996,26 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>7789580000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
@@ -7036,19 +7036,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>83.84999999999999</v>
+        <v>87.83</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -7060,7 +7060,7 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>67.69</v>
+        <v>75.66</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
         <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>73.54000000000001</v>
+        <v>75.13</v>
       </c>
       <c r="Q57" t="n">
         <v>80</v>
@@ -7084,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>91.92</v>
+        <v>93.92</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7113,26 +7113,26 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>15707450000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -7153,19 +7153,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>80.86</v>
+        <v>85.61</v>
       </c>
       <c r="G58" t="n">
-        <v>96.2</v>
+        <v>97.61</v>
       </c>
       <c r="H58" t="n">
         <v>100</v>
@@ -7174,13 +7174,13 @@
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>61.72</v>
+        <v>71.22</v>
       </c>
       <c r="K58" t="n">
-        <v>92.39</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -7192,16 +7192,16 @@
         <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>72.73999999999999</v>
+        <v>84.25</v>
       </c>
       <c r="Q58" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>90.92</v>
+        <v>93.61</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7230,26 +7230,26 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>5671610000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
@@ -7270,19 +7270,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>75.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>98.95</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="H59" t="n">
         <v>100</v>
@@ -7291,10 +7291,10 @@
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>51.48</v>
+        <v>100</v>
       </c>
       <c r="K59" t="n">
-        <v>97.89</v>
+        <v>67.69</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>72.3</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="Q59" t="n">
         <v>80</v>
@@ -7318,7 +7318,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>90.38</v>
+        <v>91.92</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>13489830000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -7356,17 +7356,17 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7387,19 +7387,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>80.79000000000001</v>
+        <v>80.86</v>
       </c>
       <c r="G60" t="n">
-        <v>94.36</v>
+        <v>96.2</v>
       </c>
       <c r="H60" t="n">
         <v>100</v>
@@ -7408,16 +7408,16 @@
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>61.58</v>
+        <v>61.72</v>
       </c>
       <c r="K60" t="n">
-        <v>77.42</v>
+        <v>92.39</v>
       </c>
       <c r="L60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>100</v>
@@ -7426,16 +7426,16 @@
         <v>100</v>
       </c>
       <c r="P60" t="n">
-        <v>89.72</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="Q60" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>89.72</v>
+        <v>90.92</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>6368000000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7499,24 +7499,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>73.13</v>
+        <v>98.95</v>
       </c>
       <c r="H61" t="n">
         <v>100</v>
@@ -7525,10 +7525,10 @@
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>100</v>
+        <v>51.48</v>
       </c>
       <c r="K61" t="n">
-        <v>46.25</v>
+        <v>97.89</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -7543,7 +7543,7 @@
         <v>100</v>
       </c>
       <c r="P61" t="n">
-        <v>69.25</v>
+        <v>72.3</v>
       </c>
       <c r="Q61" t="n">
         <v>80</v>
@@ -7552,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>86.56</v>
+        <v>90.38</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7581,26 +7581,26 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>114852670000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7621,31 +7621,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>82.27</v>
       </c>
       <c r="G62" t="n">
-        <v>87.83</v>
+        <v>94.05</v>
       </c>
       <c r="H62" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>100</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>75.66</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -7657,10 +7657,10 @@
         <v>100</v>
       </c>
       <c r="O62" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P62" t="n">
-        <v>66.38</v>
+        <v>72.3</v>
       </c>
       <c r="Q62" t="n">
         <v>80</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>82.98</v>
+        <v>90.38</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>7585360000</v>
+        <v>4481070000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -7707,17 +7707,17 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7738,55 +7738,55 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>82.27</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>94.05</v>
+        <v>94.36</v>
       </c>
       <c r="H63" t="n">
-        <v>67.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>64.54000000000001</v>
+        <v>61.58</v>
       </c>
       <c r="K63" t="n">
-        <v>88.09999999999999</v>
+        <v>77.42</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N63" t="n">
         <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>67.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="P63" t="n">
-        <v>64.06</v>
+        <v>89.72</v>
       </c>
       <c r="Q63" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>80.08</v>
+        <v>89.72</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>4481070000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7850,60 +7850,60 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>88.34</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>96.78</v>
+        <v>73.13</v>
       </c>
       <c r="H64" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>76.67</v>
+        <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>87.09999999999999</v>
+        <v>46.25</v>
       </c>
       <c r="L64" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="P64" t="n">
-        <v>76.42</v>
+        <v>69.25</v>
       </c>
       <c r="Q64" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>76.42</v>
+        <v>86.56</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7932,26 +7932,26 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>20589110000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -7972,12 +7972,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695184</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -8031,7 +8031,7 @@
         <v>2026</v>
       </c>
       <c r="V65" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>6728240000</v>
+        <v>6722660000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -8058,17 +8058,17 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENHAJ OKUS</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU (695176)</t>
+          <t>KANTOR KEMENHAJ OKUS (695184)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENHAJ OKUS</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
@@ -8089,12 +8089,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8148,7 +8148,7 @@
         <v>2026</v>
       </c>
       <c r="V66" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>6314270000</v>
+        <v>6728240000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -8175,17 +8175,17 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENHAJ OKU</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR (695182)</t>
+          <t>KANTOR KEMENHAJ OKU (695176)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENHAJ OKU</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -8206,12 +8206,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8265,7 +8265,7 @@
         <v>2026</v>
       </c>
       <c r="V67" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>6722660000</v>
+        <v>6314270000</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -8292,17 +8292,17 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENHAJ OKUT</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN (695184)</t>
+          <t>KANTOR KEMENHAJ OKUT (695182)</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENHAJ OKUT</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE67"/>
+  <dimension ref="A1:AE72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,7 +704,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -713,17 +713,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>11480750000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -804,24 +804,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -830,17 +830,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>31572500000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -947,17 +947,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -979,10 +979,10 @@
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -991,10 +991,10 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1029,33 +1029,33 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>139571760000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1096,10 +1096,10 @@
         <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1108,10 +1108,10 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1146,33 +1146,33 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>106528210000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>692725</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>RUPBASAN KELAS II BATURAJA</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1263,33 +1263,33 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>105914680000</v>
+        <v>16300640000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>RUPBASAN BATURAJA (692725)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,17 +1298,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>405581540000</v>
+        <v>727218440000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1389,24 +1389,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1415,17 +1415,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1459,10 +1459,10 @@
         <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>40671640000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1506,24 +1506,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1532,17 +1532,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1614,33 +1614,33 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>3484030000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>3127760000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1740,24 +1740,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1801,7 +1801,7 @@
         <v>100</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
         <v>100</v>
@@ -1810,10 +1810,10 @@
         <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>475588950000</v>
+        <v>819256290000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1857,24 +1857,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2000,17 +2000,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2032,10 +2032,10 @@
         <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>100</v>
@@ -2044,10 +2044,10 @@
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>819256290000</v>
+        <v>475588950000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2091,24 +2091,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2117,17 +2117,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>43471570000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2208,24 +2208,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -2316,33 +2316,33 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>38902730000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2383,10 +2383,10 @@
         <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>100</v>
@@ -2395,10 +2395,10 @@
         <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q17" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2433,33 +2433,33 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>727218440000</v>
+        <v>970430000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2473,12 +2473,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>970430000</v>
+        <v>3484030000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2559,24 +2559,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2585,17 +2585,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>666507</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2617,10 +2617,10 @@
         <v>100</v>
       </c>
       <c r="L19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>100</v>
@@ -2629,10 +2629,10 @@
         <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q19" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2667,33 +2667,33 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>128489370000</v>
+        <v>360100000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>KEMENAG OKUT (666507)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2702,17 +2702,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -2734,10 +2734,10 @@
         <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" t="n">
         <v>100</v>
@@ -2746,10 +2746,10 @@
         <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q20" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2784,33 +2784,33 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>1001460000</v>
+        <v>40671640000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2851,10 +2851,10 @@
         <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N21" t="n">
         <v>100</v>
@@ -2863,10 +2863,10 @@
         <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2901,33 +2901,33 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>10710500000</v>
+        <v>65205040000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2968,7 +2968,7 @@
         <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2980,10 +2980,10 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q22" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>317944150000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3027,24 +3027,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3053,17 +3053,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -3135,33 +3135,33 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>5891850000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3170,17 +3170,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -3205,7 +3205,7 @@
         <v>100</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
@@ -3214,10 +3214,10 @@
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q24" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3252,33 +3252,33 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>9346940000</v>
+        <v>95645370000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3287,17 +3287,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -3322,7 +3322,7 @@
         <v>100</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
         <v>100</v>
@@ -3331,10 +3331,10 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q25" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3369,33 +3369,33 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>53136840000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3404,17 +3404,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -3486,33 +3486,33 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>729500000</v>
+        <v>106528210000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -3603,33 +3603,33 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>1376500000</v>
+        <v>139571760000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3638,17 +3638,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -3670,10 +3670,10 @@
         <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
@@ -3682,10 +3682,10 @@
         <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q28" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3720,33 +3720,33 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>1230000000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3755,17 +3755,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3837,33 +3837,33 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>42331120000</v>
+        <v>81321040000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3872,17 +3872,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3904,10 +3904,10 @@
         <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>100</v>
@@ -3916,10 +3916,10 @@
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q30" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3954,33 +3954,33 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>64847500000</v>
+        <v>360100000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>KEMENAG OKUS (440507)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3989,17 +3989,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>10675360000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4080,24 +4080,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>1707230000</v>
+        <v>1001460000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4197,24 +4197,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4223,17 +4223,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4255,7 +4255,7 @@
         <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4267,10 +4267,10 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q33" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4305,33 +4305,33 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>5127100000</v>
+        <v>53136840000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>99.95</v>
+        <v>100</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4369,13 +4369,13 @@
         <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N34" t="n">
         <v>100</v>
@@ -4384,16 +4384,16 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>79.98</v>
+        <v>100</v>
       </c>
       <c r="Q34" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>99.98</v>
+        <v>100</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4422,33 +4422,33 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>39931940000</v>
+        <v>82576290000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4457,24 +4457,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>99.93000000000001</v>
+        <v>100</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4486,10 +4486,10 @@
         <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>99.86</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4501,16 +4501,16 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>79.97</v>
+        <v>90</v>
       </c>
       <c r="Q35" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>99.97</v>
+        <v>100</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>345163450000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -4548,24 +4548,24 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4579,19 +4579,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>99.83</v>
+        <v>100</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4603,13 +4603,13 @@
         <v>100</v>
       </c>
       <c r="K36" t="n">
-        <v>99.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="L36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>100</v>
@@ -4618,16 +4618,16 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>99.86</v>
+        <v>80</v>
       </c>
       <c r="Q36" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>99.86</v>
+        <v>100</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4656,33 +4656,33 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>40484710000</v>
+        <v>5127100000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>96.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
         <v>100</v>
@@ -4717,7 +4717,7 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>93.98</v>
+        <v>100</v>
       </c>
       <c r="K37" t="n">
         <v>100</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>79.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q37" t="n">
         <v>80</v>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>98.87</v>
+        <v>100</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4773,33 +4773,33 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>39404370000</v>
+        <v>1707230000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4808,24 +4808,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4837,10 +4837,10 @@
         <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>94.89</v>
+        <v>100</v>
       </c>
       <c r="L38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4852,16 +4852,16 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>88.98</v>
+        <v>80</v>
       </c>
       <c r="Q38" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>98.86</v>
+        <v>100</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4890,33 +4890,33 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>95645370000</v>
+        <v>10675360000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4925,21 +4925,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>96.02</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -4951,7 +4951,7 @@
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>92.03</v>
+        <v>100</v>
       </c>
       <c r="K39" t="n">
         <v>100</v>
@@ -4969,16 +4969,16 @@
         <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>98.8</v>
+        <v>90</v>
       </c>
       <c r="Q39" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -5007,33 +5007,33 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>13427580000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5042,21 +5042,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>95.94</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
         <v>100</v>
@@ -5068,7 +5068,7 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>91.87</v>
+        <v>100</v>
       </c>
       <c r="K40" t="n">
         <v>100</v>
@@ -5077,7 +5077,7 @@
         <v>100</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -5086,16 +5086,16 @@
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>88.78</v>
+        <v>100</v>
       </c>
       <c r="Q40" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>98.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5124,33 +5124,33 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>9098870000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5159,21 +5159,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>95.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="G41" t="n">
         <v>100</v>
@@ -5185,16 +5185,16 @@
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>90.97</v>
+        <v>100</v>
       </c>
       <c r="K41" t="n">
         <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>100</v>
@@ -5203,16 +5203,16 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>98.65000000000001</v>
+        <v>80</v>
       </c>
       <c r="Q41" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>98.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5241,33 +5241,33 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>82576290000</v>
+        <v>10808640000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5276,24 +5276,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>97.13</v>
+        <v>100</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5305,13 +5305,13 @@
         <v>100</v>
       </c>
       <c r="K42" t="n">
-        <v>94.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N42" t="n">
         <v>100</v>
@@ -5320,16 +5320,16 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>78.84999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q42" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>98.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5358,33 +5358,33 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>74397990000</v>
+        <v>42331120000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5393,21 +5393,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>95.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="G43" t="n">
         <v>100</v>
@@ -5419,16 +5419,16 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>91.63</v>
+        <v>100</v>
       </c>
       <c r="K43" t="n">
         <v>100</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N43" t="n">
         <v>100</v>
@@ -5437,16 +5437,16 @@
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>78.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q43" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>98.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5475,33 +5475,33 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>15177700000</v>
+        <v>1230000000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5510,24 +5510,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5539,13 +5539,13 @@
         <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>93.59</v>
+        <v>100</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N44" t="n">
         <v>100</v>
@@ -5554,16 +5554,16 @@
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>78.72</v>
+        <v>100</v>
       </c>
       <c r="Q44" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>3898470000</v>
+        <v>1376500000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -5601,24 +5601,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5627,21 +5627,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>93.92</v>
+        <v>100</v>
       </c>
       <c r="G45" t="n">
         <v>100</v>
@@ -5653,7 +5653,7 @@
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>87.83</v>
+        <v>100</v>
       </c>
       <c r="K45" t="n">
         <v>100</v>
@@ -5671,7 +5671,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>98.17</v>
+        <v>100</v>
       </c>
       <c r="Q45" t="n">
         <v>100</v>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>98.17</v>
+        <v>100</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>2026</v>
       </c>
       <c r="V45" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5709,33 +5709,33 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>81321040000</v>
+        <v>729500000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5744,21 +5744,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>89.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="G46" t="n">
         <v>100</v>
@@ -5770,7 +5770,7 @@
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>78.08</v>
+        <v>100</v>
       </c>
       <c r="K46" t="n">
         <v>100</v>
@@ -5788,7 +5788,7 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>96.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q46" t="n">
         <v>100</v>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>96.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>31225620000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5835,24 +5835,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5861,24 +5861,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>94.98</v>
+        <v>100</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5890,13 +5890,13 @@
         <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>84.94</v>
+        <v>100</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>100</v>
@@ -5905,16 +5905,16 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>86.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q47" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>96.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5943,33 +5943,33 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>65205040000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5995,7 +5995,7 @@
         <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>92.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="H48" t="n">
         <v>100</v>
@@ -6007,7 +6007,7 @@
         <v>100</v>
       </c>
       <c r="K48" t="n">
-        <v>85.97</v>
+        <v>100</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>77.19</v>
+        <v>80</v>
       </c>
       <c r="Q48" t="n">
         <v>80</v>
@@ -6031,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>96.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>7789580000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
@@ -6086,7 +6086,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>418461</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6112,7 +6112,7 @@
         <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>92.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -6124,7 +6124,7 @@
         <v>100</v>
       </c>
       <c r="K49" t="n">
-        <v>85.41</v>
+        <v>100</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>77.08</v>
+        <v>80</v>
       </c>
       <c r="Q49" t="n">
         <v>80</v>
@@ -6148,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>96.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>1731600000</v>
+        <v>360100000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>KEMENAG OKU (418461)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -6203,7 +6203,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6217,16 +6217,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>90.06</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
         <v>100</v>
@@ -6238,7 +6238,7 @@
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>80.12</v>
+        <v>100</v>
       </c>
       <c r="K50" t="n">
         <v>100</v>
@@ -6256,7 +6256,7 @@
         <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>77.02</v>
+        <v>80</v>
       </c>
       <c r="Q50" t="n">
         <v>80</v>
@@ -6265,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>96.27</v>
+        <v>100</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>9731020000</v>
+        <v>5891850000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -6303,24 +6303,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6334,16 +6334,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>89.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="G51" t="n">
         <v>100</v>
@@ -6355,7 +6355,7 @@
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>78.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="K51" t="n">
         <v>100</v>
@@ -6373,7 +6373,7 @@
         <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>76.7</v>
+        <v>80</v>
       </c>
       <c r="Q51" t="n">
         <v>80</v>
@@ -6382,7 +6382,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>95.88</v>
+        <v>100</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>5176090000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -6420,24 +6420,24 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6446,24 +6446,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>97.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="G52" t="n">
-        <v>95.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -6472,13 +6472,13 @@
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>94.52</v>
+        <v>100</v>
       </c>
       <c r="K52" t="n">
-        <v>85.13</v>
+        <v>100</v>
       </c>
       <c r="L52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -6490,16 +6490,16 @@
         <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>86.2</v>
+        <v>80</v>
       </c>
       <c r="Q52" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>95.78</v>
+        <v>100</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6528,33 +6528,33 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>10808640000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6563,21 +6563,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>87.02</v>
+        <v>100</v>
       </c>
       <c r="G53" t="n">
         <v>100</v>
@@ -6589,16 +6589,16 @@
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>74.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="K53" t="n">
-        <v>97.62</v>
+        <v>100</v>
       </c>
       <c r="L53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
@@ -6607,16 +6607,16 @@
         <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>85.63</v>
+        <v>80</v>
       </c>
       <c r="Q53" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>95.14</v>
+        <v>100</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6645,33 +6645,33 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>287629890000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6680,24 +6680,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>95.19</v>
+        <v>100</v>
       </c>
       <c r="G54" t="n">
-        <v>93.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -6706,10 +6706,10 @@
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>90.37</v>
+        <v>100</v>
       </c>
       <c r="K54" t="n">
-        <v>86.52</v>
+        <v>100</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -6724,7 +6724,7 @@
         <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>75.86</v>
+        <v>80</v>
       </c>
       <c r="Q54" t="n">
         <v>80</v>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>94.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>50054370000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -6771,24 +6771,24 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6797,24 +6797,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>89.63</v>
+        <v>100</v>
       </c>
       <c r="G55" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,10 +6823,10 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>79.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="K55" t="n">
-        <v>93.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>75.65000000000001</v>
+        <v>80</v>
       </c>
       <c r="Q55" t="n">
         <v>80</v>
@@ -6850,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>94.56</v>
+        <v>100</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6879,33 +6879,33 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>29335310000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>88.34</v>
+        <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>96.78</v>
+        <v>100</v>
       </c>
       <c r="H56" t="n">
         <v>100</v>
@@ -6940,16 +6940,16 @@
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>76.67</v>
+        <v>100</v>
       </c>
       <c r="K56" t="n">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="L56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>100</v>
@@ -6958,16 +6958,16 @@
         <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>93.92</v>
+        <v>80</v>
       </c>
       <c r="Q56" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>93.92</v>
+        <v>100</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7031,24 +7031,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>87.83</v>
+        <v>100</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -7060,13 +7060,13 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>75.66</v>
+        <v>100</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" t="n">
         <v>100</v>
@@ -7075,16 +7075,16 @@
         <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>75.13</v>
+        <v>100</v>
       </c>
       <c r="Q57" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>93.92</v>
+        <v>100</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7113,33 +7113,33 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>7585360000</v>
+        <v>39404370000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7148,24 +7148,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>85.61</v>
+        <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>97.61</v>
+        <v>100</v>
       </c>
       <c r="H58" t="n">
         <v>100</v>
@@ -7174,13 +7174,13 @@
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>71.22</v>
+        <v>100</v>
       </c>
       <c r="K58" t="n">
-        <v>92.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="L58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -7192,16 +7192,16 @@
         <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>84.25</v>
+        <v>80</v>
       </c>
       <c r="Q58" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>93.61</v>
+        <v>100</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7230,33 +7230,33 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>16133240000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7270,19 +7270,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>83.84999999999999</v>
+        <v>100</v>
       </c>
       <c r="H59" t="n">
         <v>100</v>
@@ -7294,7 +7294,7 @@
         <v>100</v>
       </c>
       <c r="K59" t="n">
-        <v>67.69</v>
+        <v>100</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>73.54000000000001</v>
+        <v>80</v>
       </c>
       <c r="Q59" t="n">
         <v>80</v>
@@ -7318,7 +7318,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>91.92</v>
+        <v>100</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7347,26 +7347,26 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>15707450000</v>
+        <v>317944150000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7387,31 +7387,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>80.86</v>
+        <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>95.88</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>61.72</v>
+        <v>100</v>
       </c>
       <c r="K60" t="n">
-        <v>92.39</v>
+        <v>100</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -7423,10 +7423,10 @@
         <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>100</v>
+        <v>95.88</v>
       </c>
       <c r="P60" t="n">
-        <v>72.73999999999999</v>
+        <v>78.97</v>
       </c>
       <c r="Q60" t="n">
         <v>80</v>
@@ -7435,7 +7435,7 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>90.92</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>5671610000</v>
+        <v>10710500000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7499,36 +7499,36 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>75.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>98.95</v>
+        <v>100</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>95.33</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>51.48</v>
+        <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>97.89</v>
+        <v>100</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -7540,10 +7540,10 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>100</v>
+        <v>95.33</v>
       </c>
       <c r="P61" t="n">
-        <v>72.3</v>
+        <v>78.83</v>
       </c>
       <c r="Q61" t="n">
         <v>80</v>
@@ -7552,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>90.38</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>13489830000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -7590,17 +7590,17 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7616,60 +7616,60 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>82.27</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>94.05</v>
+        <v>100</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>87.83</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>64.54000000000001</v>
+        <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>88.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N62" t="n">
         <v>100</v>
       </c>
       <c r="O62" t="n">
-        <v>100</v>
+        <v>87.83</v>
       </c>
       <c r="P62" t="n">
-        <v>72.3</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="Q62" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>90.38</v>
+        <v>96.62</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7698,26 +7698,26 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>4481070000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7738,55 +7738,55 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>80.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>94.36</v>
+        <v>100</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I63" t="n">
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>61.58</v>
+        <v>100</v>
       </c>
       <c r="K63" t="n">
-        <v>77.42</v>
+        <v>100</v>
       </c>
       <c r="L63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="P63" t="n">
-        <v>89.72</v>
+        <v>76.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>89.72</v>
+        <v>95.63</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7815,26 +7815,26 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>6368000000</v>
+        <v>345163450000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7850,27 +7850,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>73.13</v>
+        <v>100</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
@@ -7879,7 +7879,7 @@
         <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>46.25</v>
+        <v>100</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -7891,10 +7891,10 @@
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="P64" t="n">
-        <v>69.25</v>
+        <v>75.63</v>
       </c>
       <c r="Q64" t="n">
         <v>80</v>
@@ -7903,7 +7903,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>86.56</v>
+        <v>94.53</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7932,26 +7932,26 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>114852670000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -7967,36 +7967,36 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
         <v>100</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>76.67</v>
       </c>
       <c r="I65" t="n">
         <v>100</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -8008,19 +8008,19 @@
         <v>100</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>76.67</v>
       </c>
       <c r="P65" t="n">
-        <v>10</v>
+        <v>74.17</v>
       </c>
       <c r="Q65" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>14.29</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>2026</v>
       </c>
       <c r="V65" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8049,26 +8049,26 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>6722660000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS (695184)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
@@ -8084,36 +8084,36 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G66" t="n">
         <v>100</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I66" t="n">
         <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -8125,19 +8125,19 @@
         <v>100</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P66" t="n">
-        <v>10</v>
+        <v>71.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>14.29</v>
+        <v>89.06</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>2026</v>
       </c>
       <c r="V66" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>6728240000</v>
+        <v>4481070000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -8175,17 +8175,17 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKU</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKU (695176)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKU</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -8201,36 +8201,36 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G67" t="n">
         <v>100</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I67" t="n">
         <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -8242,19 +8242,19 @@
         <v>100</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P67" t="n">
-        <v>10</v>
+        <v>71.25</v>
       </c>
       <c r="Q67" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>14.29</v>
+        <v>89.06</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8265,47 +8265,632 @@
         <v>2026</v>
       </c>
       <c r="V67" t="n">
+        <v>8</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>5176090000</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUT</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUT (553099)</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>MTSN 3 OKUT</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>500163</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>50</v>
+      </c>
+      <c r="G68" t="n">
+        <v>100</v>
+      </c>
+      <c r="H68" t="n">
+        <v>100</v>
+      </c>
+      <c r="I68" t="n">
+        <v>100</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>100</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>100</v>
+      </c>
+      <c r="P68" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>70</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V68" t="n">
+        <v>9</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>25001062180000</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM (500163)</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>600092</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>50</v>
+      </c>
+      <c r="G69" t="n">
+        <v>100</v>
+      </c>
+      <c r="H69" t="n">
+        <v>100</v>
+      </c>
+      <c r="I69" t="n">
+        <v>100</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>100</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>100</v>
+      </c>
+      <c r="P69" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>70</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V69" t="n">
+        <v>9</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>6858654090000</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS (600092)</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>700283</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>50</v>
+      </c>
+      <c r="G70" t="n">
+        <v>100</v>
+      </c>
+      <c r="H70" t="n">
+        <v>100</v>
+      </c>
+      <c r="I70" t="n">
+        <v>100</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>100</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>100</v>
+      </c>
+      <c r="P70" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>70</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V70" t="n">
+        <v>9</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>2130588270000</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN (700283)</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>662127</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>100</v>
+      </c>
+      <c r="G71" t="n">
+        <v>100</v>
+      </c>
+      <c r="H71" t="n">
         <v>30</v>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="I71" t="n">
+        <v>100</v>
+      </c>
+      <c r="J71" t="n">
+        <v>100</v>
+      </c>
+      <c r="K71" t="n">
+        <v>100</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>100</v>
+      </c>
+      <c r="O71" t="n">
+        <v>30</v>
+      </c>
+      <c r="P71" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>80</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>78.13</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V71" t="n">
+        <v>10</v>
+      </c>
+      <c r="W71" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>MARET 2026</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="Z67" t="n">
-        <v>6314270000</v>
-      </c>
-      <c r="AA67" t="inlineStr">
+      <c r="Z71" t="n">
+        <v>13489830000</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUS</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUS (662127)</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>MAN 1 OKUS</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>691653</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>100</v>
+      </c>
+      <c r="G72" t="n">
+        <v>100</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>100</v>
+      </c>
+      <c r="J72" t="n">
+        <v>100</v>
+      </c>
+      <c r="K72" t="n">
+        <v>100</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>100</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>70</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>MARET</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>2026</v>
+      </c>
+      <c r="V72" t="n">
+        <v>11</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>MARET 2026</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="inlineStr">
         <is>
           <t>KECIL</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>KANTOR KEMENHAJ OKUT</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>KANTOR KEMENHAJ OKUT (695182)</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>KANTOR KEMENHAJ OKUT</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr"/>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>DISNAKERTRANS OKUT</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>DISNAKERTRANS OKUT (691653)</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>DISNAKERTRANS OKUT</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/IKPA_MARET_2026.xlsx
+++ b/data/IKPA_MARET_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE72"/>
+  <dimension ref="A1:AE67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,7 +704,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -713,17 +713,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>16133240000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -804,24 +804,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -830,17 +830,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>11480750000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -947,17 +947,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -979,10 +979,10 @@
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -991,10 +991,10 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1029,33 +1029,33 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>9731020000</v>
+        <v>139571760000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1096,10 +1096,10 @@
         <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1108,10 +1108,10 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1146,33 +1146,33 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>7585360000</v>
+        <v>106528210000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>692725</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RUPBASAN KELAS II BATURAJA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1263,33 +1263,33 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>16300640000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA (692725)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,17 +1298,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>727218440000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1389,24 +1389,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1415,17 +1415,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1459,10 +1459,10 @@
         <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="Q9" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>38902730000</v>
+        <v>40671640000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1506,24 +1506,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1532,17 +1532,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1614,33 +1614,33 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>43471570000</v>
+        <v>3484030000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>5671610000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1740,24 +1740,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1801,7 +1801,7 @@
         <v>100</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>100</v>
@@ -1810,10 +1810,10 @@
         <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>819256290000</v>
+        <v>475588950000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1857,24 +1857,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2000,17 +2000,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2032,10 +2032,10 @@
         <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14" t="n">
         <v>100</v>
@@ -2044,10 +2044,10 @@
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q14" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>475588950000</v>
+        <v>819256290000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2091,24 +2091,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2117,17 +2117,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>15707450000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2208,24 +2208,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -2316,33 +2316,33 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>3127760000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2383,10 +2383,10 @@
         <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17" t="n">
         <v>100</v>
@@ -2395,10 +2395,10 @@
         <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q17" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2433,33 +2433,33 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>970430000</v>
+        <v>727218440000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2473,12 +2473,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>3484030000</v>
+        <v>970430000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2559,24 +2559,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2585,17 +2585,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2617,10 +2617,10 @@
         <v>100</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19" t="n">
         <v>100</v>
@@ -2629,10 +2629,10 @@
         <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2667,33 +2667,33 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>360100000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666507)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2702,17 +2702,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -2734,10 +2734,10 @@
         <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>100</v>
@@ -2746,10 +2746,10 @@
         <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q20" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2784,33 +2784,33 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>40671640000</v>
+        <v>1001460000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2851,10 +2851,10 @@
         <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>100</v>
@@ -2863,10 +2863,10 @@
         <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q21" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2901,33 +2901,33 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>65205040000</v>
+        <v>10710500000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2968,7 +2968,7 @@
         <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2980,10 +2980,10 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q22" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>114852670000</v>
+        <v>317944150000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3027,24 +3027,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3053,17 +3053,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -3135,33 +3135,33 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>50054370000</v>
+        <v>5891850000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3170,17 +3170,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -3205,7 +3205,7 @@
         <v>100</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
@@ -3214,10 +3214,10 @@
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q24" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3252,33 +3252,33 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>95645370000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3287,17 +3287,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -3322,7 +3322,7 @@
         <v>100</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>100</v>
@@ -3331,10 +3331,10 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q25" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3369,33 +3369,33 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>105914680000</v>
+        <v>53136840000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3404,17 +3404,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -3486,33 +3486,33 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>106528210000</v>
+        <v>729500000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -3603,33 +3603,33 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>139571760000</v>
+        <v>1376500000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3638,17 +3638,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -3670,10 +3670,10 @@
         <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
@@ -3682,10 +3682,10 @@
         <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q28" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3720,33 +3720,33 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>31572500000</v>
+        <v>1230000000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3755,17 +3755,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3837,33 +3837,33 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>81321040000</v>
+        <v>42331120000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3872,17 +3872,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3904,10 +3904,10 @@
         <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30" t="n">
         <v>100</v>
@@ -3916,10 +3916,10 @@
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q30" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3954,33 +3954,33 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>360100000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440507)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3989,17 +3989,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>3898470000</v>
+        <v>10675360000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4080,24 +4080,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>1001460000</v>
+        <v>1707230000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4197,24 +4197,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4223,17 +4223,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4255,7 +4255,7 @@
         <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4267,10 +4267,10 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q33" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4305,33 +4305,33 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>53136840000</v>
+        <v>5127100000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>99.95</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4369,13 +4369,13 @@
         <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>100</v>
@@ -4384,16 +4384,16 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>100</v>
+        <v>79.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>100</v>
+        <v>99.98</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4422,33 +4422,33 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>82576290000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4457,24 +4457,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>100</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4486,10 +4486,10 @@
         <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>99.86</v>
       </c>
       <c r="L35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4501,16 +4501,16 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>90</v>
+        <v>79.97</v>
       </c>
       <c r="Q35" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>100</v>
+        <v>99.97</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>128489370000</v>
+        <v>345163450000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -4548,24 +4548,24 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4579,19 +4579,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>100</v>
+        <v>99.83</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4603,13 +4603,13 @@
         <v>100</v>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N36" t="n">
         <v>100</v>
@@ -4618,16 +4618,16 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>80</v>
+        <v>99.86</v>
       </c>
       <c r="Q36" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>100</v>
+        <v>99.86</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4656,33 +4656,33 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>5127100000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="G37" t="n">
         <v>100</v>
@@ -4717,7 +4717,7 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="K37" t="n">
         <v>100</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>80</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="Q37" t="n">
         <v>80</v>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>98.87</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4773,33 +4773,33 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>1707230000</v>
+        <v>39404370000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4808,24 +4808,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4837,10 +4837,10 @@
         <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>100</v>
+        <v>94.89</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4852,16 +4852,16 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>80</v>
+        <v>88.98</v>
       </c>
       <c r="Q38" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>98.86</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4890,33 +4890,33 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>10675360000</v>
+        <v>95645370000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4925,21 +4925,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>96.02</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -4951,7 +4951,7 @@
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>100</v>
+        <v>92.03</v>
       </c>
       <c r="K39" t="n">
         <v>100</v>
@@ -4969,16 +4969,16 @@
         <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>90</v>
+        <v>98.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -5007,33 +5007,33 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>287629890000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5042,21 +5042,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>95.94</v>
       </c>
       <c r="G40" t="n">
         <v>100</v>
@@ -5068,7 +5068,7 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>100</v>
+        <v>91.87</v>
       </c>
       <c r="K40" t="n">
         <v>100</v>
@@ -5077,7 +5077,7 @@
         <v>100</v>
       </c>
       <c r="M40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -5086,16 +5086,16 @@
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>100</v>
+        <v>88.78</v>
       </c>
       <c r="Q40" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>100</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5124,33 +5124,33 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>64847500000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5159,21 +5159,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="G41" t="n">
         <v>100</v>
@@ -5185,16 +5185,16 @@
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>100</v>
+        <v>90.97</v>
       </c>
       <c r="K41" t="n">
         <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41" t="n">
         <v>100</v>
@@ -5203,16 +5203,16 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>80</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="Q41" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>100</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5241,33 +5241,33 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>10808640000</v>
+        <v>82576290000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5276,24 +5276,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>100</v>
+        <v>97.13</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5305,13 +5305,13 @@
         <v>100</v>
       </c>
       <c r="K42" t="n">
-        <v>100</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>100</v>
@@ -5320,16 +5320,16 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>100</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>100</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5358,33 +5358,33 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>42331120000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5393,21 +5393,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>100</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="G43" t="n">
         <v>100</v>
@@ -5419,16 +5419,16 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>100</v>
+        <v>91.63</v>
       </c>
       <c r="K43" t="n">
         <v>100</v>
       </c>
       <c r="L43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>100</v>
@@ -5437,16 +5437,16 @@
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>100</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="Q43" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>100</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5475,33 +5475,33 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>1230000000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5510,24 +5510,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5539,13 +5539,13 @@
         <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>100</v>
+        <v>93.59</v>
       </c>
       <c r="L44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>100</v>
@@ -5554,16 +5554,16 @@
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>100</v>
+        <v>78.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>1376500000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -5601,24 +5601,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5627,21 +5627,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>93.92</v>
       </c>
       <c r="G45" t="n">
         <v>100</v>
@@ -5653,7 +5653,7 @@
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>87.83</v>
       </c>
       <c r="K45" t="n">
         <v>100</v>
@@ -5671,7 +5671,7 @@
         <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>100</v>
+        <v>98.17</v>
       </c>
       <c r="Q45" t="n">
         <v>100</v>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>100</v>
+        <v>98.17</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>2026</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5709,33 +5709,33 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>729500000</v>
+        <v>81321040000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5744,21 +5744,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>100</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="G46" t="n">
         <v>100</v>
@@ -5770,7 +5770,7 @@
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>100</v>
+        <v>78.08</v>
       </c>
       <c r="K46" t="n">
         <v>100</v>
@@ -5788,7 +5788,7 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>100</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="Q46" t="n">
         <v>100</v>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>100</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>40484710000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5835,24 +5835,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5861,24 +5861,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>100</v>
+        <v>94.98</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5890,13 +5890,13 @@
         <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>100</v>
+        <v>84.94</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N47" t="n">
         <v>100</v>
@@ -5905,16 +5905,16 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>80</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="Q47" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>100</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5943,33 +5943,33 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>7789580000</v>
+        <v>65205040000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5995,7 +5995,7 @@
         <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>100</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="H48" t="n">
         <v>100</v>
@@ -6007,7 +6007,7 @@
         <v>100</v>
       </c>
       <c r="K48" t="n">
-        <v>100</v>
+        <v>85.97</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>80</v>
+        <v>77.19</v>
       </c>
       <c r="Q48" t="n">
         <v>80</v>
@@ -6031,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>100</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>1731600000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
@@ -6086,7 +6086,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6112,7 +6112,7 @@
         <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>100</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -6124,7 +6124,7 @@
         <v>100</v>
       </c>
       <c r="K49" t="n">
-        <v>100</v>
+        <v>85.41</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>80</v>
+        <v>77.08</v>
       </c>
       <c r="Q49" t="n">
         <v>80</v>
@@ -6148,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>100</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>360100000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418461)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -6203,7 +6203,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6217,16 +6217,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>90.06</v>
       </c>
       <c r="G50" t="n">
         <v>100</v>
@@ -6238,7 +6238,7 @@
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>100</v>
+        <v>80.12</v>
       </c>
       <c r="K50" t="n">
         <v>100</v>
@@ -6256,7 +6256,7 @@
         <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>80</v>
+        <v>77.02</v>
       </c>
       <c r="Q50" t="n">
         <v>80</v>
@@ -6265,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>100</v>
+        <v>96.27</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>5891850000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -6303,24 +6303,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6334,16 +6334,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="G51" t="n">
         <v>100</v>
@@ -6355,7 +6355,7 @@
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>100</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="K51" t="n">
         <v>100</v>
@@ -6373,7 +6373,7 @@
         <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>80</v>
+        <v>76.7</v>
       </c>
       <c r="Q51" t="n">
         <v>80</v>
@@ -6382,7 +6382,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>100</v>
+        <v>95.88</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>6368000000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -6420,24 +6420,24 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6446,24 +6446,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>100</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -6472,13 +6472,13 @@
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>100</v>
+        <v>94.52</v>
       </c>
       <c r="K52" t="n">
-        <v>100</v>
+        <v>85.13</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -6490,16 +6490,16 @@
         <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>80</v>
+        <v>86.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>100</v>
+        <v>95.78</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6528,33 +6528,33 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>29335310000</v>
+        <v>10808640000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6563,21 +6563,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>87.02</v>
       </c>
       <c r="G53" t="n">
         <v>100</v>
@@ -6589,16 +6589,16 @@
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>100</v>
+        <v>97.62</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
@@ -6607,16 +6607,16 @@
         <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>80</v>
+        <v>85.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>100</v>
+        <v>95.14</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6645,33 +6645,33 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>15177700000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6680,24 +6680,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>95.19</v>
       </c>
       <c r="G54" t="n">
-        <v>100</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -6706,10 +6706,10 @@
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>100</v>
+        <v>90.37</v>
       </c>
       <c r="K54" t="n">
-        <v>100</v>
+        <v>86.52</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -6724,7 +6724,7 @@
         <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>80</v>
+        <v>75.86</v>
       </c>
       <c r="Q54" t="n">
         <v>80</v>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>100</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>13427580000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -6771,24 +6771,24 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6797,24 +6797,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>89.63</v>
       </c>
       <c r="G55" t="n">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,10 +6823,10 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>100</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>100</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>80</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="Q55" t="n">
         <v>80</v>
@@ -6850,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>100</v>
+        <v>94.56</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6879,33 +6879,33 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>9098870000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>88.34</v>
       </c>
       <c r="G56" t="n">
-        <v>100</v>
+        <v>96.78</v>
       </c>
       <c r="H56" t="n">
         <v>100</v>
@@ -6940,16 +6940,16 @@
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>100</v>
+        <v>76.67</v>
       </c>
       <c r="K56" t="n">
-        <v>100</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N56" t="n">
         <v>100</v>
@@ -6958,16 +6958,16 @@
         <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>80</v>
+        <v>93.92</v>
       </c>
       <c r="Q56" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>100</v>
+        <v>93.92</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7031,24 +7031,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>100</v>
+        <v>87.83</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -7060,13 +7060,13 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>100</v>
+        <v>75.66</v>
       </c>
       <c r="L57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>100</v>
@@ -7075,16 +7075,16 @@
         <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>100</v>
+        <v>75.13</v>
       </c>
       <c r="Q57" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>100</v>
+        <v>93.92</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7113,33 +7113,33 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>39404370000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7148,24 +7148,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>85.61</v>
       </c>
       <c r="G58" t="n">
-        <v>100</v>
+        <v>97.61</v>
       </c>
       <c r="H58" t="n">
         <v>100</v>
@@ -7174,13 +7174,13 @@
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>71.22</v>
       </c>
       <c r="K58" t="n">
-        <v>100</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -7192,16 +7192,16 @@
         <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>80</v>
+        <v>84.25</v>
       </c>
       <c r="Q58" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>100</v>
+        <v>93.61</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7230,33 +7230,33 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>74397990000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7270,19 +7270,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="H59" t="n">
         <v>100</v>
@@ -7294,7 +7294,7 @@
         <v>100</v>
       </c>
       <c r="K59" t="n">
-        <v>100</v>
+        <v>67.69</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>80</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="Q59" t="n">
         <v>80</v>
@@ -7318,7 +7318,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>100</v>
+        <v>91.92</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7347,26 +7347,26 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>317944150000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7387,31 +7387,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>80.86</v>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="H60" t="n">
-        <v>95.88</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>100</v>
+        <v>61.72</v>
       </c>
       <c r="K60" t="n">
-        <v>100</v>
+        <v>92.39</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -7423,10 +7423,10 @@
         <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>95.88</v>
+        <v>100</v>
       </c>
       <c r="P60" t="n">
-        <v>78.97</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="Q60" t="n">
         <v>80</v>
@@ -7435,7 +7435,7 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>98.70999999999999</v>
+        <v>90.92</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>10710500000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7499,36 +7499,36 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>100</v>
+        <v>98.95</v>
       </c>
       <c r="H61" t="n">
-        <v>95.33</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>100</v>
+        <v>51.48</v>
       </c>
       <c r="K61" t="n">
-        <v>100</v>
+        <v>97.89</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -7540,10 +7540,10 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>95.33</v>
+        <v>100</v>
       </c>
       <c r="P61" t="n">
-        <v>78.83</v>
+        <v>72.3</v>
       </c>
       <c r="Q61" t="n">
         <v>80</v>
@@ -7552,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>98.54000000000001</v>
+        <v>90.38</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>31225620000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -7590,17 +7590,17 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7616,60 +7616,60 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>82.27</v>
       </c>
       <c r="G62" t="n">
-        <v>100</v>
+        <v>94.05</v>
       </c>
       <c r="H62" t="n">
-        <v>87.83</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>100</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>100</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>100</v>
       </c>
       <c r="O62" t="n">
-        <v>87.83</v>
+        <v>100</v>
       </c>
       <c r="P62" t="n">
-        <v>86.95999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="Q62" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>96.62</v>
+        <v>90.38</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7698,26 +7698,26 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>405581540000</v>
+        <v>4481070000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7738,55 +7738,55 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>100</v>
+        <v>94.36</v>
       </c>
       <c r="H63" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>100</v>
+        <v>61.58</v>
       </c>
       <c r="K63" t="n">
-        <v>100</v>
+        <v>77.42</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N63" t="n">
         <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="P63" t="n">
-        <v>76.5</v>
+        <v>89.72</v>
       </c>
       <c r="Q63" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>95.63</v>
+        <v>89.72</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7815,26 +7815,26 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>345163450000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7850,27 +7850,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>100</v>
+        <v>73.13</v>
       </c>
       <c r="H64" t="n">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
@@ -7879,7 +7879,7 @@
         <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>100</v>
+        <v>46.25</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -7891,10 +7891,10 @@
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="P64" t="n">
-        <v>75.63</v>
+        <v>69.25</v>
       </c>
       <c r="Q64" t="n">
         <v>80</v>
@@ -7903,7 +7903,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>94.53</v>
+        <v>86.56</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7932,26 +7932,26 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>9346940000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -7967,36 +7967,36 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>695184</t>
         </is>
       </c>
       <c r="E65" t="inli